--- a/data/template/boq/Template_BOQ_Report.xlsx
+++ b/data/template/boq/Template_BOQ_Report.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JACOBS\SERVICE\API\data\template\boq\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F23B1E6-4B48-4EC5-A639-6B723D1D13AB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{666EA180-2AEC-4CEC-8165-32858ECB5608}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOQ" sheetId="4" r:id="rId1"/>
+    <sheet name="BOQ PR" sheetId="5" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
@@ -52,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="599">
   <si>
     <t>No</t>
   </si>
@@ -1810,13 +1811,128 @@
   </si>
   <si>
     <t>D.2 Documentation</t>
+  </si>
+  <si>
+    <t>Comcase</t>
+  </si>
+  <si>
+    <t>Material HDPE</t>
+  </si>
+  <si>
+    <t>Meter</t>
+  </si>
+  <si>
+    <t>Pcs</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Permit
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Arial - Burial) All In</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Shopping List Pekerjaan FO Intersite 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Incl. Instalasi Pole) - Aerial (All In)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Shopping List Pekerjaan FO Intersite 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(Excl. Instalasi Pole) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Aerial (All In)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Shopping List Pekerjaan FO Intersite
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>- Burial (All In)</t>
+    </r>
+  </si>
+  <si>
+    <t>Material
+Pole 7</t>
+  </si>
+  <si>
+    <t>Material
+Pole 9</t>
+  </si>
+  <si>
+    <t>Material Kabel
+FO 24 C</t>
+  </si>
+  <si>
+    <t>Material Kabel
+FO 96 C</t>
+  </si>
+  <si>
+    <t>Pole Exist</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1859,8 +1975,22 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1943,6 +2073,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFE2EFD9"/>
         <bgColor rgb="FFE2EFD9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor rgb="FF00B0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AA84F"/>
+        <bgColor rgb="FF6AA84F"/>
       </patternFill>
     </fill>
   </fills>
@@ -2124,69 +2266,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2195,22 +2277,13 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="14" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2267,28 +2340,58 @@
     <xf numFmtId="3" fontId="5" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2308,6 +2411,66 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="14" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2656,4023 +2819,4055 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:263" ht="15" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7" t="s">
+      <c r="R1" s="30"/>
+      <c r="S1" s="30"/>
+      <c r="T1" s="30"/>
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
+      <c r="W1" s="30"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="Z1" s="5"/>
-      <c r="AA1" s="5"/>
-      <c r="AB1" s="5"/>
-      <c r="AC1" s="5"/>
-      <c r="AD1" s="5"/>
-      <c r="AE1" s="5"/>
-      <c r="AF1" s="5"/>
-      <c r="AG1" s="5"/>
-      <c r="AH1" s="5"/>
-      <c r="AI1" s="5"/>
-      <c r="AJ1" s="5"/>
-      <c r="AK1" s="5"/>
-      <c r="AL1" s="5"/>
-      <c r="AM1" s="5"/>
-      <c r="AN1" s="5"/>
-      <c r="AO1" s="5"/>
-      <c r="AP1" s="5"/>
-      <c r="AQ1" s="5"/>
-      <c r="AR1" s="5"/>
-      <c r="AS1" s="5"/>
-      <c r="AT1" s="5"/>
-      <c r="AU1" s="5"/>
-      <c r="AV1" s="5"/>
-      <c r="AW1" s="5"/>
-      <c r="AX1" s="5"/>
-      <c r="AY1" s="5"/>
-      <c r="AZ1" s="5"/>
-      <c r="BA1" s="5"/>
-      <c r="BB1" s="5"/>
-      <c r="BC1" s="5"/>
-      <c r="BD1" s="5"/>
-      <c r="BE1" s="5"/>
-      <c r="BF1" s="5"/>
-      <c r="BG1" s="5"/>
-      <c r="BH1" s="5"/>
-      <c r="BI1" s="5"/>
-      <c r="BJ1" s="5"/>
-      <c r="BK1" s="5"/>
-      <c r="BL1" s="5"/>
-      <c r="BM1" s="5"/>
-      <c r="BN1" s="5"/>
-      <c r="BO1" s="5"/>
-      <c r="BP1" s="5"/>
-      <c r="BQ1" s="5"/>
-      <c r="BR1" s="5"/>
-      <c r="BS1" s="5"/>
-      <c r="BT1" s="5"/>
-      <c r="BU1" s="5"/>
-      <c r="BV1" s="5"/>
-      <c r="BW1" s="5"/>
-      <c r="BX1" s="5"/>
-      <c r="BY1" s="5"/>
-      <c r="BZ1" s="5"/>
-      <c r="CA1" s="5"/>
-      <c r="CB1" s="5"/>
-      <c r="CC1" s="5"/>
-      <c r="CD1" s="5"/>
-      <c r="CE1" s="5"/>
-      <c r="CF1" s="5"/>
-      <c r="CG1" s="5"/>
-      <c r="CH1" s="5"/>
-      <c r="CI1" s="5"/>
-      <c r="CJ1" s="5"/>
-      <c r="CK1" s="5"/>
-      <c r="CL1" s="5"/>
-      <c r="CM1" s="5"/>
-      <c r="CN1" s="5"/>
-      <c r="CO1" s="5"/>
-      <c r="CP1" s="5"/>
-      <c r="CQ1" s="5"/>
-      <c r="CR1" s="5"/>
-      <c r="CS1" s="5"/>
-      <c r="CT1" s="5"/>
-      <c r="CU1" s="5"/>
-      <c r="CV1" s="5"/>
-      <c r="CW1" s="5"/>
-      <c r="CX1" s="5"/>
-      <c r="CY1" s="5"/>
-      <c r="CZ1" s="5"/>
-      <c r="DA1" s="5"/>
-      <c r="DB1" s="5"/>
-      <c r="DC1" s="5"/>
-      <c r="DD1" s="5"/>
-      <c r="DE1" s="5"/>
-      <c r="DF1" s="5"/>
-      <c r="DG1" s="5"/>
-      <c r="DH1" s="5"/>
-      <c r="DI1" s="5"/>
-      <c r="DJ1" s="5"/>
-      <c r="DK1" s="5"/>
-      <c r="DL1" s="5"/>
-      <c r="DM1" s="5"/>
-      <c r="DN1" s="5"/>
-      <c r="DO1" s="5"/>
-      <c r="DP1" s="5"/>
-      <c r="DQ1" s="5"/>
-      <c r="DR1" s="5"/>
-      <c r="DS1" s="5"/>
-      <c r="DT1" s="5"/>
-      <c r="DU1" s="5"/>
-      <c r="DV1" s="5"/>
-      <c r="DW1" s="5"/>
-      <c r="DX1" s="5"/>
-      <c r="DY1" s="5"/>
-      <c r="DZ1" s="5"/>
-      <c r="EA1" s="5"/>
-      <c r="EB1" s="5"/>
-      <c r="EC1" s="5"/>
-      <c r="ED1" s="5"/>
-      <c r="EE1" s="5"/>
-      <c r="EF1" s="5"/>
-      <c r="EG1" s="5"/>
-      <c r="EH1" s="5"/>
-      <c r="EI1" s="5"/>
-      <c r="EJ1" s="5"/>
-      <c r="EK1" s="5"/>
-      <c r="EL1" s="5"/>
-      <c r="EM1" s="5"/>
-      <c r="EN1" s="5"/>
-      <c r="EO1" s="5"/>
-      <c r="EP1" s="5"/>
-      <c r="EQ1" s="5"/>
-      <c r="ER1" s="5"/>
-      <c r="ES1" s="5"/>
-      <c r="ET1" s="5"/>
-      <c r="EU1" s="5"/>
-      <c r="EV1" s="5"/>
-      <c r="EW1" s="5"/>
-      <c r="EX1" s="5"/>
-      <c r="EY1" s="5"/>
-      <c r="EZ1" s="6"/>
-      <c r="FA1" s="4" t="s">
+      <c r="Z1" s="30"/>
+      <c r="AA1" s="30"/>
+      <c r="AB1" s="30"/>
+      <c r="AC1" s="30"/>
+      <c r="AD1" s="30"/>
+      <c r="AE1" s="30"/>
+      <c r="AF1" s="30"/>
+      <c r="AG1" s="30"/>
+      <c r="AH1" s="30"/>
+      <c r="AI1" s="30"/>
+      <c r="AJ1" s="30"/>
+      <c r="AK1" s="30"/>
+      <c r="AL1" s="30"/>
+      <c r="AM1" s="30"/>
+      <c r="AN1" s="30"/>
+      <c r="AO1" s="30"/>
+      <c r="AP1" s="30"/>
+      <c r="AQ1" s="30"/>
+      <c r="AR1" s="30"/>
+      <c r="AS1" s="30"/>
+      <c r="AT1" s="30"/>
+      <c r="AU1" s="30"/>
+      <c r="AV1" s="30"/>
+      <c r="AW1" s="30"/>
+      <c r="AX1" s="30"/>
+      <c r="AY1" s="30"/>
+      <c r="AZ1" s="30"/>
+      <c r="BA1" s="30"/>
+      <c r="BB1" s="30"/>
+      <c r="BC1" s="30"/>
+      <c r="BD1" s="30"/>
+      <c r="BE1" s="30"/>
+      <c r="BF1" s="30"/>
+      <c r="BG1" s="30"/>
+      <c r="BH1" s="30"/>
+      <c r="BI1" s="30"/>
+      <c r="BJ1" s="30"/>
+      <c r="BK1" s="30"/>
+      <c r="BL1" s="30"/>
+      <c r="BM1" s="30"/>
+      <c r="BN1" s="30"/>
+      <c r="BO1" s="30"/>
+      <c r="BP1" s="30"/>
+      <c r="BQ1" s="30"/>
+      <c r="BR1" s="30"/>
+      <c r="BS1" s="30"/>
+      <c r="BT1" s="30"/>
+      <c r="BU1" s="30"/>
+      <c r="BV1" s="30"/>
+      <c r="BW1" s="30"/>
+      <c r="BX1" s="30"/>
+      <c r="BY1" s="30"/>
+      <c r="BZ1" s="30"/>
+      <c r="CA1" s="30"/>
+      <c r="CB1" s="30"/>
+      <c r="CC1" s="30"/>
+      <c r="CD1" s="30"/>
+      <c r="CE1" s="30"/>
+      <c r="CF1" s="30"/>
+      <c r="CG1" s="30"/>
+      <c r="CH1" s="30"/>
+      <c r="CI1" s="30"/>
+      <c r="CJ1" s="30"/>
+      <c r="CK1" s="30"/>
+      <c r="CL1" s="30"/>
+      <c r="CM1" s="30"/>
+      <c r="CN1" s="30"/>
+      <c r="CO1" s="30"/>
+      <c r="CP1" s="30"/>
+      <c r="CQ1" s="30"/>
+      <c r="CR1" s="30"/>
+      <c r="CS1" s="30"/>
+      <c r="CT1" s="30"/>
+      <c r="CU1" s="30"/>
+      <c r="CV1" s="30"/>
+      <c r="CW1" s="30"/>
+      <c r="CX1" s="30"/>
+      <c r="CY1" s="30"/>
+      <c r="CZ1" s="30"/>
+      <c r="DA1" s="30"/>
+      <c r="DB1" s="30"/>
+      <c r="DC1" s="30"/>
+      <c r="DD1" s="30"/>
+      <c r="DE1" s="30"/>
+      <c r="DF1" s="30"/>
+      <c r="DG1" s="30"/>
+      <c r="DH1" s="30"/>
+      <c r="DI1" s="30"/>
+      <c r="DJ1" s="30"/>
+      <c r="DK1" s="30"/>
+      <c r="DL1" s="30"/>
+      <c r="DM1" s="30"/>
+      <c r="DN1" s="30"/>
+      <c r="DO1" s="30"/>
+      <c r="DP1" s="30"/>
+      <c r="DQ1" s="30"/>
+      <c r="DR1" s="30"/>
+      <c r="DS1" s="30"/>
+      <c r="DT1" s="30"/>
+      <c r="DU1" s="30"/>
+      <c r="DV1" s="30"/>
+      <c r="DW1" s="30"/>
+      <c r="DX1" s="30"/>
+      <c r="DY1" s="30"/>
+      <c r="DZ1" s="30"/>
+      <c r="EA1" s="30"/>
+      <c r="EB1" s="30"/>
+      <c r="EC1" s="30"/>
+      <c r="ED1" s="30"/>
+      <c r="EE1" s="30"/>
+      <c r="EF1" s="30"/>
+      <c r="EG1" s="30"/>
+      <c r="EH1" s="30"/>
+      <c r="EI1" s="30"/>
+      <c r="EJ1" s="30"/>
+      <c r="EK1" s="30"/>
+      <c r="EL1" s="30"/>
+      <c r="EM1" s="30"/>
+      <c r="EN1" s="30"/>
+      <c r="EO1" s="30"/>
+      <c r="EP1" s="30"/>
+      <c r="EQ1" s="30"/>
+      <c r="ER1" s="30"/>
+      <c r="ES1" s="30"/>
+      <c r="ET1" s="30"/>
+      <c r="EU1" s="30"/>
+      <c r="EV1" s="30"/>
+      <c r="EW1" s="30"/>
+      <c r="EX1" s="30"/>
+      <c r="EY1" s="30"/>
+      <c r="EZ1" s="31"/>
+      <c r="FA1" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="FB1" s="5"/>
-      <c r="FC1" s="5"/>
-      <c r="FD1" s="5"/>
-      <c r="FE1" s="5"/>
-      <c r="FF1" s="5"/>
-      <c r="FG1" s="5"/>
-      <c r="FH1" s="5"/>
-      <c r="FI1" s="5"/>
-      <c r="FJ1" s="5"/>
-      <c r="FK1" s="5"/>
-      <c r="FL1" s="5"/>
-      <c r="FM1" s="5"/>
-      <c r="FN1" s="5"/>
-      <c r="FO1" s="5"/>
-      <c r="FP1" s="5"/>
-      <c r="FQ1" s="5"/>
-      <c r="FR1" s="5"/>
-      <c r="FS1" s="5"/>
-      <c r="FT1" s="5"/>
-      <c r="FU1" s="5"/>
-      <c r="FV1" s="5"/>
-      <c r="FW1" s="5"/>
-      <c r="FX1" s="5"/>
-      <c r="FY1" s="5"/>
-      <c r="FZ1" s="5"/>
-      <c r="GA1" s="5"/>
-      <c r="GB1" s="5"/>
-      <c r="GC1" s="5"/>
-      <c r="GD1" s="5"/>
-      <c r="GE1" s="5"/>
-      <c r="GF1" s="5"/>
-      <c r="GG1" s="5"/>
-      <c r="GH1" s="5"/>
-      <c r="GI1" s="5"/>
-      <c r="GJ1" s="5"/>
-      <c r="GK1" s="5"/>
-      <c r="GL1" s="5"/>
-      <c r="GM1" s="5"/>
-      <c r="GN1" s="5"/>
-      <c r="GO1" s="5"/>
-      <c r="GP1" s="5"/>
-      <c r="GQ1" s="5"/>
-      <c r="GR1" s="5"/>
-      <c r="GS1" s="5"/>
-      <c r="GT1" s="5"/>
-      <c r="GU1" s="5"/>
-      <c r="GV1" s="5"/>
-      <c r="GW1" s="5"/>
-      <c r="GX1" s="5"/>
-      <c r="GY1" s="5"/>
-      <c r="GZ1" s="5"/>
-      <c r="HA1" s="5"/>
-      <c r="HB1" s="5"/>
-      <c r="HC1" s="5"/>
-      <c r="HD1" s="5"/>
-      <c r="HE1" s="5"/>
-      <c r="HF1" s="5"/>
-      <c r="HG1" s="5"/>
-      <c r="HH1" s="5"/>
-      <c r="HI1" s="5"/>
-      <c r="HJ1" s="5"/>
-      <c r="HK1" s="5"/>
-      <c r="HL1" s="5"/>
-      <c r="HM1" s="5"/>
-      <c r="HN1" s="5"/>
-      <c r="HO1" s="5"/>
-      <c r="HP1" s="5"/>
-      <c r="HQ1" s="5"/>
-      <c r="HR1" s="5"/>
-      <c r="HS1" s="5"/>
-      <c r="HT1" s="5"/>
-      <c r="HU1" s="5"/>
-      <c r="HV1" s="5"/>
-      <c r="HW1" s="5"/>
-      <c r="HX1" s="5"/>
-      <c r="HY1" s="5"/>
-      <c r="HZ1" s="5"/>
-      <c r="IA1" s="5"/>
-      <c r="IB1" s="5"/>
-      <c r="IC1" s="5"/>
-      <c r="ID1" s="5"/>
-      <c r="IE1" s="5"/>
-      <c r="IF1" s="5"/>
-      <c r="IG1" s="5"/>
-      <c r="IH1" s="5"/>
-      <c r="II1" s="5"/>
-      <c r="IJ1" s="5"/>
-      <c r="IK1" s="5"/>
-      <c r="IL1" s="5"/>
-      <c r="IM1" s="5"/>
-      <c r="IN1" s="5"/>
-      <c r="IO1" s="5"/>
-      <c r="IP1" s="5"/>
-      <c r="IQ1" s="5"/>
-      <c r="IR1" s="5"/>
-      <c r="IS1" s="5"/>
-      <c r="IT1" s="5"/>
-      <c r="IU1" s="5"/>
-      <c r="IV1" s="5"/>
-      <c r="IW1" s="5"/>
-      <c r="IX1" s="6"/>
-      <c r="IY1" s="7" t="s">
+      <c r="FB1" s="30"/>
+      <c r="FC1" s="30"/>
+      <c r="FD1" s="30"/>
+      <c r="FE1" s="30"/>
+      <c r="FF1" s="30"/>
+      <c r="FG1" s="30"/>
+      <c r="FH1" s="30"/>
+      <c r="FI1" s="30"/>
+      <c r="FJ1" s="30"/>
+      <c r="FK1" s="30"/>
+      <c r="FL1" s="30"/>
+      <c r="FM1" s="30"/>
+      <c r="FN1" s="30"/>
+      <c r="FO1" s="30"/>
+      <c r="FP1" s="30"/>
+      <c r="FQ1" s="30"/>
+      <c r="FR1" s="30"/>
+      <c r="FS1" s="30"/>
+      <c r="FT1" s="30"/>
+      <c r="FU1" s="30"/>
+      <c r="FV1" s="30"/>
+      <c r="FW1" s="30"/>
+      <c r="FX1" s="30"/>
+      <c r="FY1" s="30"/>
+      <c r="FZ1" s="30"/>
+      <c r="GA1" s="30"/>
+      <c r="GB1" s="30"/>
+      <c r="GC1" s="30"/>
+      <c r="GD1" s="30"/>
+      <c r="GE1" s="30"/>
+      <c r="GF1" s="30"/>
+      <c r="GG1" s="30"/>
+      <c r="GH1" s="30"/>
+      <c r="GI1" s="30"/>
+      <c r="GJ1" s="30"/>
+      <c r="GK1" s="30"/>
+      <c r="GL1" s="30"/>
+      <c r="GM1" s="30"/>
+      <c r="GN1" s="30"/>
+      <c r="GO1" s="30"/>
+      <c r="GP1" s="30"/>
+      <c r="GQ1" s="30"/>
+      <c r="GR1" s="30"/>
+      <c r="GS1" s="30"/>
+      <c r="GT1" s="30"/>
+      <c r="GU1" s="30"/>
+      <c r="GV1" s="30"/>
+      <c r="GW1" s="30"/>
+      <c r="GX1" s="30"/>
+      <c r="GY1" s="30"/>
+      <c r="GZ1" s="30"/>
+      <c r="HA1" s="30"/>
+      <c r="HB1" s="30"/>
+      <c r="HC1" s="30"/>
+      <c r="HD1" s="30"/>
+      <c r="HE1" s="30"/>
+      <c r="HF1" s="30"/>
+      <c r="HG1" s="30"/>
+      <c r="HH1" s="30"/>
+      <c r="HI1" s="30"/>
+      <c r="HJ1" s="30"/>
+      <c r="HK1" s="30"/>
+      <c r="HL1" s="30"/>
+      <c r="HM1" s="30"/>
+      <c r="HN1" s="30"/>
+      <c r="HO1" s="30"/>
+      <c r="HP1" s="30"/>
+      <c r="HQ1" s="30"/>
+      <c r="HR1" s="30"/>
+      <c r="HS1" s="30"/>
+      <c r="HT1" s="30"/>
+      <c r="HU1" s="30"/>
+      <c r="HV1" s="30"/>
+      <c r="HW1" s="30"/>
+      <c r="HX1" s="30"/>
+      <c r="HY1" s="30"/>
+      <c r="HZ1" s="30"/>
+      <c r="IA1" s="30"/>
+      <c r="IB1" s="30"/>
+      <c r="IC1" s="30"/>
+      <c r="ID1" s="30"/>
+      <c r="IE1" s="30"/>
+      <c r="IF1" s="30"/>
+      <c r="IG1" s="30"/>
+      <c r="IH1" s="30"/>
+      <c r="II1" s="30"/>
+      <c r="IJ1" s="30"/>
+      <c r="IK1" s="30"/>
+      <c r="IL1" s="30"/>
+      <c r="IM1" s="30"/>
+      <c r="IN1" s="30"/>
+      <c r="IO1" s="30"/>
+      <c r="IP1" s="30"/>
+      <c r="IQ1" s="30"/>
+      <c r="IR1" s="30"/>
+      <c r="IS1" s="30"/>
+      <c r="IT1" s="30"/>
+      <c r="IU1" s="30"/>
+      <c r="IV1" s="30"/>
+      <c r="IW1" s="30"/>
+      <c r="IX1" s="31"/>
+      <c r="IY1" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="IZ1" s="5"/>
-      <c r="JA1" s="5"/>
-      <c r="JB1" s="6"/>
-      <c r="JC1" s="8" t="s">
+      <c r="IZ1" s="30"/>
+      <c r="JA1" s="30"/>
+      <c r="JB1" s="31"/>
+      <c r="JC1" s="33" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:263" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="11"/>
-      <c r="U2" s="11"/>
-      <c r="V2" s="11"/>
-      <c r="W2" s="11"/>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="13" t="s">
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="36"/>
+      <c r="Y2" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="5"/>
-      <c r="AD2" s="5"/>
-      <c r="AE2" s="5"/>
-      <c r="AF2" s="5"/>
-      <c r="AG2" s="5"/>
-      <c r="AH2" s="5"/>
-      <c r="AI2" s="5"/>
-      <c r="AJ2" s="5"/>
-      <c r="AK2" s="5"/>
-      <c r="AL2" s="5"/>
-      <c r="AM2" s="5"/>
-      <c r="AN2" s="5"/>
-      <c r="AO2" s="5"/>
-      <c r="AP2" s="5"/>
-      <c r="AQ2" s="5"/>
-      <c r="AR2" s="5"/>
-      <c r="AS2" s="5"/>
-      <c r="AT2" s="5"/>
-      <c r="AU2" s="5"/>
-      <c r="AV2" s="5"/>
-      <c r="AW2" s="5"/>
-      <c r="AX2" s="5"/>
-      <c r="AY2" s="5"/>
-      <c r="AZ2" s="5"/>
-      <c r="BA2" s="5"/>
-      <c r="BB2" s="5"/>
-      <c r="BC2" s="5"/>
-      <c r="BD2" s="5"/>
-      <c r="BE2" s="5"/>
-      <c r="BF2" s="5"/>
-      <c r="BG2" s="6"/>
-      <c r="BH2" s="14" t="s">
+      <c r="Z2" s="30"/>
+      <c r="AA2" s="30"/>
+      <c r="AB2" s="30"/>
+      <c r="AC2" s="30"/>
+      <c r="AD2" s="30"/>
+      <c r="AE2" s="30"/>
+      <c r="AF2" s="30"/>
+      <c r="AG2" s="30"/>
+      <c r="AH2" s="30"/>
+      <c r="AI2" s="30"/>
+      <c r="AJ2" s="30"/>
+      <c r="AK2" s="30"/>
+      <c r="AL2" s="30"/>
+      <c r="AM2" s="30"/>
+      <c r="AN2" s="30"/>
+      <c r="AO2" s="30"/>
+      <c r="AP2" s="30"/>
+      <c r="AQ2" s="30"/>
+      <c r="AR2" s="30"/>
+      <c r="AS2" s="30"/>
+      <c r="AT2" s="30"/>
+      <c r="AU2" s="30"/>
+      <c r="AV2" s="30"/>
+      <c r="AW2" s="30"/>
+      <c r="AX2" s="30"/>
+      <c r="AY2" s="30"/>
+      <c r="AZ2" s="30"/>
+      <c r="BA2" s="30"/>
+      <c r="BB2" s="30"/>
+      <c r="BC2" s="30"/>
+      <c r="BD2" s="30"/>
+      <c r="BE2" s="30"/>
+      <c r="BF2" s="30"/>
+      <c r="BG2" s="31"/>
+      <c r="BH2" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="BI2" s="5"/>
-      <c r="BJ2" s="5"/>
-      <c r="BK2" s="5"/>
-      <c r="BL2" s="5"/>
-      <c r="BM2" s="5"/>
-      <c r="BN2" s="5"/>
-      <c r="BO2" s="5"/>
-      <c r="BP2" s="5"/>
-      <c r="BQ2" s="6"/>
-      <c r="BR2" s="13" t="s">
+      <c r="BI2" s="30"/>
+      <c r="BJ2" s="30"/>
+      <c r="BK2" s="30"/>
+      <c r="BL2" s="30"/>
+      <c r="BM2" s="30"/>
+      <c r="BN2" s="30"/>
+      <c r="BO2" s="30"/>
+      <c r="BP2" s="30"/>
+      <c r="BQ2" s="31"/>
+      <c r="BR2" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="BS2" s="5"/>
-      <c r="BT2" s="5"/>
-      <c r="BU2" s="5"/>
-      <c r="BV2" s="5"/>
-      <c r="BW2" s="5"/>
-      <c r="BX2" s="5"/>
-      <c r="BY2" s="5"/>
-      <c r="BZ2" s="5"/>
-      <c r="CA2" s="5"/>
-      <c r="CB2" s="5"/>
-      <c r="CC2" s="5"/>
-      <c r="CD2" s="5"/>
-      <c r="CE2" s="5"/>
-      <c r="CF2" s="5"/>
-      <c r="CG2" s="5"/>
-      <c r="CH2" s="5"/>
-      <c r="CI2" s="5"/>
-      <c r="CJ2" s="5"/>
-      <c r="CK2" s="5"/>
-      <c r="CL2" s="6"/>
-      <c r="CM2" s="14" t="s">
+      <c r="BS2" s="30"/>
+      <c r="BT2" s="30"/>
+      <c r="BU2" s="30"/>
+      <c r="BV2" s="30"/>
+      <c r="BW2" s="30"/>
+      <c r="BX2" s="30"/>
+      <c r="BY2" s="30"/>
+      <c r="BZ2" s="30"/>
+      <c r="CA2" s="30"/>
+      <c r="CB2" s="30"/>
+      <c r="CC2" s="30"/>
+      <c r="CD2" s="30"/>
+      <c r="CE2" s="30"/>
+      <c r="CF2" s="30"/>
+      <c r="CG2" s="30"/>
+      <c r="CH2" s="30"/>
+      <c r="CI2" s="30"/>
+      <c r="CJ2" s="30"/>
+      <c r="CK2" s="30"/>
+      <c r="CL2" s="31"/>
+      <c r="CM2" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="CN2" s="5"/>
-      <c r="CO2" s="5"/>
-      <c r="CP2" s="5"/>
-      <c r="CQ2" s="5"/>
-      <c r="CR2" s="5"/>
-      <c r="CS2" s="5"/>
-      <c r="CT2" s="5"/>
-      <c r="CU2" s="5"/>
-      <c r="CV2" s="5"/>
-      <c r="CW2" s="5"/>
-      <c r="CX2" s="5"/>
-      <c r="CY2" s="5"/>
-      <c r="CZ2" s="5"/>
-      <c r="DA2" s="5"/>
-      <c r="DB2" s="5"/>
-      <c r="DC2" s="5"/>
-      <c r="DD2" s="5"/>
-      <c r="DE2" s="5"/>
-      <c r="DF2" s="5"/>
-      <c r="DG2" s="5"/>
-      <c r="DH2" s="5"/>
-      <c r="DI2" s="5"/>
-      <c r="DJ2" s="5"/>
-      <c r="DK2" s="6"/>
-      <c r="DL2" s="13" t="s">
+      <c r="CN2" s="30"/>
+      <c r="CO2" s="30"/>
+      <c r="CP2" s="30"/>
+      <c r="CQ2" s="30"/>
+      <c r="CR2" s="30"/>
+      <c r="CS2" s="30"/>
+      <c r="CT2" s="30"/>
+      <c r="CU2" s="30"/>
+      <c r="CV2" s="30"/>
+      <c r="CW2" s="30"/>
+      <c r="CX2" s="30"/>
+      <c r="CY2" s="30"/>
+      <c r="CZ2" s="30"/>
+      <c r="DA2" s="30"/>
+      <c r="DB2" s="30"/>
+      <c r="DC2" s="30"/>
+      <c r="DD2" s="30"/>
+      <c r="DE2" s="30"/>
+      <c r="DF2" s="30"/>
+      <c r="DG2" s="30"/>
+      <c r="DH2" s="30"/>
+      <c r="DI2" s="30"/>
+      <c r="DJ2" s="30"/>
+      <c r="DK2" s="31"/>
+      <c r="DL2" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="DM2" s="5"/>
-      <c r="DN2" s="5"/>
-      <c r="DO2" s="5"/>
-      <c r="DP2" s="5"/>
-      <c r="DQ2" s="5"/>
-      <c r="DR2" s="5"/>
-      <c r="DS2" s="6"/>
-      <c r="DT2" s="14" t="s">
+      <c r="DM2" s="30"/>
+      <c r="DN2" s="30"/>
+      <c r="DO2" s="30"/>
+      <c r="DP2" s="30"/>
+      <c r="DQ2" s="30"/>
+      <c r="DR2" s="30"/>
+      <c r="DS2" s="31"/>
+      <c r="DT2" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="DU2" s="13" t="s">
+      <c r="DU2" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="DV2" s="11"/>
-      <c r="DW2" s="11"/>
-      <c r="DX2" s="11"/>
-      <c r="DY2" s="12"/>
-      <c r="DZ2" s="14" t="s">
+      <c r="DV2" s="35"/>
+      <c r="DW2" s="35"/>
+      <c r="DX2" s="35"/>
+      <c r="DY2" s="36"/>
+      <c r="DZ2" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="EA2" s="5"/>
-      <c r="EB2" s="5"/>
-      <c r="EC2" s="5"/>
-      <c r="ED2" s="5"/>
-      <c r="EE2" s="5"/>
-      <c r="EF2" s="5"/>
-      <c r="EG2" s="5"/>
-      <c r="EH2" s="5"/>
-      <c r="EI2" s="5"/>
-      <c r="EJ2" s="5"/>
-      <c r="EK2" s="5"/>
-      <c r="EL2" s="5"/>
-      <c r="EM2" s="5"/>
-      <c r="EN2" s="5"/>
-      <c r="EO2" s="5"/>
-      <c r="EP2" s="5"/>
-      <c r="EQ2" s="5"/>
-      <c r="ER2" s="5"/>
-      <c r="ES2" s="5"/>
-      <c r="ET2" s="5"/>
-      <c r="EU2" s="5"/>
-      <c r="EV2" s="5"/>
-      <c r="EW2" s="5"/>
-      <c r="EX2" s="6"/>
-      <c r="EY2" s="13" t="s">
+      <c r="EA2" s="30"/>
+      <c r="EB2" s="30"/>
+      <c r="EC2" s="30"/>
+      <c r="ED2" s="30"/>
+      <c r="EE2" s="30"/>
+      <c r="EF2" s="30"/>
+      <c r="EG2" s="30"/>
+      <c r="EH2" s="30"/>
+      <c r="EI2" s="30"/>
+      <c r="EJ2" s="30"/>
+      <c r="EK2" s="30"/>
+      <c r="EL2" s="30"/>
+      <c r="EM2" s="30"/>
+      <c r="EN2" s="30"/>
+      <c r="EO2" s="30"/>
+      <c r="EP2" s="30"/>
+      <c r="EQ2" s="30"/>
+      <c r="ER2" s="30"/>
+      <c r="ES2" s="30"/>
+      <c r="ET2" s="30"/>
+      <c r="EU2" s="30"/>
+      <c r="EV2" s="30"/>
+      <c r="EW2" s="30"/>
+      <c r="EX2" s="31"/>
+      <c r="EY2" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="EZ2" s="14" t="s">
+      <c r="EZ2" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="FA2" s="15" t="s">
+      <c r="FA2" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="FB2" s="11"/>
-      <c r="FC2" s="11"/>
-      <c r="FD2" s="11"/>
-      <c r="FE2" s="11"/>
-      <c r="FF2" s="11"/>
-      <c r="FG2" s="11"/>
-      <c r="FH2" s="12"/>
-      <c r="FI2" s="16" t="s">
+      <c r="FB2" s="35"/>
+      <c r="FC2" s="35"/>
+      <c r="FD2" s="35"/>
+      <c r="FE2" s="35"/>
+      <c r="FF2" s="35"/>
+      <c r="FG2" s="35"/>
+      <c r="FH2" s="36"/>
+      <c r="FI2" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="FJ2" s="5"/>
-      <c r="FK2" s="5"/>
-      <c r="FL2" s="5"/>
-      <c r="FM2" s="5"/>
-      <c r="FN2" s="5"/>
-      <c r="FO2" s="5"/>
-      <c r="FP2" s="5"/>
-      <c r="FQ2" s="5"/>
-      <c r="FR2" s="5"/>
-      <c r="FS2" s="5"/>
-      <c r="FT2" s="5"/>
-      <c r="FU2" s="5"/>
-      <c r="FV2" s="5"/>
-      <c r="FW2" s="5"/>
-      <c r="FX2" s="5"/>
-      <c r="FY2" s="5"/>
-      <c r="FZ2" s="5"/>
-      <c r="GA2" s="5"/>
-      <c r="GB2" s="5"/>
-      <c r="GC2" s="6"/>
-      <c r="GD2" s="53" t="s">
+      <c r="FJ2" s="30"/>
+      <c r="FK2" s="30"/>
+      <c r="FL2" s="30"/>
+      <c r="FM2" s="30"/>
+      <c r="FN2" s="30"/>
+      <c r="FO2" s="30"/>
+      <c r="FP2" s="30"/>
+      <c r="FQ2" s="30"/>
+      <c r="FR2" s="30"/>
+      <c r="FS2" s="30"/>
+      <c r="FT2" s="30"/>
+      <c r="FU2" s="30"/>
+      <c r="FV2" s="30"/>
+      <c r="FW2" s="30"/>
+      <c r="FX2" s="30"/>
+      <c r="FY2" s="30"/>
+      <c r="FZ2" s="30"/>
+      <c r="GA2" s="30"/>
+      <c r="GB2" s="30"/>
+      <c r="GC2" s="31"/>
+      <c r="GD2" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="GE2" s="54"/>
-      <c r="GF2" s="54"/>
-      <c r="GG2" s="54"/>
-      <c r="GH2" s="54"/>
-      <c r="GI2" s="54"/>
-      <c r="GJ2" s="55"/>
-      <c r="GK2" s="16" t="s">
+      <c r="GE2" s="60"/>
+      <c r="GF2" s="60"/>
+      <c r="GG2" s="60"/>
+      <c r="GH2" s="60"/>
+      <c r="GI2" s="60"/>
+      <c r="GJ2" s="61"/>
+      <c r="GK2" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="GL2" s="11"/>
-      <c r="GM2" s="11"/>
-      <c r="GN2" s="11"/>
-      <c r="GO2" s="11"/>
-      <c r="GP2" s="12"/>
-      <c r="GQ2" s="56" t="s">
+      <c r="GL2" s="35"/>
+      <c r="GM2" s="35"/>
+      <c r="GN2" s="35"/>
+      <c r="GO2" s="35"/>
+      <c r="GP2" s="36"/>
+      <c r="GQ2" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="GR2" s="57"/>
-      <c r="GS2" s="57"/>
-      <c r="GT2" s="57"/>
-      <c r="GU2" s="57"/>
-      <c r="GV2" s="57"/>
-      <c r="GW2" s="58"/>
-      <c r="GX2" s="16" t="s">
+      <c r="GR2" s="44"/>
+      <c r="GS2" s="44"/>
+      <c r="GT2" s="44"/>
+      <c r="GU2" s="44"/>
+      <c r="GV2" s="44"/>
+      <c r="GW2" s="45"/>
+      <c r="GX2" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="GY2" s="56" t="s">
+      <c r="GY2" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="GZ2" s="57"/>
-      <c r="HA2" s="57"/>
-      <c r="HB2" s="57"/>
-      <c r="HC2" s="16" t="s">
+      <c r="GZ2" s="44"/>
+      <c r="HA2" s="44"/>
+      <c r="HB2" s="44"/>
+      <c r="HC2" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="HD2" s="5"/>
-      <c r="HE2" s="5"/>
-      <c r="HF2" s="5"/>
-      <c r="HG2" s="5"/>
-      <c r="HH2" s="5"/>
-      <c r="HI2" s="6"/>
-      <c r="HJ2" s="56" t="s">
+      <c r="HD2" s="30"/>
+      <c r="HE2" s="30"/>
+      <c r="HF2" s="30"/>
+      <c r="HG2" s="30"/>
+      <c r="HH2" s="30"/>
+      <c r="HI2" s="31"/>
+      <c r="HJ2" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="HK2" s="58"/>
-      <c r="HL2" s="16" t="s">
+      <c r="HK2" s="45"/>
+      <c r="HL2" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="HM2" s="50" t="s">
+      <c r="HM2" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="HN2" s="51"/>
-      <c r="HO2" s="51"/>
-      <c r="HP2" s="51"/>
-      <c r="HQ2" s="51"/>
-      <c r="HR2" s="51"/>
-      <c r="HS2" s="51"/>
-      <c r="HT2" s="51"/>
-      <c r="HU2" s="51"/>
-      <c r="HV2" s="51"/>
-      <c r="HW2" s="51"/>
-      <c r="HX2" s="51"/>
-      <c r="HY2" s="51"/>
-      <c r="HZ2" s="51"/>
-      <c r="IA2" s="51"/>
-      <c r="IB2" s="51"/>
-      <c r="IC2" s="51"/>
-      <c r="ID2" s="51"/>
-      <c r="IE2" s="51"/>
-      <c r="IF2" s="51"/>
-      <c r="IG2" s="51"/>
-      <c r="IH2" s="51"/>
-      <c r="II2" s="52"/>
-      <c r="IJ2" s="16" t="s">
+      <c r="HN2" s="55"/>
+      <c r="HO2" s="55"/>
+      <c r="HP2" s="55"/>
+      <c r="HQ2" s="55"/>
+      <c r="HR2" s="55"/>
+      <c r="HS2" s="55"/>
+      <c r="HT2" s="55"/>
+      <c r="HU2" s="55"/>
+      <c r="HV2" s="55"/>
+      <c r="HW2" s="55"/>
+      <c r="HX2" s="55"/>
+      <c r="HY2" s="55"/>
+      <c r="HZ2" s="55"/>
+      <c r="IA2" s="55"/>
+      <c r="IB2" s="55"/>
+      <c r="IC2" s="55"/>
+      <c r="ID2" s="55"/>
+      <c r="IE2" s="55"/>
+      <c r="IF2" s="55"/>
+      <c r="IG2" s="55"/>
+      <c r="IH2" s="55"/>
+      <c r="II2" s="56"/>
+      <c r="IJ2" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="IK2" s="5"/>
-      <c r="IL2" s="5"/>
-      <c r="IM2" s="5"/>
-      <c r="IN2" s="5"/>
-      <c r="IO2" s="5"/>
-      <c r="IP2" s="5"/>
-      <c r="IQ2" s="5"/>
-      <c r="IR2" s="5"/>
-      <c r="IS2" s="5"/>
-      <c r="IT2" s="5"/>
-      <c r="IU2" s="5"/>
-      <c r="IV2" s="5"/>
-      <c r="IW2" s="6"/>
-      <c r="IX2" s="48" t="s">
+      <c r="IK2" s="30"/>
+      <c r="IL2" s="30"/>
+      <c r="IM2" s="30"/>
+      <c r="IN2" s="30"/>
+      <c r="IO2" s="30"/>
+      <c r="IP2" s="30"/>
+      <c r="IQ2" s="30"/>
+      <c r="IR2" s="30"/>
+      <c r="IS2" s="30"/>
+      <c r="IT2" s="30"/>
+      <c r="IU2" s="30"/>
+      <c r="IV2" s="30"/>
+      <c r="IW2" s="31"/>
+      <c r="IX2" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="IY2" s="17" t="s">
+      <c r="IY2" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="IZ2" s="12"/>
-      <c r="JA2" s="18" t="s">
+      <c r="IZ2" s="36"/>
+      <c r="JA2" s="53" t="s">
         <v>585</v>
       </c>
-      <c r="JB2" s="12"/>
-      <c r="JC2" s="9"/>
+      <c r="JB2" s="36"/>
+      <c r="JC2" s="26"/>
     </row>
     <row r="3" spans="1:263" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="19"/>
-      <c r="R3" s="20"/>
-      <c r="S3" s="20"/>
-      <c r="T3" s="20"/>
-      <c r="U3" s="20"/>
-      <c r="V3" s="20"/>
-      <c r="W3" s="20"/>
-      <c r="X3" s="21"/>
-      <c r="Y3" s="18" t="s">
+      <c r="A3" s="26"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="38"/>
+      <c r="S3" s="38"/>
+      <c r="T3" s="38"/>
+      <c r="U3" s="38"/>
+      <c r="V3" s="38"/>
+      <c r="W3" s="38"/>
+      <c r="X3" s="39"/>
+      <c r="Y3" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="Z3" s="5"/>
-      <c r="AA3" s="5"/>
-      <c r="AB3" s="5"/>
-      <c r="AC3" s="5"/>
-      <c r="AD3" s="6"/>
-      <c r="AE3" s="17" t="s">
+      <c r="Z3" s="30"/>
+      <c r="AA3" s="30"/>
+      <c r="AB3" s="30"/>
+      <c r="AC3" s="30"/>
+      <c r="AD3" s="31"/>
+      <c r="AE3" s="52" t="s">
         <v>45</v>
       </c>
-      <c r="AF3" s="5"/>
-      <c r="AG3" s="5"/>
-      <c r="AH3" s="5"/>
-      <c r="AI3" s="5"/>
-      <c r="AJ3" s="6"/>
-      <c r="AK3" s="18" t="s">
+      <c r="AF3" s="30"/>
+      <c r="AG3" s="30"/>
+      <c r="AH3" s="30"/>
+      <c r="AI3" s="30"/>
+      <c r="AJ3" s="31"/>
+      <c r="AK3" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="AL3" s="5"/>
-      <c r="AM3" s="5"/>
-      <c r="AN3" s="5"/>
-      <c r="AO3" s="5"/>
-      <c r="AP3" s="5"/>
-      <c r="AQ3" s="5"/>
-      <c r="AR3" s="6"/>
-      <c r="AS3" s="17" t="s">
+      <c r="AL3" s="30"/>
+      <c r="AM3" s="30"/>
+      <c r="AN3" s="30"/>
+      <c r="AO3" s="30"/>
+      <c r="AP3" s="30"/>
+      <c r="AQ3" s="30"/>
+      <c r="AR3" s="31"/>
+      <c r="AS3" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="AT3" s="5"/>
-      <c r="AU3" s="5"/>
-      <c r="AV3" s="5"/>
-      <c r="AW3" s="5"/>
-      <c r="AX3" s="5"/>
-      <c r="AY3" s="5"/>
-      <c r="AZ3" s="6"/>
-      <c r="BA3" s="18" t="s">
+      <c r="AT3" s="30"/>
+      <c r="AU3" s="30"/>
+      <c r="AV3" s="30"/>
+      <c r="AW3" s="30"/>
+      <c r="AX3" s="30"/>
+      <c r="AY3" s="30"/>
+      <c r="AZ3" s="31"/>
+      <c r="BA3" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="BB3" s="5"/>
-      <c r="BC3" s="5"/>
-      <c r="BD3" s="5"/>
-      <c r="BE3" s="6"/>
-      <c r="BF3" s="17" t="s">
+      <c r="BB3" s="30"/>
+      <c r="BC3" s="30"/>
+      <c r="BD3" s="30"/>
+      <c r="BE3" s="31"/>
+      <c r="BF3" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="BG3" s="6"/>
-      <c r="BH3" s="18" t="s">
+      <c r="BG3" s="31"/>
+      <c r="BH3" s="53" t="s">
         <v>50</v>
       </c>
-      <c r="BI3" s="5"/>
-      <c r="BJ3" s="5"/>
-      <c r="BK3" s="5"/>
-      <c r="BL3" s="6"/>
-      <c r="BM3" s="17" t="s">
+      <c r="BI3" s="30"/>
+      <c r="BJ3" s="30"/>
+      <c r="BK3" s="30"/>
+      <c r="BL3" s="31"/>
+      <c r="BM3" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BN3" s="5"/>
-      <c r="BO3" s="5"/>
-      <c r="BP3" s="5"/>
-      <c r="BQ3" s="6"/>
-      <c r="BR3" s="18" t="s">
+      <c r="BN3" s="30"/>
+      <c r="BO3" s="30"/>
+      <c r="BP3" s="30"/>
+      <c r="BQ3" s="31"/>
+      <c r="BR3" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="BS3" s="5"/>
-      <c r="BT3" s="5"/>
-      <c r="BU3" s="5"/>
-      <c r="BV3" s="5"/>
-      <c r="BW3" s="5"/>
-      <c r="BX3" s="5"/>
-      <c r="BY3" s="5"/>
-      <c r="BZ3" s="6"/>
-      <c r="CA3" s="17" t="s">
+      <c r="BS3" s="30"/>
+      <c r="BT3" s="30"/>
+      <c r="BU3" s="30"/>
+      <c r="BV3" s="30"/>
+      <c r="BW3" s="30"/>
+      <c r="BX3" s="30"/>
+      <c r="BY3" s="30"/>
+      <c r="BZ3" s="31"/>
+      <c r="CA3" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="CB3" s="5"/>
-      <c r="CC3" s="5"/>
-      <c r="CD3" s="5"/>
-      <c r="CE3" s="5"/>
-      <c r="CF3" s="6"/>
-      <c r="CG3" s="18" t="s">
+      <c r="CB3" s="30"/>
+      <c r="CC3" s="30"/>
+      <c r="CD3" s="30"/>
+      <c r="CE3" s="30"/>
+      <c r="CF3" s="31"/>
+      <c r="CG3" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="CH3" s="5"/>
-      <c r="CI3" s="5"/>
-      <c r="CJ3" s="5"/>
-      <c r="CK3" s="6"/>
-      <c r="CL3" s="22" t="s">
+      <c r="CH3" s="30"/>
+      <c r="CI3" s="30"/>
+      <c r="CJ3" s="30"/>
+      <c r="CK3" s="31"/>
+      <c r="CL3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="CM3" s="18" t="s">
+      <c r="CM3" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="CN3" s="5"/>
-      <c r="CO3" s="6"/>
-      <c r="CP3" s="17" t="s">
+      <c r="CN3" s="30"/>
+      <c r="CO3" s="31"/>
+      <c r="CP3" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="CQ3" s="5"/>
-      <c r="CR3" s="5"/>
-      <c r="CS3" s="5"/>
-      <c r="CT3" s="5"/>
-      <c r="CU3" s="6"/>
-      <c r="CV3" s="18" t="s">
+      <c r="CQ3" s="30"/>
+      <c r="CR3" s="30"/>
+      <c r="CS3" s="30"/>
+      <c r="CT3" s="30"/>
+      <c r="CU3" s="31"/>
+      <c r="CV3" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="CW3" s="5"/>
-      <c r="CX3" s="5"/>
-      <c r="CY3" s="5"/>
-      <c r="CZ3" s="5"/>
-      <c r="DA3" s="6"/>
-      <c r="DB3" s="17" t="s">
+      <c r="CW3" s="30"/>
+      <c r="CX3" s="30"/>
+      <c r="CY3" s="30"/>
+      <c r="CZ3" s="30"/>
+      <c r="DA3" s="31"/>
+      <c r="DB3" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="DC3" s="5"/>
-      <c r="DD3" s="5"/>
-      <c r="DE3" s="5"/>
-      <c r="DF3" s="5"/>
-      <c r="DG3" s="6"/>
-      <c r="DH3" s="18" t="s">
+      <c r="DC3" s="30"/>
+      <c r="DD3" s="30"/>
+      <c r="DE3" s="30"/>
+      <c r="DF3" s="30"/>
+      <c r="DG3" s="31"/>
+      <c r="DH3" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="DI3" s="5"/>
-      <c r="DJ3" s="5"/>
-      <c r="DK3" s="6"/>
-      <c r="DL3" s="23" t="s">
+      <c r="DI3" s="30"/>
+      <c r="DJ3" s="30"/>
+      <c r="DK3" s="31"/>
+      <c r="DL3" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="DM3" s="18" t="s">
+      <c r="DM3" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="DN3" s="5"/>
-      <c r="DO3" s="5"/>
-      <c r="DP3" s="6"/>
-      <c r="DQ3" s="17" t="s">
+      <c r="DN3" s="30"/>
+      <c r="DO3" s="30"/>
+      <c r="DP3" s="31"/>
+      <c r="DQ3" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="DR3" s="5"/>
-      <c r="DS3" s="6"/>
-      <c r="DT3" s="24"/>
-      <c r="DU3" s="19"/>
-      <c r="DV3" s="20"/>
-      <c r="DW3" s="20"/>
-      <c r="DX3" s="20"/>
-      <c r="DY3" s="21"/>
-      <c r="DZ3" s="17" t="s">
+      <c r="DR3" s="30"/>
+      <c r="DS3" s="31"/>
+      <c r="DT3" s="27"/>
+      <c r="DU3" s="37"/>
+      <c r="DV3" s="38"/>
+      <c r="DW3" s="38"/>
+      <c r="DX3" s="38"/>
+      <c r="DY3" s="39"/>
+      <c r="DZ3" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="EA3" s="5"/>
-      <c r="EB3" s="5"/>
-      <c r="EC3" s="5"/>
-      <c r="ED3" s="5"/>
-      <c r="EE3" s="5"/>
-      <c r="EF3" s="5"/>
-      <c r="EG3" s="6"/>
-      <c r="EH3" s="18" t="s">
+      <c r="EA3" s="30"/>
+      <c r="EB3" s="30"/>
+      <c r="EC3" s="30"/>
+      <c r="ED3" s="30"/>
+      <c r="EE3" s="30"/>
+      <c r="EF3" s="30"/>
+      <c r="EG3" s="31"/>
+      <c r="EH3" s="53" t="s">
         <v>65</v>
       </c>
-      <c r="EI3" s="5"/>
-      <c r="EJ3" s="5"/>
-      <c r="EK3" s="5"/>
-      <c r="EL3" s="5"/>
-      <c r="EM3" s="6"/>
-      <c r="EN3" s="17" t="s">
+      <c r="EI3" s="30"/>
+      <c r="EJ3" s="30"/>
+      <c r="EK3" s="30"/>
+      <c r="EL3" s="30"/>
+      <c r="EM3" s="31"/>
+      <c r="EN3" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="EO3" s="6"/>
-      <c r="EP3" s="25" t="s">
+      <c r="EO3" s="31"/>
+      <c r="EP3" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="EQ3" s="17" t="s">
+      <c r="EQ3" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="ER3" s="5"/>
-      <c r="ES3" s="5"/>
-      <c r="ET3" s="5"/>
-      <c r="EU3" s="5"/>
-      <c r="EV3" s="5"/>
-      <c r="EW3" s="5"/>
-      <c r="EX3" s="6"/>
-      <c r="EY3" s="24"/>
-      <c r="EZ3" s="24"/>
-      <c r="FA3" s="19"/>
-      <c r="FB3" s="20"/>
-      <c r="FC3" s="20"/>
-      <c r="FD3" s="20"/>
-      <c r="FE3" s="20"/>
-      <c r="FF3" s="20"/>
-      <c r="FG3" s="20"/>
-      <c r="FH3" s="21"/>
-      <c r="FI3" s="26" t="s">
+      <c r="ER3" s="30"/>
+      <c r="ES3" s="30"/>
+      <c r="ET3" s="30"/>
+      <c r="EU3" s="30"/>
+      <c r="EV3" s="30"/>
+      <c r="EW3" s="30"/>
+      <c r="EX3" s="31"/>
+      <c r="EY3" s="27"/>
+      <c r="EZ3" s="27"/>
+      <c r="FA3" s="37"/>
+      <c r="FB3" s="38"/>
+      <c r="FC3" s="38"/>
+      <c r="FD3" s="38"/>
+      <c r="FE3" s="38"/>
+      <c r="FF3" s="38"/>
+      <c r="FG3" s="38"/>
+      <c r="FH3" s="39"/>
+      <c r="FI3" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="FJ3" s="5"/>
-      <c r="FK3" s="6"/>
-      <c r="FL3" s="10" t="s">
+      <c r="FJ3" s="30"/>
+      <c r="FK3" s="31"/>
+      <c r="FL3" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="FM3" s="5"/>
-      <c r="FN3" s="5"/>
-      <c r="FO3" s="5"/>
-      <c r="FP3" s="5"/>
-      <c r="FQ3" s="6"/>
-      <c r="FR3" s="26" t="s">
+      <c r="FM3" s="30"/>
+      <c r="FN3" s="30"/>
+      <c r="FO3" s="30"/>
+      <c r="FP3" s="30"/>
+      <c r="FQ3" s="31"/>
+      <c r="FR3" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="FS3" s="5"/>
-      <c r="FT3" s="5"/>
-      <c r="FU3" s="5"/>
-      <c r="FV3" s="5"/>
-      <c r="FW3" s="6"/>
-      <c r="FX3" s="10" t="s">
+      <c r="FS3" s="30"/>
+      <c r="FT3" s="30"/>
+      <c r="FU3" s="30"/>
+      <c r="FV3" s="30"/>
+      <c r="FW3" s="31"/>
+      <c r="FX3" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="FY3" s="5"/>
-      <c r="FZ3" s="5"/>
-      <c r="GA3" s="5"/>
-      <c r="GB3" s="5"/>
-      <c r="GC3" s="6"/>
-      <c r="GD3" s="27" t="s">
+      <c r="FY3" s="30"/>
+      <c r="FZ3" s="30"/>
+      <c r="GA3" s="30"/>
+      <c r="GB3" s="30"/>
+      <c r="GC3" s="31"/>
+      <c r="GD3" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="GE3" s="28" t="s">
+      <c r="GE3" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="GF3" s="26" t="s">
+      <c r="GF3" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="GG3" s="6"/>
-      <c r="GH3" s="27"/>
-      <c r="GI3" s="10" t="s">
+      <c r="GG3" s="31"/>
+      <c r="GH3" s="5"/>
+      <c r="GI3" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="GJ3" s="6"/>
-      <c r="GK3" s="19"/>
-      <c r="GL3" s="20"/>
-      <c r="GM3" s="20"/>
-      <c r="GN3" s="20"/>
-      <c r="GO3" s="20"/>
-      <c r="GP3" s="21"/>
-      <c r="GQ3" s="59"/>
-      <c r="GR3" s="60"/>
-      <c r="GS3" s="60"/>
-      <c r="GT3" s="60"/>
-      <c r="GU3" s="60"/>
-      <c r="GV3" s="60"/>
-      <c r="GW3" s="61"/>
-      <c r="GX3" s="24"/>
-      <c r="GY3" s="59"/>
-      <c r="GZ3" s="60"/>
-      <c r="HA3" s="60"/>
-      <c r="HB3" s="60"/>
-      <c r="HC3" s="29" t="s">
+      <c r="GJ3" s="31"/>
+      <c r="GK3" s="37"/>
+      <c r="GL3" s="38"/>
+      <c r="GM3" s="38"/>
+      <c r="GN3" s="38"/>
+      <c r="GO3" s="38"/>
+      <c r="GP3" s="39"/>
+      <c r="GQ3" s="46"/>
+      <c r="GR3" s="47"/>
+      <c r="GS3" s="47"/>
+      <c r="GT3" s="47"/>
+      <c r="GU3" s="47"/>
+      <c r="GV3" s="47"/>
+      <c r="GW3" s="48"/>
+      <c r="GX3" s="27"/>
+      <c r="GY3" s="46"/>
+      <c r="GZ3" s="47"/>
+      <c r="HA3" s="47"/>
+      <c r="HB3" s="47"/>
+      <c r="HC3" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="HD3" s="6"/>
-      <c r="HE3" s="30"/>
-      <c r="HF3" s="31"/>
-      <c r="HG3" s="30"/>
-      <c r="HH3" s="31"/>
-      <c r="HI3" s="30"/>
-      <c r="HJ3" s="59"/>
-      <c r="HK3" s="61"/>
-      <c r="HL3" s="24"/>
-      <c r="HM3" s="10" t="s">
+      <c r="HD3" s="31"/>
+      <c r="HE3" s="7"/>
+      <c r="HF3" s="8"/>
+      <c r="HG3" s="7"/>
+      <c r="HH3" s="8"/>
+      <c r="HI3" s="7"/>
+      <c r="HJ3" s="46"/>
+      <c r="HK3" s="48"/>
+      <c r="HL3" s="27"/>
+      <c r="HM3" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="HN3" s="5"/>
-      <c r="HO3" s="5"/>
-      <c r="HP3" s="5"/>
-      <c r="HQ3" s="5"/>
-      <c r="HR3" s="6"/>
-      <c r="HS3" s="26" t="s">
+      <c r="HN3" s="30"/>
+      <c r="HO3" s="30"/>
+      <c r="HP3" s="30"/>
+      <c r="HQ3" s="30"/>
+      <c r="HR3" s="31"/>
+      <c r="HS3" s="49" t="s">
         <v>79</v>
       </c>
-      <c r="HT3" s="5"/>
-      <c r="HU3" s="5"/>
-      <c r="HV3" s="5"/>
-      <c r="HW3" s="5"/>
-      <c r="HX3" s="6"/>
-      <c r="HY3" s="10" t="s">
+      <c r="HT3" s="30"/>
+      <c r="HU3" s="30"/>
+      <c r="HV3" s="30"/>
+      <c r="HW3" s="30"/>
+      <c r="HX3" s="31"/>
+      <c r="HY3" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="HZ3" s="6"/>
-      <c r="IA3" s="27" t="s">
+      <c r="HZ3" s="31"/>
+      <c r="IA3" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="IB3" s="10" t="s">
+      <c r="IB3" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="IC3" s="5"/>
-      <c r="ID3" s="5"/>
-      <c r="IE3" s="5"/>
-      <c r="IF3" s="5"/>
-      <c r="IG3" s="5"/>
-      <c r="IH3" s="5"/>
-      <c r="II3" s="6"/>
-      <c r="IJ3" s="26" t="s">
+      <c r="IC3" s="30"/>
+      <c r="ID3" s="30"/>
+      <c r="IE3" s="30"/>
+      <c r="IF3" s="30"/>
+      <c r="IG3" s="30"/>
+      <c r="IH3" s="30"/>
+      <c r="II3" s="31"/>
+      <c r="IJ3" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="IK3" s="5"/>
-      <c r="IL3" s="5"/>
-      <c r="IM3" s="5"/>
-      <c r="IN3" s="5"/>
-      <c r="IO3" s="5"/>
-      <c r="IP3" s="5"/>
-      <c r="IQ3" s="5"/>
-      <c r="IR3" s="6"/>
-      <c r="IS3" s="10" t="s">
+      <c r="IK3" s="30"/>
+      <c r="IL3" s="30"/>
+      <c r="IM3" s="30"/>
+      <c r="IN3" s="30"/>
+      <c r="IO3" s="30"/>
+      <c r="IP3" s="30"/>
+      <c r="IQ3" s="30"/>
+      <c r="IR3" s="31"/>
+      <c r="IS3" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="IT3" s="5"/>
-      <c r="IU3" s="5"/>
-      <c r="IV3" s="5"/>
-      <c r="IW3" s="6"/>
-      <c r="IX3" s="49"/>
-      <c r="IY3" s="19"/>
-      <c r="IZ3" s="21"/>
-      <c r="JA3" s="19"/>
-      <c r="JB3" s="21"/>
-      <c r="JC3" s="24"/>
+      <c r="IT3" s="30"/>
+      <c r="IU3" s="30"/>
+      <c r="IV3" s="30"/>
+      <c r="IW3" s="31"/>
+      <c r="IX3" s="51"/>
+      <c r="IY3" s="37"/>
+      <c r="IZ3" s="39"/>
+      <c r="JA3" s="37"/>
+      <c r="JB3" s="39"/>
+      <c r="JC3" s="27"/>
     </row>
     <row r="4" spans="1:263" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="28" t="s">
+      <c r="A4" s="26"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="R4" s="28" t="s">
+      <c r="R4" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="S4" s="28" t="s">
+      <c r="S4" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="T4" s="28" t="s">
+      <c r="T4" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="U4" s="28" t="s">
+      <c r="U4" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="V4" s="28" t="s">
+      <c r="V4" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="W4" s="28" t="s">
+      <c r="W4" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="X4" s="28" t="s">
+      <c r="X4" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="Y4" s="25" t="s">
+      <c r="Y4" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="Z4" s="25" t="s">
+      <c r="Z4" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="AA4" s="25" t="s">
+      <c r="AA4" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="AB4" s="25" t="s">
+      <c r="AB4" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="AC4" s="25" t="s">
+      <c r="AC4" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="AD4" s="25" t="s">
+      <c r="AD4" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="AE4" s="23" t="s">
+      <c r="AE4" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="AF4" s="32" t="s">
+      <c r="AF4" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="AG4" s="23" t="s">
+      <c r="AG4" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="AH4" s="23" t="s">
+      <c r="AH4" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="AI4" s="32" t="s">
+      <c r="AI4" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="AJ4" s="23" t="s">
+      <c r="AJ4" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="AK4" s="25" t="s">
+      <c r="AK4" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="AL4" s="25" t="s">
+      <c r="AL4" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="AM4" s="25" t="s">
+      <c r="AM4" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="AN4" s="25" t="s">
+      <c r="AN4" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="AO4" s="25" t="s">
+      <c r="AO4" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="AP4" s="25" t="s">
+      <c r="AP4" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="AQ4" s="25" t="s">
+      <c r="AQ4" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="AR4" s="25" t="s">
+      <c r="AR4" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="AS4" s="23" t="s">
+      <c r="AS4" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="AT4" s="23" t="s">
+      <c r="AT4" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="AU4" s="23" t="s">
+      <c r="AU4" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="AV4" s="23" t="s">
+      <c r="AV4" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="AW4" s="23" t="s">
+      <c r="AW4" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="AX4" s="23" t="s">
+      <c r="AX4" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="AY4" s="23" t="s">
+      <c r="AY4" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="AZ4" s="23" t="s">
+      <c r="AZ4" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="BA4" s="25" t="s">
+      <c r="BA4" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="BB4" s="25" t="s">
+      <c r="BB4" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="BC4" s="25" t="s">
+      <c r="BC4" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="BD4" s="25" t="s">
+      <c r="BD4" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="BE4" s="25" t="s">
+      <c r="BE4" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="BF4" s="23" t="s">
+      <c r="BF4" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="BG4" s="23" t="s">
+      <c r="BG4" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="BH4" s="25" t="s">
+      <c r="BH4" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="BI4" s="25" t="s">
+      <c r="BI4" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="BJ4" s="25" t="s">
+      <c r="BJ4" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="BK4" s="25" t="s">
+      <c r="BK4" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="BL4" s="25" t="s">
+      <c r="BL4" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="BM4" s="23" t="s">
+      <c r="BM4" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="BN4" s="23" t="s">
+      <c r="BN4" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="BO4" s="23" t="s">
+      <c r="BO4" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="BP4" s="23" t="s">
+      <c r="BP4" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="BQ4" s="23" t="s">
+      <c r="BQ4" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="BR4" s="25" t="s">
+      <c r="BR4" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="BS4" s="25" t="s">
+      <c r="BS4" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="BT4" s="25" t="s">
+      <c r="BT4" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="BU4" s="25" t="s">
+      <c r="BU4" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="BV4" s="25" t="s">
+      <c r="BV4" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="BW4" s="25" t="s">
+      <c r="BW4" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="BX4" s="25" t="s">
+      <c r="BX4" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="BY4" s="25" t="s">
+      <c r="BY4" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="BZ4" s="25" t="s">
+      <c r="BZ4" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="CA4" s="23" t="s">
+      <c r="CA4" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="CB4" s="23" t="s">
+      <c r="CB4" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="CC4" s="23" t="s">
+      <c r="CC4" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="CD4" s="23" t="s">
+      <c r="CD4" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="CE4" s="23" t="s">
+      <c r="CE4" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="CF4" s="23" t="s">
+      <c r="CF4" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="CG4" s="25" t="s">
+      <c r="CG4" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="CH4" s="25" t="s">
+      <c r="CH4" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="CI4" s="25" t="s">
+      <c r="CI4" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="CJ4" s="25" t="s">
+      <c r="CJ4" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="CK4" s="25" t="s">
+      <c r="CK4" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="CL4" s="23" t="s">
+      <c r="CL4" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="CM4" s="25" t="s">
+      <c r="CM4" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="CN4" s="25" t="s">
+      <c r="CN4" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="CO4" s="25" t="s">
+      <c r="CO4" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="CP4" s="23" t="s">
+      <c r="CP4" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="CQ4" s="23" t="s">
+      <c r="CQ4" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="CR4" s="23" t="s">
+      <c r="CR4" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="CS4" s="23" t="s">
+      <c r="CS4" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="CT4" s="23" t="s">
+      <c r="CT4" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="CU4" s="23" t="s">
+      <c r="CU4" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="CV4" s="25" t="s">
+      <c r="CV4" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="CW4" s="25" t="s">
+      <c r="CW4" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="CX4" s="25" t="s">
+      <c r="CX4" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="CY4" s="25" t="s">
+      <c r="CY4" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="CZ4" s="25" t="s">
+      <c r="CZ4" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="DA4" s="25" t="s">
+      <c r="DA4" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="DB4" s="23" t="s">
+      <c r="DB4" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="DC4" s="23" t="s">
+      <c r="DC4" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="DD4" s="23" t="s">
+      <c r="DD4" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="DE4" s="23" t="s">
+      <c r="DE4" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="DF4" s="23" t="s">
+      <c r="DF4" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="DG4" s="23" t="s">
+      <c r="DG4" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="DH4" s="25" t="s">
+      <c r="DH4" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="DI4" s="25" t="s">
+      <c r="DI4" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="DJ4" s="25" t="s">
+      <c r="DJ4" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="DK4" s="25" t="s">
+      <c r="DK4" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="DL4" s="23" t="s">
+      <c r="DL4" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="DM4" s="25" t="s">
+      <c r="DM4" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="DN4" s="25" t="s">
+      <c r="DN4" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="DO4" s="25" t="s">
+      <c r="DO4" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="DP4" s="25" t="s">
+      <c r="DP4" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="DQ4" s="23" t="s">
+      <c r="DQ4" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="DR4" s="23" t="s">
+      <c r="DR4" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="DS4" s="23" t="s">
+      <c r="DS4" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="DT4" s="25" t="s">
+      <c r="DT4" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="DU4" s="23" t="s">
+      <c r="DU4" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="DV4" s="23" t="s">
+      <c r="DV4" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="DW4" s="25" t="s">
+      <c r="DW4" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="DX4" s="25" t="s">
+      <c r="DX4" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="DY4" s="25" t="s">
+      <c r="DY4" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="DZ4" s="23" t="s">
+      <c r="DZ4" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="EA4" s="23" t="s">
+      <c r="EA4" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="EB4" s="23" t="s">
+      <c r="EB4" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="EC4" s="23" t="s">
+      <c r="EC4" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="ED4" s="23" t="s">
+      <c r="ED4" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="EE4" s="23" t="s">
+      <c r="EE4" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="EF4" s="23" t="s">
+      <c r="EF4" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="EG4" s="23" t="s">
+      <c r="EG4" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="EH4" s="25" t="s">
+      <c r="EH4" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="EI4" s="25" t="s">
+      <c r="EI4" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="EJ4" s="25" t="s">
+      <c r="EJ4" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="EK4" s="25" t="s">
+      <c r="EK4" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="EL4" s="25" t="s">
+      <c r="EL4" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="EM4" s="25" t="s">
+      <c r="EM4" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="EN4" s="23" t="s">
+      <c r="EN4" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="EO4" s="23" t="s">
+      <c r="EO4" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="EP4" s="25" t="s">
+      <c r="EP4" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="EQ4" s="23" t="s">
+      <c r="EQ4" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="ER4" s="23" t="s">
+      <c r="ER4" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="ES4" s="23" t="s">
+      <c r="ES4" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="ET4" s="23" t="s">
+      <c r="ET4" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="EU4" s="23" t="s">
+      <c r="EU4" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="EV4" s="23" t="s">
+      <c r="EV4" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="EW4" s="23" t="s">
+      <c r="EW4" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="EX4" s="23" t="s">
+      <c r="EX4" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="EY4" s="25" t="s">
+      <c r="EY4" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="EZ4" s="23" t="s">
+      <c r="EZ4" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="FA4" s="28" t="s">
+      <c r="FA4" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="FB4" s="28" t="s">
+      <c r="FB4" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="FC4" s="28" t="s">
+      <c r="FC4" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="FD4" s="28" t="s">
+      <c r="FD4" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="FE4" s="28" t="s">
+      <c r="FE4" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="FF4" s="28" t="s">
+      <c r="FF4" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="FG4" s="28" t="s">
+      <c r="FG4" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="FH4" s="28" t="s">
+      <c r="FH4" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="FI4" s="27" t="s">
+      <c r="FI4" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="FJ4" s="27" t="s">
+      <c r="FJ4" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="FK4" s="27" t="s">
+      <c r="FK4" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="FL4" s="28" t="s">
+      <c r="FL4" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="FM4" s="28" t="s">
+      <c r="FM4" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="FN4" s="28" t="s">
+      <c r="FN4" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="FO4" s="28" t="s">
+      <c r="FO4" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="FP4" s="28" t="s">
+      <c r="FP4" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="FQ4" s="28" t="s">
+      <c r="FQ4" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="FR4" s="27" t="s">
+      <c r="FR4" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="FS4" s="27" t="s">
+      <c r="FS4" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="FT4" s="27" t="s">
+      <c r="FT4" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="FU4" s="27" t="s">
+      <c r="FU4" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="FV4" s="27" t="s">
+      <c r="FV4" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="FW4" s="27" t="s">
+      <c r="FW4" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="FX4" s="28" t="s">
+      <c r="FX4" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="FY4" s="28" t="s">
+      <c r="FY4" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="FZ4" s="28" t="s">
+      <c r="FZ4" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="GA4" s="28" t="s">
+      <c r="GA4" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="GB4" s="28" t="s">
+      <c r="GB4" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="GC4" s="28" t="s">
+      <c r="GC4" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="GD4" s="27" t="s">
+      <c r="GD4" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="GE4" s="28" t="s">
+      <c r="GE4" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="GF4" s="27" t="s">
+      <c r="GF4" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="GG4" s="27" t="s">
+      <c r="GG4" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="GH4" s="27" t="s">
+      <c r="GH4" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="GI4" s="28" t="s">
+      <c r="GI4" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="GJ4" s="28" t="s">
+      <c r="GJ4" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="GK4" s="27" t="s">
+      <c r="GK4" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="GL4" s="27" t="s">
+      <c r="GL4" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="GM4" s="27" t="s">
+      <c r="GM4" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="GN4" s="27" t="s">
+      <c r="GN4" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="GO4" s="27" t="s">
+      <c r="GO4" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="GP4" s="27" t="s">
+      <c r="GP4" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="GQ4" s="28" t="s">
+      <c r="GQ4" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="GR4" s="28" t="s">
+      <c r="GR4" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="GS4" s="28" t="s">
+      <c r="GS4" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="GT4" s="28" t="s">
+      <c r="GT4" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="GU4" s="28" t="s">
+      <c r="GU4" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="GV4" s="28" t="s">
+      <c r="GV4" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="GW4" s="28" t="s">
+      <c r="GW4" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="GX4" s="27" t="s">
+      <c r="GX4" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="GY4" s="28" t="s">
+      <c r="GY4" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="GZ4" s="28" t="s">
+      <c r="GZ4" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="HA4" s="28" t="s">
+      <c r="HA4" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="HB4" s="28" t="s">
+      <c r="HB4" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="HC4" s="33" t="s">
+      <c r="HC4" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="HD4" s="33" t="s">
+      <c r="HD4" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="HE4" s="28" t="s">
+      <c r="HE4" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="HF4" s="27" t="s">
+      <c r="HF4" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="HG4" s="28" t="s">
+      <c r="HG4" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="HH4" s="27" t="s">
+      <c r="HH4" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="HI4" s="28" t="s">
+      <c r="HI4" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="HJ4" s="28" t="s">
+      <c r="HJ4" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="HK4" s="28" t="s">
+      <c r="HK4" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="HL4" s="27" t="s">
+      <c r="HL4" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="HM4" s="28" t="s">
+      <c r="HM4" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="HN4" s="28" t="s">
+      <c r="HN4" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="HO4" s="28" t="s">
+      <c r="HO4" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="HP4" s="28" t="s">
+      <c r="HP4" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="HQ4" s="28" t="s">
+      <c r="HQ4" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="HR4" s="28" t="s">
+      <c r="HR4" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="HS4" s="27" t="s">
+      <c r="HS4" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="HT4" s="27" t="s">
+      <c r="HT4" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="HU4" s="27" t="s">
+      <c r="HU4" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="HV4" s="27" t="s">
+      <c r="HV4" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="HW4" s="27" t="s">
+      <c r="HW4" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="HX4" s="27" t="s">
+      <c r="HX4" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="HY4" s="28" t="s">
+      <c r="HY4" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="HZ4" s="28" t="s">
+      <c r="HZ4" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="IA4" s="27" t="s">
+      <c r="IA4" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="IB4" s="28" t="s">
+      <c r="IB4" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="IC4" s="28" t="s">
+      <c r="IC4" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="ID4" s="28" t="s">
+      <c r="ID4" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="IE4" s="28" t="s">
+      <c r="IE4" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="IF4" s="28" t="s">
+      <c r="IF4" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="IG4" s="28" t="s">
+      <c r="IG4" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="IH4" s="28" t="s">
+      <c r="IH4" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="II4" s="28" t="s">
+      <c r="II4" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="IJ4" s="27" t="s">
+      <c r="IJ4" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="IK4" s="27" t="s">
+      <c r="IK4" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="IL4" s="27" t="s">
+      <c r="IL4" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="IM4" s="27" t="s">
+      <c r="IM4" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="IN4" s="27" t="s">
+      <c r="IN4" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="IO4" s="27" t="s">
+      <c r="IO4" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="IP4" s="27" t="s">
+      <c r="IP4" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="IQ4" s="27" t="s">
+      <c r="IQ4" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="IR4" s="27" t="s">
+      <c r="IR4" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="IS4" s="28" t="s">
+      <c r="IS4" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="IT4" s="28" t="s">
+      <c r="IT4" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="IU4" s="28" t="s">
+      <c r="IU4" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="IV4" s="28" t="s">
+      <c r="IV4" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="IW4" s="28" t="s">
+      <c r="IW4" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="IX4" s="27" t="s">
+      <c r="IX4" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="IY4" s="23" t="s">
+      <c r="IY4" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="IZ4" s="23" t="s">
+      <c r="IZ4" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="JA4" s="25" t="s">
+      <c r="JA4" s="4" t="s">
         <v>583</v>
       </c>
-      <c r="JB4" s="25" t="s">
+      <c r="JB4" s="4" t="s">
         <v>584</v>
       </c>
-      <c r="JC4" s="34"/>
+      <c r="JC4" s="11"/>
     </row>
     <row r="5" spans="1:263" ht="199.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="35" t="s">
+      <c r="A5" s="26"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="26"/>
+      <c r="O5" s="26"/>
+      <c r="P5" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="Q5" s="36" t="s">
+      <c r="Q5" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="R5" s="36" t="s">
+      <c r="R5" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="S5" s="36" t="s">
+      <c r="S5" s="13" t="s">
         <v>332</v>
       </c>
-      <c r="T5" s="36" t="s">
+      <c r="T5" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="U5" s="36" t="s">
+      <c r="U5" s="13" t="s">
         <v>334</v>
       </c>
-      <c r="V5" s="36" t="s">
+      <c r="V5" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="W5" s="36" t="s">
+      <c r="W5" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="X5" s="36" t="s">
+      <c r="X5" s="13" t="s">
         <v>337</v>
       </c>
-      <c r="Y5" s="41" t="s">
+      <c r="Y5" s="18" t="s">
         <v>338</v>
       </c>
-      <c r="Z5" s="41" t="s">
+      <c r="Z5" s="18" t="s">
         <v>339</v>
       </c>
-      <c r="AA5" s="41" t="s">
+      <c r="AA5" s="18" t="s">
         <v>340</v>
       </c>
-      <c r="AB5" s="41" t="s">
+      <c r="AB5" s="18" t="s">
         <v>341</v>
       </c>
-      <c r="AC5" s="41" t="s">
+      <c r="AC5" s="18" t="s">
         <v>342</v>
       </c>
-      <c r="AD5" s="41" t="s">
+      <c r="AD5" s="18" t="s">
         <v>343</v>
       </c>
-      <c r="AE5" s="42" t="s">
+      <c r="AE5" s="19" t="s">
         <v>344</v>
       </c>
-      <c r="AF5" s="47" t="s">
+      <c r="AF5" s="24" t="s">
         <v>345</v>
       </c>
-      <c r="AG5" s="42" t="s">
+      <c r="AG5" s="19" t="s">
         <v>346</v>
       </c>
-      <c r="AH5" s="42" t="s">
+      <c r="AH5" s="19" t="s">
         <v>347</v>
       </c>
-      <c r="AI5" s="47" t="s">
+      <c r="AI5" s="24" t="s">
         <v>348</v>
       </c>
-      <c r="AJ5" s="42" t="s">
+      <c r="AJ5" s="19" t="s">
         <v>349</v>
       </c>
-      <c r="AK5" s="41" t="s">
+      <c r="AK5" s="18" t="s">
         <v>350</v>
       </c>
-      <c r="AL5" s="41" t="s">
+      <c r="AL5" s="18" t="s">
         <v>351</v>
       </c>
-      <c r="AM5" s="41" t="s">
+      <c r="AM5" s="18" t="s">
         <v>352</v>
       </c>
-      <c r="AN5" s="41" t="s">
+      <c r="AN5" s="18" t="s">
         <v>353</v>
       </c>
-      <c r="AO5" s="41" t="s">
+      <c r="AO5" s="18" t="s">
         <v>354</v>
       </c>
-      <c r="AP5" s="41" t="s">
+      <c r="AP5" s="18" t="s">
         <v>355</v>
       </c>
-      <c r="AQ5" s="41" t="s">
+      <c r="AQ5" s="18" t="s">
         <v>356</v>
       </c>
-      <c r="AR5" s="41" t="s">
+      <c r="AR5" s="18" t="s">
         <v>357</v>
       </c>
-      <c r="AS5" s="42" t="s">
+      <c r="AS5" s="19" t="s">
         <v>358</v>
       </c>
-      <c r="AT5" s="42" t="s">
+      <c r="AT5" s="19" t="s">
         <v>359</v>
       </c>
-      <c r="AU5" s="42" t="s">
+      <c r="AU5" s="19" t="s">
         <v>360</v>
       </c>
-      <c r="AV5" s="42" t="s">
+      <c r="AV5" s="19" t="s">
         <v>361</v>
       </c>
-      <c r="AW5" s="42" t="s">
+      <c r="AW5" s="19" t="s">
         <v>362</v>
       </c>
-      <c r="AX5" s="42" t="s">
+      <c r="AX5" s="19" t="s">
         <v>363</v>
       </c>
-      <c r="AY5" s="42" t="s">
+      <c r="AY5" s="19" t="s">
         <v>364</v>
       </c>
-      <c r="AZ5" s="42" t="s">
+      <c r="AZ5" s="19" t="s">
         <v>365</v>
       </c>
-      <c r="BA5" s="41" t="s">
+      <c r="BA5" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="BB5" s="41" t="s">
+      <c r="BB5" s="18" t="s">
         <v>367</v>
       </c>
-      <c r="BC5" s="41" t="s">
+      <c r="BC5" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="BD5" s="41" t="s">
+      <c r="BD5" s="18" t="s">
         <v>369</v>
       </c>
-      <c r="BE5" s="41" t="s">
+      <c r="BE5" s="18" t="s">
         <v>370</v>
       </c>
-      <c r="BF5" s="42" t="s">
+      <c r="BF5" s="19" t="s">
         <v>371</v>
       </c>
-      <c r="BG5" s="42" t="s">
+      <c r="BG5" s="19" t="s">
         <v>372</v>
       </c>
-      <c r="BH5" s="41" t="s">
+      <c r="BH5" s="18" t="s">
         <v>373</v>
       </c>
-      <c r="BI5" s="41" t="s">
+      <c r="BI5" s="18" t="s">
         <v>374</v>
       </c>
-      <c r="BJ5" s="41" t="s">
+      <c r="BJ5" s="18" t="s">
         <v>375</v>
       </c>
-      <c r="BK5" s="41" t="s">
+      <c r="BK5" s="18" t="s">
         <v>376</v>
       </c>
-      <c r="BL5" s="41" t="s">
+      <c r="BL5" s="18" t="s">
         <v>377</v>
       </c>
-      <c r="BM5" s="42" t="s">
+      <c r="BM5" s="19" t="s">
         <v>378</v>
       </c>
-      <c r="BN5" s="42" t="s">
+      <c r="BN5" s="19" t="s">
         <v>379</v>
       </c>
-      <c r="BO5" s="42" t="s">
+      <c r="BO5" s="19" t="s">
         <v>380</v>
       </c>
-      <c r="BP5" s="42" t="s">
+      <c r="BP5" s="19" t="s">
         <v>381</v>
       </c>
-      <c r="BQ5" s="42" t="s">
+      <c r="BQ5" s="19" t="s">
         <v>382</v>
       </c>
-      <c r="BR5" s="41" t="s">
+      <c r="BR5" s="18" t="s">
         <v>383</v>
       </c>
-      <c r="BS5" s="41" t="s">
+      <c r="BS5" s="18" t="s">
         <v>384</v>
       </c>
-      <c r="BT5" s="41" t="s">
+      <c r="BT5" s="18" t="s">
         <v>385</v>
       </c>
-      <c r="BU5" s="41" t="s">
+      <c r="BU5" s="18" t="s">
         <v>386</v>
       </c>
-      <c r="BV5" s="41" t="s">
+      <c r="BV5" s="18" t="s">
         <v>387</v>
       </c>
-      <c r="BW5" s="41" t="s">
+      <c r="BW5" s="18" t="s">
         <v>388</v>
       </c>
-      <c r="BX5" s="41" t="s">
+      <c r="BX5" s="18" t="s">
         <v>389</v>
       </c>
-      <c r="BY5" s="41" t="s">
+      <c r="BY5" s="18" t="s">
         <v>390</v>
       </c>
-      <c r="BZ5" s="41" t="s">
+      <c r="BZ5" s="18" t="s">
         <v>391</v>
       </c>
-      <c r="CA5" s="42" t="s">
+      <c r="CA5" s="19" t="s">
         <v>392</v>
       </c>
-      <c r="CB5" s="42" t="s">
+      <c r="CB5" s="19" t="s">
         <v>393</v>
       </c>
-      <c r="CC5" s="42" t="s">
+      <c r="CC5" s="19" t="s">
         <v>394</v>
       </c>
-      <c r="CD5" s="42" t="s">
+      <c r="CD5" s="19" t="s">
         <v>395</v>
       </c>
-      <c r="CE5" s="42" t="s">
+      <c r="CE5" s="19" t="s">
         <v>396</v>
       </c>
-      <c r="CF5" s="42" t="s">
+      <c r="CF5" s="19" t="s">
         <v>397</v>
       </c>
-      <c r="CG5" s="41" t="s">
+      <c r="CG5" s="18" t="s">
         <v>398</v>
       </c>
-      <c r="CH5" s="41" t="s">
+      <c r="CH5" s="18" t="s">
         <v>399</v>
       </c>
-      <c r="CI5" s="41" t="s">
+      <c r="CI5" s="18" t="s">
         <v>400</v>
       </c>
-      <c r="CJ5" s="41" t="s">
+      <c r="CJ5" s="18" t="s">
         <v>401</v>
       </c>
-      <c r="CK5" s="41" t="s">
+      <c r="CK5" s="18" t="s">
         <v>402</v>
       </c>
-      <c r="CL5" s="42" t="s">
+      <c r="CL5" s="19" t="s">
         <v>403</v>
       </c>
-      <c r="CM5" s="41" t="s">
+      <c r="CM5" s="18" t="s">
         <v>404</v>
       </c>
-      <c r="CN5" s="41" t="s">
+      <c r="CN5" s="18" t="s">
         <v>405</v>
       </c>
-      <c r="CO5" s="41" t="s">
+      <c r="CO5" s="18" t="s">
         <v>406</v>
       </c>
-      <c r="CP5" s="42" t="s">
+      <c r="CP5" s="19" t="s">
         <v>407</v>
       </c>
-      <c r="CQ5" s="42" t="s">
+      <c r="CQ5" s="19" t="s">
         <v>408</v>
       </c>
-      <c r="CR5" s="42" t="s">
+      <c r="CR5" s="19" t="s">
         <v>409</v>
       </c>
-      <c r="CS5" s="42" t="s">
+      <c r="CS5" s="19" t="s">
         <v>410</v>
       </c>
-      <c r="CT5" s="42" t="s">
+      <c r="CT5" s="19" t="s">
         <v>411</v>
       </c>
-      <c r="CU5" s="42" t="s">
+      <c r="CU5" s="19" t="s">
         <v>412</v>
       </c>
-      <c r="CV5" s="41" t="s">
+      <c r="CV5" s="18" t="s">
         <v>413</v>
       </c>
-      <c r="CW5" s="41" t="s">
+      <c r="CW5" s="18" t="s">
         <v>414</v>
       </c>
-      <c r="CX5" s="41" t="s">
+      <c r="CX5" s="18" t="s">
         <v>415</v>
       </c>
-      <c r="CY5" s="41" t="s">
+      <c r="CY5" s="18" t="s">
         <v>416</v>
       </c>
-      <c r="CZ5" s="41" t="s">
+      <c r="CZ5" s="18" t="s">
         <v>417</v>
       </c>
-      <c r="DA5" s="41" t="s">
+      <c r="DA5" s="18" t="s">
         <v>418</v>
       </c>
-      <c r="DB5" s="42" t="s">
+      <c r="DB5" s="19" t="s">
         <v>419</v>
       </c>
-      <c r="DC5" s="42" t="s">
+      <c r="DC5" s="19" t="s">
         <v>420</v>
       </c>
-      <c r="DD5" s="42" t="s">
+      <c r="DD5" s="19" t="s">
         <v>421</v>
       </c>
-      <c r="DE5" s="42" t="s">
+      <c r="DE5" s="19" t="s">
         <v>422</v>
       </c>
-      <c r="DF5" s="42" t="s">
+      <c r="DF5" s="19" t="s">
         <v>423</v>
       </c>
-      <c r="DG5" s="42" t="s">
+      <c r="DG5" s="19" t="s">
         <v>424</v>
       </c>
-      <c r="DH5" s="41" t="s">
+      <c r="DH5" s="18" t="s">
         <v>425</v>
       </c>
-      <c r="DI5" s="41" t="s">
+      <c r="DI5" s="18" t="s">
         <v>426</v>
       </c>
-      <c r="DJ5" s="41" t="s">
+      <c r="DJ5" s="18" t="s">
         <v>427</v>
       </c>
-      <c r="DK5" s="41" t="s">
+      <c r="DK5" s="18" t="s">
         <v>428</v>
       </c>
-      <c r="DL5" s="42" t="s">
+      <c r="DL5" s="19" t="s">
         <v>429</v>
       </c>
-      <c r="DM5" s="41" t="s">
+      <c r="DM5" s="18" t="s">
         <v>430</v>
       </c>
-      <c r="DN5" s="41" t="s">
+      <c r="DN5" s="18" t="s">
         <v>431</v>
       </c>
-      <c r="DO5" s="41" t="s">
+      <c r="DO5" s="18" t="s">
         <v>432</v>
       </c>
-      <c r="DP5" s="41" t="s">
+      <c r="DP5" s="18" t="s">
         <v>433</v>
       </c>
-      <c r="DQ5" s="42" t="s">
+      <c r="DQ5" s="19" t="s">
         <v>434</v>
       </c>
-      <c r="DR5" s="42" t="s">
+      <c r="DR5" s="19" t="s">
         <v>435</v>
       </c>
-      <c r="DS5" s="42" t="s">
+      <c r="DS5" s="19" t="s">
         <v>436</v>
       </c>
-      <c r="DT5" s="41" t="s">
+      <c r="DT5" s="18" t="s">
         <v>437</v>
       </c>
-      <c r="DU5" s="42" t="s">
+      <c r="DU5" s="19" t="s">
         <v>438</v>
       </c>
-      <c r="DV5" s="42" t="s">
+      <c r="DV5" s="19" t="s">
         <v>439</v>
       </c>
-      <c r="DW5" s="41" t="s">
+      <c r="DW5" s="18" t="s">
         <v>440</v>
       </c>
-      <c r="DX5" s="41" t="s">
+      <c r="DX5" s="18" t="s">
         <v>582</v>
       </c>
-      <c r="DY5" s="41" t="s">
+      <c r="DY5" s="18" t="s">
         <v>441</v>
       </c>
-      <c r="DZ5" s="42" t="s">
+      <c r="DZ5" s="19" t="s">
         <v>442</v>
       </c>
-      <c r="EA5" s="42" t="s">
+      <c r="EA5" s="19" t="s">
         <v>443</v>
       </c>
-      <c r="EB5" s="42" t="s">
+      <c r="EB5" s="19" t="s">
         <v>444</v>
       </c>
-      <c r="EC5" s="42" t="s">
+      <c r="EC5" s="19" t="s">
         <v>445</v>
       </c>
-      <c r="ED5" s="42" t="s">
+      <c r="ED5" s="19" t="s">
         <v>446</v>
       </c>
-      <c r="EE5" s="42" t="s">
+      <c r="EE5" s="19" t="s">
         <v>447</v>
       </c>
-      <c r="EF5" s="42" t="s">
+      <c r="EF5" s="19" t="s">
         <v>448</v>
       </c>
-      <c r="EG5" s="42" t="s">
+      <c r="EG5" s="19" t="s">
         <v>449</v>
       </c>
-      <c r="EH5" s="41" t="s">
+      <c r="EH5" s="18" t="s">
         <v>450</v>
       </c>
-      <c r="EI5" s="41" t="s">
+      <c r="EI5" s="18" t="s">
         <v>451</v>
       </c>
-      <c r="EJ5" s="41" t="s">
+      <c r="EJ5" s="18" t="s">
         <v>452</v>
       </c>
-      <c r="EK5" s="41" t="s">
+      <c r="EK5" s="18" t="s">
         <v>453</v>
       </c>
-      <c r="EL5" s="41" t="s">
+      <c r="EL5" s="18" t="s">
         <v>454</v>
       </c>
-      <c r="EM5" s="41" t="s">
+      <c r="EM5" s="18" t="s">
         <v>455</v>
       </c>
-      <c r="EN5" s="42" t="s">
+      <c r="EN5" s="19" t="s">
         <v>456</v>
       </c>
-      <c r="EO5" s="42" t="s">
+      <c r="EO5" s="19" t="s">
         <v>457</v>
       </c>
-      <c r="EP5" s="41" t="s">
+      <c r="EP5" s="18" t="s">
         <v>458</v>
       </c>
-      <c r="EQ5" s="42" t="s">
+      <c r="EQ5" s="19" t="s">
         <v>459</v>
       </c>
-      <c r="ER5" s="42" t="s">
+      <c r="ER5" s="19" t="s">
         <v>460</v>
       </c>
-      <c r="ES5" s="42" t="s">
+      <c r="ES5" s="19" t="s">
         <v>461</v>
       </c>
-      <c r="ET5" s="42" t="s">
+      <c r="ET5" s="19" t="s">
         <v>462</v>
       </c>
-      <c r="EU5" s="42" t="s">
+      <c r="EU5" s="19" t="s">
         <v>463</v>
       </c>
-      <c r="EV5" s="42" t="s">
+      <c r="EV5" s="19" t="s">
         <v>464</v>
       </c>
-      <c r="EW5" s="42" t="s">
+      <c r="EW5" s="19" t="s">
         <v>465</v>
       </c>
-      <c r="EX5" s="42" t="s">
+      <c r="EX5" s="19" t="s">
         <v>466</v>
       </c>
-      <c r="EY5" s="41" t="s">
+      <c r="EY5" s="18" t="s">
         <v>467</v>
       </c>
-      <c r="EZ5" s="42" t="s">
+      <c r="EZ5" s="19" t="s">
         <v>468</v>
       </c>
-      <c r="FA5" s="36" t="s">
+      <c r="FA5" s="13" t="s">
         <v>469</v>
       </c>
-      <c r="FB5" s="36" t="s">
+      <c r="FB5" s="13" t="s">
         <v>470</v>
       </c>
-      <c r="FC5" s="36" t="s">
+      <c r="FC5" s="13" t="s">
         <v>471</v>
       </c>
-      <c r="FD5" s="36" t="s">
+      <c r="FD5" s="13" t="s">
         <v>472</v>
       </c>
-      <c r="FE5" s="36" t="s">
+      <c r="FE5" s="13" t="s">
         <v>473</v>
       </c>
-      <c r="FF5" s="36" t="s">
+      <c r="FF5" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="FG5" s="36" t="s">
+      <c r="FG5" s="13" t="s">
         <v>475</v>
       </c>
-      <c r="FH5" s="36" t="s">
+      <c r="FH5" s="13" t="s">
         <v>476</v>
       </c>
-      <c r="FI5" s="43" t="s">
+      <c r="FI5" s="20" t="s">
         <v>404</v>
       </c>
-      <c r="FJ5" s="43" t="s">
+      <c r="FJ5" s="20" t="s">
         <v>405</v>
       </c>
-      <c r="FK5" s="43" t="s">
+      <c r="FK5" s="20" t="s">
         <v>406</v>
       </c>
-      <c r="FL5" s="36" t="s">
+      <c r="FL5" s="13" t="s">
         <v>407</v>
       </c>
-      <c r="FM5" s="36" t="s">
+      <c r="FM5" s="13" t="s">
         <v>408</v>
       </c>
-      <c r="FN5" s="36" t="s">
+      <c r="FN5" s="13" t="s">
         <v>409</v>
       </c>
-      <c r="FO5" s="36" t="s">
+      <c r="FO5" s="13" t="s">
         <v>410</v>
       </c>
-      <c r="FP5" s="36" t="s">
+      <c r="FP5" s="13" t="s">
         <v>411</v>
       </c>
-      <c r="FQ5" s="36" t="s">
+      <c r="FQ5" s="13" t="s">
         <v>412</v>
       </c>
-      <c r="FR5" s="43" t="s">
+      <c r="FR5" s="20" t="s">
         <v>413</v>
       </c>
-      <c r="FS5" s="43" t="s">
+      <c r="FS5" s="20" t="s">
         <v>414</v>
       </c>
-      <c r="FT5" s="43" t="s">
+      <c r="FT5" s="20" t="s">
         <v>415</v>
       </c>
-      <c r="FU5" s="43" t="s">
+      <c r="FU5" s="20" t="s">
         <v>416</v>
       </c>
-      <c r="FV5" s="43" t="s">
+      <c r="FV5" s="20" t="s">
         <v>417</v>
       </c>
-      <c r="FW5" s="43" t="s">
+      <c r="FW5" s="20" t="s">
         <v>418</v>
       </c>
-      <c r="FX5" s="36" t="s">
+      <c r="FX5" s="13" t="s">
         <v>419</v>
       </c>
-      <c r="FY5" s="36" t="s">
+      <c r="FY5" s="13" t="s">
         <v>420</v>
       </c>
-      <c r="FZ5" s="36" t="s">
+      <c r="FZ5" s="13" t="s">
         <v>421</v>
       </c>
-      <c r="GA5" s="36" t="s">
+      <c r="GA5" s="13" t="s">
         <v>422</v>
       </c>
-      <c r="GB5" s="36" t="s">
+      <c r="GB5" s="13" t="s">
         <v>423</v>
       </c>
-      <c r="GC5" s="36" t="s">
+      <c r="GC5" s="13" t="s">
         <v>424</v>
       </c>
-      <c r="GD5" s="43" t="s">
+      <c r="GD5" s="20" t="s">
         <v>477</v>
       </c>
-      <c r="GE5" s="36" t="s">
+      <c r="GE5" s="13" t="s">
         <v>478</v>
       </c>
-      <c r="GF5" s="43" t="s">
+      <c r="GF5" s="20" t="s">
         <v>479</v>
       </c>
-      <c r="GG5" s="43" t="s">
+      <c r="GG5" s="20" t="s">
         <v>581</v>
       </c>
-      <c r="GH5" s="43" t="s">
+      <c r="GH5" s="20" t="s">
         <v>480</v>
       </c>
-      <c r="GI5" s="36" t="s">
+      <c r="GI5" s="13" t="s">
         <v>481</v>
       </c>
-      <c r="GJ5" s="36" t="s">
+      <c r="GJ5" s="13" t="s">
         <v>482</v>
       </c>
-      <c r="GK5" s="43" t="s">
+      <c r="GK5" s="20" t="s">
         <v>483</v>
       </c>
-      <c r="GL5" s="43" t="s">
+      <c r="GL5" s="20" t="s">
         <v>484</v>
       </c>
-      <c r="GM5" s="43" t="s">
+      <c r="GM5" s="20" t="s">
         <v>485</v>
       </c>
-      <c r="GN5" s="43" t="s">
+      <c r="GN5" s="20" t="s">
         <v>486</v>
       </c>
-      <c r="GO5" s="43" t="s">
+      <c r="GO5" s="20" t="s">
         <v>487</v>
       </c>
-      <c r="GP5" s="43" t="s">
+      <c r="GP5" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="GQ5" s="36" t="s">
+      <c r="GQ5" s="13" t="s">
         <v>489</v>
       </c>
-      <c r="GR5" s="36" t="s">
+      <c r="GR5" s="13" t="s">
         <v>490</v>
       </c>
-      <c r="GS5" s="36" t="s">
+      <c r="GS5" s="13" t="s">
         <v>491</v>
       </c>
-      <c r="GT5" s="36" t="s">
+      <c r="GT5" s="13" t="s">
         <v>492</v>
       </c>
-      <c r="GU5" s="36" t="s">
+      <c r="GU5" s="13" t="s">
         <v>493</v>
       </c>
-      <c r="GV5" s="36" t="s">
+      <c r="GV5" s="13" t="s">
         <v>494</v>
       </c>
-      <c r="GW5" s="36" t="s">
+      <c r="GW5" s="13" t="s">
         <v>495</v>
       </c>
-      <c r="GX5" s="43" t="s">
+      <c r="GX5" s="20" t="s">
         <v>496</v>
       </c>
-      <c r="GY5" s="36" t="s">
+      <c r="GY5" s="13" t="s">
         <v>497</v>
       </c>
-      <c r="GZ5" s="36" t="s">
+      <c r="GZ5" s="13" t="s">
         <v>498</v>
       </c>
-      <c r="HA5" s="36" t="s">
+      <c r="HA5" s="13" t="s">
         <v>499</v>
       </c>
-      <c r="HB5" s="36" t="s">
+      <c r="HB5" s="13" t="s">
         <v>500</v>
       </c>
-      <c r="HC5" s="45" t="s">
+      <c r="HC5" s="22" t="s">
         <v>501</v>
       </c>
-      <c r="HD5" s="45" t="s">
+      <c r="HD5" s="22" t="s">
         <v>502</v>
       </c>
-      <c r="HE5" s="36" t="s">
+      <c r="HE5" s="13" t="s">
         <v>503</v>
       </c>
-      <c r="HF5" s="43" t="s">
+      <c r="HF5" s="20" t="s">
         <v>504</v>
       </c>
-      <c r="HG5" s="36" t="s">
+      <c r="HG5" s="13" t="s">
         <v>505</v>
       </c>
-      <c r="HH5" s="43" t="s">
+      <c r="HH5" s="20" t="s">
         <v>506</v>
       </c>
-      <c r="HI5" s="36" t="s">
+      <c r="HI5" s="13" t="s">
         <v>507</v>
       </c>
-      <c r="HJ5" s="36" t="s">
+      <c r="HJ5" s="13" t="s">
         <v>508</v>
       </c>
-      <c r="HK5" s="36" t="s">
+      <c r="HK5" s="13" t="s">
         <v>509</v>
       </c>
-      <c r="HL5" s="43" t="s">
+      <c r="HL5" s="20" t="s">
         <v>510</v>
       </c>
-      <c r="HM5" s="36" t="s">
+      <c r="HM5" s="13" t="s">
         <v>511</v>
       </c>
-      <c r="HN5" s="36" t="s">
+      <c r="HN5" s="13" t="s">
         <v>512</v>
       </c>
-      <c r="HO5" s="36" t="s">
+      <c r="HO5" s="13" t="s">
         <v>513</v>
       </c>
-      <c r="HP5" s="36" t="s">
+      <c r="HP5" s="13" t="s">
         <v>514</v>
       </c>
-      <c r="HQ5" s="36" t="s">
+      <c r="HQ5" s="13" t="s">
         <v>515</v>
       </c>
-      <c r="HR5" s="36" t="s">
+      <c r="HR5" s="13" t="s">
         <v>516</v>
       </c>
-      <c r="HS5" s="43" t="s">
+      <c r="HS5" s="20" t="s">
         <v>517</v>
       </c>
-      <c r="HT5" s="43" t="s">
+      <c r="HT5" s="20" t="s">
         <v>518</v>
       </c>
-      <c r="HU5" s="43" t="s">
+      <c r="HU5" s="20" t="s">
         <v>519</v>
       </c>
-      <c r="HV5" s="43" t="s">
+      <c r="HV5" s="20" t="s">
         <v>520</v>
       </c>
-      <c r="HW5" s="43" t="s">
+      <c r="HW5" s="20" t="s">
         <v>521</v>
       </c>
-      <c r="HX5" s="43" t="s">
+      <c r="HX5" s="20" t="s">
         <v>522</v>
       </c>
-      <c r="HY5" s="36" t="s">
+      <c r="HY5" s="13" t="s">
         <v>523</v>
       </c>
-      <c r="HZ5" s="36" t="s">
+      <c r="HZ5" s="13" t="s">
         <v>524</v>
       </c>
-      <c r="IA5" s="43" t="s">
+      <c r="IA5" s="20" t="s">
         <v>525</v>
       </c>
-      <c r="IB5" s="36" t="s">
+      <c r="IB5" s="13" t="s">
         <v>526</v>
       </c>
-      <c r="IC5" s="36" t="s">
+      <c r="IC5" s="13" t="s">
         <v>527</v>
       </c>
-      <c r="ID5" s="36" t="s">
+      <c r="ID5" s="13" t="s">
         <v>528</v>
       </c>
-      <c r="IE5" s="36" t="s">
+      <c r="IE5" s="13" t="s">
         <v>529</v>
       </c>
-      <c r="IF5" s="36" t="s">
+      <c r="IF5" s="13" t="s">
         <v>530</v>
       </c>
-      <c r="IG5" s="36" t="s">
+      <c r="IG5" s="13" t="s">
         <v>531</v>
       </c>
-      <c r="IH5" s="36" t="s">
+      <c r="IH5" s="13" t="s">
         <v>532</v>
       </c>
-      <c r="II5" s="36" t="s">
+      <c r="II5" s="13" t="s">
         <v>533</v>
       </c>
-      <c r="IJ5" s="43" t="s">
+      <c r="IJ5" s="20" t="s">
         <v>383</v>
       </c>
-      <c r="IK5" s="43" t="s">
+      <c r="IK5" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="IL5" s="43" t="s">
+      <c r="IL5" s="20" t="s">
         <v>385</v>
       </c>
-      <c r="IM5" s="43" t="s">
+      <c r="IM5" s="20" t="s">
         <v>386</v>
       </c>
-      <c r="IN5" s="43" t="s">
+      <c r="IN5" s="20" t="s">
         <v>387</v>
       </c>
-      <c r="IO5" s="43" t="s">
+      <c r="IO5" s="20" t="s">
         <v>388</v>
       </c>
-      <c r="IP5" s="43" t="s">
+      <c r="IP5" s="20" t="s">
         <v>389</v>
       </c>
-      <c r="IQ5" s="43" t="s">
+      <c r="IQ5" s="20" t="s">
         <v>390</v>
       </c>
-      <c r="IR5" s="43" t="s">
+      <c r="IR5" s="20" t="s">
         <v>391</v>
       </c>
-      <c r="IS5" s="36" t="s">
+      <c r="IS5" s="13" t="s">
         <v>392</v>
       </c>
-      <c r="IT5" s="36" t="s">
+      <c r="IT5" s="13" t="s">
         <v>393</v>
       </c>
-      <c r="IU5" s="36" t="s">
+      <c r="IU5" s="13" t="s">
         <v>534</v>
       </c>
-      <c r="IV5" s="36" t="s">
+      <c r="IV5" s="13" t="s">
         <v>395</v>
       </c>
-      <c r="IW5" s="36" t="s">
+      <c r="IW5" s="13" t="s">
         <v>396</v>
       </c>
-      <c r="IX5" s="43" t="s">
+      <c r="IX5" s="20" t="s">
         <v>535</v>
       </c>
-      <c r="IY5" s="42" t="s">
+      <c r="IY5" s="19" t="s">
         <v>536</v>
       </c>
-      <c r="IZ5" s="42" t="s">
+      <c r="IZ5" s="19" t="s">
         <v>537</v>
       </c>
-      <c r="JA5" s="41" t="s">
+      <c r="JA5" s="18" t="s">
         <v>538</v>
       </c>
-      <c r="JB5" s="41" t="s">
+      <c r="JB5" s="18" t="s">
         <v>539</v>
       </c>
-      <c r="JC5" s="46" t="s">
+      <c r="JC5" s="23" t="s">
         <v>540</v>
       </c>
     </row>
     <row r="6" spans="1:263" ht="30" x14ac:dyDescent="0.2">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="35" t="s">
+      <c r="A6" s="26"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="26"/>
+      <c r="N6" s="26"/>
+      <c r="O6" s="26"/>
+      <c r="P6" s="12" t="s">
         <v>541</v>
       </c>
-      <c r="Q6" s="36" t="s">
+      <c r="Q6" s="13" t="s">
         <v>542</v>
       </c>
-      <c r="R6" s="36" t="s">
+      <c r="R6" s="13" t="s">
         <v>543</v>
       </c>
-      <c r="S6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="T6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="U6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="V6" s="36" t="s">
+      <c r="S6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="T6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="U6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="V6" s="13" t="s">
         <v>545</v>
       </c>
-      <c r="W6" s="36" t="s">
+      <c r="W6" s="13" t="s">
         <v>546</v>
       </c>
-      <c r="X6" s="36" t="s">
+      <c r="X6" s="13" t="s">
         <v>547</v>
       </c>
-      <c r="Y6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="Z6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="AA6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="AB6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="AC6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="AD6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="AE6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="AF6" s="40" t="s">
-        <v>544</v>
-      </c>
-      <c r="AG6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="AH6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="AI6" s="40" t="s">
-        <v>544</v>
-      </c>
-      <c r="AJ6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="AK6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="AL6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="AM6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="AN6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="AO6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="AP6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="AQ6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="AR6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="AS6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="AT6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="AU6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="AV6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="AW6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="AX6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="AY6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="AZ6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="BA6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="BB6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="BC6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="BD6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="BE6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="BF6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="BG6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="BH6" s="41" t="s">
+      <c r="Y6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="Z6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="AA6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="AB6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="AC6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="AD6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="AE6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="AF6" s="17" t="s">
+        <v>544</v>
+      </c>
+      <c r="AG6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="AH6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="AI6" s="17" t="s">
+        <v>544</v>
+      </c>
+      <c r="AJ6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="AK6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="AL6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="AM6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="AN6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="AO6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="AP6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="AQ6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="AR6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="AS6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="AT6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="AU6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="AV6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="AW6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="AX6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="AY6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="AZ6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="BA6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="BB6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="BC6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="BD6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="BE6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="BF6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="BG6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="BH6" s="18" t="s">
         <v>548</v>
       </c>
-      <c r="BI6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="BJ6" s="41" t="s">
+      <c r="BI6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="BJ6" s="18" t="s">
         <v>549</v>
       </c>
-      <c r="BK6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="BL6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="BM6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="BN6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="BO6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="BP6" s="42" t="s">
+      <c r="BK6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="BL6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="BM6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="BN6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="BO6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="BP6" s="19" t="s">
         <v>549</v>
       </c>
-      <c r="BQ6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="BR6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="BS6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="BT6" s="41" t="s">
+      <c r="BQ6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="BR6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="BS6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="BT6" s="18" t="s">
         <v>550</v>
       </c>
-      <c r="BU6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="BV6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="BW6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="BX6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="BY6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="BZ6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="CA6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="CB6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="CC6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="CD6" s="42" t="s">
+      <c r="BU6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="BV6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="BW6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="BX6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="BY6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="BZ6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="CA6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="CB6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="CC6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="CD6" s="19" t="s">
         <v>551</v>
       </c>
-      <c r="CE6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="CF6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="CG6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="CH6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="CI6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="CJ6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="CK6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="CL6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="CM6" s="41" t="s">
+      <c r="CE6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="CF6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="CG6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="CH6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="CI6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="CJ6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="CK6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="CL6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="CM6" s="18" t="s">
         <v>552</v>
       </c>
-      <c r="CN6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="CO6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="CP6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="CQ6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="CR6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="CS6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="CT6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="CU6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="CV6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="CW6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="CX6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="CY6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="CZ6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="DA6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="DB6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="DC6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="DD6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="DE6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="DF6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="DG6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="DH6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="DI6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="DJ6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="DK6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="DL6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="DM6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="DN6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="DO6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="DP6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="DQ6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="DR6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="DS6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="DT6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="DU6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="DV6" s="42" t="s">
-        <v>544</v>
-      </c>
-      <c r="DW6" s="41" t="s">
-        <v>544</v>
-      </c>
-      <c r="DX6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="DY6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="DZ6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="EA6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="EB6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="EC6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="ED6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="EE6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="EF6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="EG6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="EH6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="EI6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="EJ6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="EK6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="EL6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="EM6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="EN6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="EO6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="EP6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="EQ6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="ER6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="ES6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="ET6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="EU6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="EV6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="EW6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="EX6" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="EY6" s="38" t="s">
-        <v>544</v>
-      </c>
-      <c r="EZ6" s="42" t="s">
+      <c r="CN6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="CO6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="CP6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="CQ6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="CR6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="CS6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="CT6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="CU6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="CV6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="CW6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="CX6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="CY6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="CZ6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="DA6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="DB6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="DC6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="DD6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="DE6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="DF6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="DG6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="DH6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="DI6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="DJ6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="DK6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="DL6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="DM6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="DN6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="DO6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="DP6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="DQ6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="DR6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="DS6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="DT6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="DU6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="DV6" s="19" t="s">
+        <v>544</v>
+      </c>
+      <c r="DW6" s="18" t="s">
+        <v>544</v>
+      </c>
+      <c r="DX6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="DY6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="DZ6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="EA6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="EB6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="EC6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="ED6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="EE6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="EF6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="EG6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="EH6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="EI6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="EJ6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="EK6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="EL6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="EM6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="EN6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="EO6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="EP6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="EQ6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="ER6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="ES6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="ET6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="EU6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="EV6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="EW6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="EX6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="EY6" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="EZ6" s="19" t="s">
         <v>553</v>
       </c>
-      <c r="FA6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="FB6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="FC6" s="36" t="s">
+      <c r="FA6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="FB6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="FC6" s="13" t="s">
         <v>554</v>
       </c>
-      <c r="FD6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="FE6" s="36" t="s">
+      <c r="FD6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="FE6" s="13" t="s">
         <v>555</v>
       </c>
-      <c r="FF6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="FG6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="FH6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="FI6" s="43" t="s">
+      <c r="FF6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="FG6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="FH6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="FI6" s="20" t="s">
         <v>552</v>
       </c>
-      <c r="FJ6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="FK6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="FL6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="FM6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="FN6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="FO6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="FP6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="FQ6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="FR6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="FS6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="FT6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="FU6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="FV6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="FW6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="FX6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="FY6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="FZ6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="GA6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="GB6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="GC6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="GD6" s="43" t="s">
+      <c r="FJ6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="FK6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="FL6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="FM6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="FN6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="FO6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="FP6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="FQ6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="FR6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="FS6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="FT6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="FU6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="FV6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="FW6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="FX6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="FY6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="FZ6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="GA6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="GB6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="GC6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="GD6" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="GE6" s="36" t="s">
+      <c r="GE6" s="13" t="s">
         <v>557</v>
       </c>
-      <c r="GF6" s="43" t="s">
+      <c r="GF6" s="20" t="s">
         <v>558</v>
       </c>
-      <c r="GG6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="GH6" s="43"/>
-      <c r="GI6" s="36" t="s">
+      <c r="GG6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="GH6" s="20"/>
+      <c r="GI6" s="13" t="s">
         <v>559</v>
       </c>
-      <c r="GJ6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="GK6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="GL6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="GM6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="GN6" s="43" t="s">
+      <c r="GJ6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="GK6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="GL6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="GM6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="GN6" s="20" t="s">
         <v>560</v>
       </c>
-      <c r="GO6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="GP6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="GQ6" s="36" t="s">
+      <c r="GO6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="GP6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="GQ6" s="13" t="s">
         <v>561</v>
       </c>
-      <c r="GR6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="GS6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="GT6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="GU6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="GV6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="GW6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="GX6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="GY6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="GZ6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="HA6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="HB6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="HC6" s="45" t="s">
+      <c r="GR6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="GS6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="GT6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="GU6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="GV6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="GW6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="GX6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="GY6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="GZ6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="HA6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="HB6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="HC6" s="22" t="s">
         <v>562</v>
       </c>
-      <c r="HD6" s="45"/>
-      <c r="HE6" s="36" t="s">
+      <c r="HD6" s="22"/>
+      <c r="HE6" s="13" t="s">
         <v>563</v>
       </c>
-      <c r="HF6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="HG6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="HH6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="HI6" s="36" t="s">
+      <c r="HF6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="HG6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="HH6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="HI6" s="13" t="s">
         <v>564</v>
       </c>
-      <c r="HJ6" s="36" t="s">
+      <c r="HJ6" s="13" t="s">
         <v>565</v>
       </c>
-      <c r="HK6" s="36" t="s">
+      <c r="HK6" s="13" t="s">
         <v>566</v>
       </c>
-      <c r="HL6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="HM6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="HN6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="HO6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="HP6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="HQ6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="HR6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="HS6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="HT6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="HU6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="HV6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="HW6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="HX6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="HY6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="HZ6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="IA6" s="43" t="s">
+      <c r="HL6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="HM6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="HN6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="HO6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="HP6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="HQ6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="HR6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="HS6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="HT6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="HU6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="HV6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="HW6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="HX6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="HY6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="HZ6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="IA6" s="20" t="s">
         <v>567</v>
       </c>
-      <c r="IB6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="IC6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="ID6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="IE6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="IF6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="IG6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="IH6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="II6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="IJ6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="IK6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="IL6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="IM6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="IN6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="IO6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="IP6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="IQ6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="IR6" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="IS6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="IT6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="IU6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="IV6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="IW6" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="IX6" s="43" t="s">
+      <c r="IB6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="IC6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="ID6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="IE6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="IF6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="IG6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="IH6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="II6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="IJ6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="IK6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="IL6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="IM6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="IN6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="IO6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="IP6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="IQ6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="IR6" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="IS6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="IT6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="IU6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="IV6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="IW6" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="IX6" s="20" t="s">
         <v>568</v>
       </c>
-      <c r="IY6" s="42" t="s">
+      <c r="IY6" s="19" t="s">
         <v>569</v>
       </c>
-      <c r="IZ6" s="42" t="s">
+      <c r="IZ6" s="19" t="s">
         <v>570</v>
       </c>
-      <c r="JA6" s="41" t="s">
+      <c r="JA6" s="18" t="s">
         <v>571</v>
       </c>
-      <c r="JB6" s="41" t="s">
+      <c r="JB6" s="18" t="s">
         <v>572</v>
       </c>
-      <c r="JC6" s="46"/>
+      <c r="JC6" s="23"/>
     </row>
     <row r="7" spans="1:263" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="24"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="35" t="s">
+      <c r="A7" s="27"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="27"/>
+      <c r="P7" s="12" t="s">
         <v>573</v>
       </c>
-      <c r="Q7" s="36" t="s">
+      <c r="Q7" s="13" t="s">
         <v>574</v>
       </c>
-      <c r="R7" s="36" t="s">
+      <c r="R7" s="13" t="s">
         <v>574</v>
       </c>
-      <c r="S7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="T7" s="36" t="s">
+      <c r="S7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="T7" s="13" t="s">
         <v>574</v>
       </c>
-      <c r="U7" s="36" t="s">
+      <c r="U7" s="13" t="s">
         <v>574</v>
       </c>
-      <c r="V7" s="36" t="s">
+      <c r="V7" s="13" t="s">
         <v>574</v>
       </c>
-      <c r="W7" s="36" t="s">
+      <c r="W7" s="13" t="s">
         <v>574</v>
       </c>
-      <c r="X7" s="36" t="s">
+      <c r="X7" s="13" t="s">
         <v>574</v>
       </c>
-      <c r="Y7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="Z7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="AA7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="AB7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="AC7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="AD7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="AE7" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="AF7" s="47" t="s">
-        <v>575</v>
-      </c>
-      <c r="AG7" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="AH7" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="AI7" s="47" t="s">
-        <v>575</v>
-      </c>
-      <c r="AJ7" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="AK7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="AL7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="AM7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="AN7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="AO7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="AP7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="AQ7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="AR7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="AS7" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="AT7" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="AU7" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="AV7" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="AW7" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="AX7" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="AY7" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="AZ7" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="BA7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="BB7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="BC7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="BD7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="BE7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="BF7" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="BG7" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="BH7" s="41" t="s">
+      <c r="Y7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="Z7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="AA7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="AB7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="AC7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="AD7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="AE7" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="AF7" s="24" t="s">
+        <v>575</v>
+      </c>
+      <c r="AG7" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="AH7" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="AI7" s="24" t="s">
+        <v>575</v>
+      </c>
+      <c r="AJ7" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="AK7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="AL7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="AM7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="AN7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="AO7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="AP7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="AQ7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="AR7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="AS7" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="AT7" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="AU7" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="AV7" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="AW7" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="AX7" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="AY7" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="AZ7" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="BA7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="BB7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="BC7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="BD7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="BE7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="BF7" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="BG7" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="BH7" s="18" t="s">
         <v>576</v>
       </c>
-      <c r="BI7" s="41" t="s">
+      <c r="BI7" s="18" t="s">
         <v>576</v>
       </c>
-      <c r="BJ7" s="41" t="s">
+      <c r="BJ7" s="18" t="s">
         <v>576</v>
       </c>
-      <c r="BK7" s="41" t="s">
+      <c r="BK7" s="18" t="s">
         <v>576</v>
       </c>
-      <c r="BL7" s="41" t="s">
+      <c r="BL7" s="18" t="s">
         <v>576</v>
       </c>
-      <c r="BM7" s="42" t="s">
+      <c r="BM7" s="19" t="s">
         <v>576</v>
       </c>
-      <c r="BN7" s="42" t="s">
+      <c r="BN7" s="19" t="s">
         <v>576</v>
       </c>
-      <c r="BO7" s="42" t="s">
+      <c r="BO7" s="19" t="s">
         <v>576</v>
       </c>
-      <c r="BP7" s="42" t="s">
+      <c r="BP7" s="19" t="s">
         <v>576</v>
       </c>
-      <c r="BQ7" s="42" t="s">
+      <c r="BQ7" s="19" t="s">
         <v>576</v>
       </c>
-      <c r="BR7" s="41" t="s">
+      <c r="BR7" s="18" t="s">
         <v>577</v>
       </c>
-      <c r="BS7" s="41" t="s">
+      <c r="BS7" s="18" t="s">
         <v>577</v>
       </c>
-      <c r="BT7" s="41" t="s">
+      <c r="BT7" s="18" t="s">
         <v>577</v>
       </c>
-      <c r="BU7" s="41" t="s">
+      <c r="BU7" s="18" t="s">
         <v>577</v>
       </c>
-      <c r="BV7" s="41" t="s">
+      <c r="BV7" s="18" t="s">
         <v>577</v>
       </c>
-      <c r="BW7" s="41" t="s">
+      <c r="BW7" s="18" t="s">
         <v>577</v>
       </c>
-      <c r="BX7" s="41" t="s">
+      <c r="BX7" s="18" t="s">
         <v>577</v>
       </c>
-      <c r="BY7" s="41" t="s">
+      <c r="BY7" s="18" t="s">
         <v>577</v>
       </c>
-      <c r="BZ7" s="41" t="s">
+      <c r="BZ7" s="18" t="s">
         <v>577</v>
       </c>
-      <c r="CA7" s="42" t="s">
+      <c r="CA7" s="19" t="s">
         <v>577</v>
       </c>
-      <c r="CB7" s="42" t="s">
+      <c r="CB7" s="19" t="s">
         <v>577</v>
       </c>
-      <c r="CC7" s="42" t="s">
+      <c r="CC7" s="19" t="s">
         <v>577</v>
       </c>
-      <c r="CD7" s="42" t="s">
+      <c r="CD7" s="19" t="s">
         <v>577</v>
       </c>
-      <c r="CE7" s="42" t="s">
+      <c r="CE7" s="19" t="s">
         <v>577</v>
       </c>
-      <c r="CF7" s="42" t="s">
+      <c r="CF7" s="19" t="s">
         <v>577</v>
       </c>
-      <c r="CG7" s="41" t="s">
+      <c r="CG7" s="18" t="s">
         <v>577</v>
       </c>
-      <c r="CH7" s="41" t="s">
+      <c r="CH7" s="18" t="s">
         <v>577</v>
       </c>
-      <c r="CI7" s="41" t="s">
+      <c r="CI7" s="18" t="s">
         <v>577</v>
       </c>
-      <c r="CJ7" s="41" t="s">
+      <c r="CJ7" s="18" t="s">
         <v>577</v>
       </c>
-      <c r="CK7" s="41" t="s">
+      <c r="CK7" s="18" t="s">
         <v>577</v>
       </c>
-      <c r="CL7" s="42" t="s">
+      <c r="CL7" s="19" t="s">
         <v>577</v>
       </c>
-      <c r="CM7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="CN7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="CO7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="CP7" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="CQ7" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="CR7" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="CS7" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="CT7" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="CU7" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="CV7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="CW7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="CX7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="CY7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="CZ7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="DA7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="DB7" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="DC7" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="DD7" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="DE7" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="DF7" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="DG7" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="DH7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="DI7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="DJ7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="DK7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="DL7" s="42" t="s">
+      <c r="CM7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="CN7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="CO7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="CP7" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="CQ7" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="CR7" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="CS7" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="CT7" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="CU7" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="CV7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="CW7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="CX7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="CY7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="CZ7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="DA7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="DB7" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="DC7" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="DD7" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="DE7" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="DF7" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="DG7" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="DH7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="DI7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="DJ7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="DK7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="DL7" s="19" t="s">
         <v>577</v>
       </c>
-      <c r="DM7" s="41" t="s">
+      <c r="DM7" s="18" t="s">
         <v>577</v>
       </c>
-      <c r="DN7" s="41" t="s">
+      <c r="DN7" s="18" t="s">
         <v>577</v>
       </c>
-      <c r="DO7" s="41" t="s">
+      <c r="DO7" s="18" t="s">
         <v>577</v>
       </c>
-      <c r="DP7" s="41" t="s">
+      <c r="DP7" s="18" t="s">
         <v>577</v>
       </c>
-      <c r="DQ7" s="42" t="s">
+      <c r="DQ7" s="19" t="s">
         <v>577</v>
       </c>
-      <c r="DR7" s="42" t="s">
+      <c r="DR7" s="19" t="s">
         <v>577</v>
       </c>
-      <c r="DS7" s="42" t="s">
+      <c r="DS7" s="19" t="s">
         <v>577</v>
       </c>
-      <c r="DT7" s="41" t="s">
-        <v>575</v>
-      </c>
-      <c r="DU7" s="42" t="s">
+      <c r="DT7" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="DU7" s="19" t="s">
         <v>576</v>
       </c>
-      <c r="DV7" s="42" t="s">
+      <c r="DV7" s="19" t="s">
         <v>576</v>
       </c>
-      <c r="DW7" s="41" t="s">
+      <c r="DW7" s="18" t="s">
         <v>576</v>
       </c>
-      <c r="DX7" s="41" t="s">
+      <c r="DX7" s="18" t="s">
         <v>576</v>
       </c>
-      <c r="DY7" s="41" t="s">
+      <c r="DY7" s="18" t="s">
         <v>576</v>
       </c>
-      <c r="DZ7" s="42" t="s">
+      <c r="DZ7" s="19" t="s">
         <v>576</v>
       </c>
-      <c r="EA7" s="42" t="s">
+      <c r="EA7" s="19" t="s">
         <v>576</v>
       </c>
-      <c r="EB7" s="42" t="s">
+      <c r="EB7" s="19" t="s">
         <v>576</v>
       </c>
-      <c r="EC7" s="42" t="s">
+      <c r="EC7" s="19" t="s">
         <v>576</v>
       </c>
-      <c r="ED7" s="42" t="s">
+      <c r="ED7" s="19" t="s">
         <v>576</v>
       </c>
-      <c r="EE7" s="42" t="s">
+      <c r="EE7" s="19" t="s">
         <v>576</v>
       </c>
-      <c r="EF7" s="42" t="s">
+      <c r="EF7" s="19" t="s">
         <v>576</v>
       </c>
-      <c r="EG7" s="42" t="s">
+      <c r="EG7" s="19" t="s">
         <v>576</v>
       </c>
-      <c r="EH7" s="41" t="s">
+      <c r="EH7" s="18" t="s">
         <v>576</v>
       </c>
-      <c r="EI7" s="41" t="s">
+      <c r="EI7" s="18" t="s">
         <v>576</v>
       </c>
-      <c r="EJ7" s="41" t="s">
+      <c r="EJ7" s="18" t="s">
         <v>576</v>
       </c>
-      <c r="EK7" s="41" t="s">
+      <c r="EK7" s="18" t="s">
         <v>576</v>
       </c>
-      <c r="EL7" s="41" t="s">
+      <c r="EL7" s="18" t="s">
         <v>576</v>
       </c>
-      <c r="EM7" s="41" t="s">
+      <c r="EM7" s="18" t="s">
         <v>576</v>
       </c>
-      <c r="EN7" s="42" t="s">
+      <c r="EN7" s="19" t="s">
         <v>576</v>
       </c>
-      <c r="EO7" s="42" t="s">
+      <c r="EO7" s="19" t="s">
         <v>576</v>
       </c>
-      <c r="EP7" s="41" t="s">
+      <c r="EP7" s="18" t="s">
         <v>576</v>
       </c>
-      <c r="EQ7" s="42" t="s">
+      <c r="EQ7" s="19" t="s">
         <v>576</v>
       </c>
-      <c r="ER7" s="42" t="s">
+      <c r="ER7" s="19" t="s">
         <v>576</v>
       </c>
-      <c r="ES7" s="42" t="s">
+      <c r="ES7" s="19" t="s">
         <v>576</v>
       </c>
-      <c r="ET7" s="42" t="s">
+      <c r="ET7" s="19" t="s">
         <v>576</v>
       </c>
-      <c r="EU7" s="42" t="s">
+      <c r="EU7" s="19" t="s">
         <v>576</v>
       </c>
-      <c r="EV7" s="42" t="s">
+      <c r="EV7" s="19" t="s">
         <v>576</v>
       </c>
-      <c r="EW7" s="42" t="s">
+      <c r="EW7" s="19" t="s">
         <v>576</v>
       </c>
-      <c r="EX7" s="42" t="s">
+      <c r="EX7" s="19" t="s">
         <v>576</v>
       </c>
-      <c r="EY7" s="41" t="s">
+      <c r="EY7" s="18" t="s">
         <v>576</v>
       </c>
-      <c r="EZ7" s="42" t="s">
+      <c r="EZ7" s="19" t="s">
         <v>574</v>
       </c>
-      <c r="FA7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="FB7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="FC7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="FD7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="FE7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="FF7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="FG7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="FH7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="FI7" s="43" t="s">
-        <v>575</v>
-      </c>
-      <c r="FJ7" s="43" t="s">
-        <v>575</v>
-      </c>
-      <c r="FK7" s="43" t="s">
-        <v>575</v>
-      </c>
-      <c r="FL7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="FM7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="FN7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="FO7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="FP7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="FQ7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="FR7" s="43" t="s">
-        <v>575</v>
-      </c>
-      <c r="FS7" s="43" t="s">
-        <v>575</v>
-      </c>
-      <c r="FT7" s="43" t="s">
-        <v>575</v>
-      </c>
-      <c r="FU7" s="43" t="s">
-        <v>575</v>
-      </c>
-      <c r="FV7" s="43" t="s">
-        <v>575</v>
-      </c>
-      <c r="FW7" s="43" t="s">
-        <v>575</v>
-      </c>
-      <c r="FX7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="FY7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="FZ7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="GA7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="GB7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="GC7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="GD7" s="43" t="s">
+      <c r="FA7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="FB7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="FC7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="FD7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="FE7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="FF7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="FG7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="FH7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="FI7" s="20" t="s">
+        <v>575</v>
+      </c>
+      <c r="FJ7" s="20" t="s">
+        <v>575</v>
+      </c>
+      <c r="FK7" s="20" t="s">
+        <v>575</v>
+      </c>
+      <c r="FL7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="FM7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="FN7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="FO7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="FP7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="FQ7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="FR7" s="20" t="s">
+        <v>575</v>
+      </c>
+      <c r="FS7" s="20" t="s">
+        <v>575</v>
+      </c>
+      <c r="FT7" s="20" t="s">
+        <v>575</v>
+      </c>
+      <c r="FU7" s="20" t="s">
+        <v>575</v>
+      </c>
+      <c r="FV7" s="20" t="s">
+        <v>575</v>
+      </c>
+      <c r="FW7" s="20" t="s">
+        <v>575</v>
+      </c>
+      <c r="FX7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="FY7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="FZ7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="GA7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="GB7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="GC7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="GD7" s="20" t="s">
         <v>574</v>
       </c>
-      <c r="GE7" s="36" t="s">
+      <c r="GE7" s="13" t="s">
         <v>574</v>
       </c>
-      <c r="GF7" s="43" t="s">
+      <c r="GF7" s="20" t="s">
         <v>576</v>
       </c>
-      <c r="GG7" s="43" t="s">
+      <c r="GG7" s="20" t="s">
         <v>576</v>
       </c>
-      <c r="GH7" s="43"/>
-      <c r="GI7" s="36" t="s">
+      <c r="GH7" s="20"/>
+      <c r="GI7" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="GJ7" s="36" t="s">
+      <c r="GJ7" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="GK7" s="43" t="s">
+      <c r="GK7" s="20" t="s">
         <v>574</v>
       </c>
-      <c r="GL7" s="43" t="s">
+      <c r="GL7" s="20" t="s">
         <v>574</v>
       </c>
-      <c r="GM7" s="43" t="s">
+      <c r="GM7" s="20" t="s">
         <v>574</v>
       </c>
-      <c r="GN7" s="43" t="s">
-        <v>575</v>
-      </c>
-      <c r="GO7" s="43" t="s">
-        <v>575</v>
-      </c>
-      <c r="GP7" s="43" t="s">
-        <v>575</v>
-      </c>
-      <c r="GQ7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="GR7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="GS7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="GT7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="GU7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="GV7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="GW7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="GX7" s="43" t="s">
+      <c r="GN7" s="20" t="s">
+        <v>575</v>
+      </c>
+      <c r="GO7" s="20" t="s">
+        <v>575</v>
+      </c>
+      <c r="GP7" s="20" t="s">
+        <v>575</v>
+      </c>
+      <c r="GQ7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="GR7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="GS7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="GT7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="GU7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="GV7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="GW7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="GX7" s="20" t="s">
         <v>576</v>
       </c>
-      <c r="GY7" s="36" t="s">
+      <c r="GY7" s="13" t="s">
         <v>577</v>
       </c>
-      <c r="GZ7" s="36" t="s">
+      <c r="GZ7" s="13" t="s">
         <v>577</v>
       </c>
-      <c r="HA7" s="36" t="s">
+      <c r="HA7" s="13" t="s">
         <v>577</v>
       </c>
-      <c r="HB7" s="36" t="s">
+      <c r="HB7" s="13" t="s">
         <v>577</v>
       </c>
-      <c r="HC7" s="45" t="s">
-        <v>575</v>
-      </c>
-      <c r="HD7" s="45"/>
-      <c r="HE7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="HF7" s="43" t="s">
-        <v>575</v>
-      </c>
-      <c r="HG7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="HH7" s="43" t="s">
-        <v>575</v>
-      </c>
-      <c r="HI7" s="36" t="s">
-        <v>575</v>
-      </c>
-      <c r="HJ7" s="36" t="s">
+      <c r="HC7" s="22" t="s">
+        <v>575</v>
+      </c>
+      <c r="HD7" s="22"/>
+      <c r="HE7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="HF7" s="20" t="s">
+        <v>575</v>
+      </c>
+      <c r="HG7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="HH7" s="20" t="s">
+        <v>575</v>
+      </c>
+      <c r="HI7" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="HJ7" s="13" t="s">
         <v>578</v>
       </c>
-      <c r="HK7" s="36" t="s">
+      <c r="HK7" s="13" t="s">
         <v>578</v>
       </c>
-      <c r="HL7" s="43" t="s">
+      <c r="HL7" s="20" t="s">
         <v>579</v>
       </c>
-      <c r="HM7" s="36" t="s">
+      <c r="HM7" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="HN7" s="36" t="s">
+      <c r="HN7" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="HO7" s="36" t="s">
+      <c r="HO7" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="HP7" s="36" t="s">
+      <c r="HP7" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="HQ7" s="36" t="s">
+      <c r="HQ7" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="HR7" s="36" t="s">
+      <c r="HR7" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="HS7" s="43" t="s">
+      <c r="HS7" s="20" t="s">
         <v>576</v>
       </c>
-      <c r="HT7" s="43" t="s">
+      <c r="HT7" s="20" t="s">
         <v>576</v>
       </c>
-      <c r="HU7" s="43" t="s">
+      <c r="HU7" s="20" t="s">
         <v>576</v>
       </c>
-      <c r="HV7" s="43" t="s">
+      <c r="HV7" s="20" t="s">
         <v>576</v>
       </c>
-      <c r="HW7" s="43" t="s">
+      <c r="HW7" s="20" t="s">
         <v>576</v>
       </c>
-      <c r="HX7" s="43" t="s">
+      <c r="HX7" s="20" t="s">
         <v>576</v>
       </c>
-      <c r="HY7" s="36" t="s">
+      <c r="HY7" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="HZ7" s="36" t="s">
+      <c r="HZ7" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="IA7" s="43" t="s">
+      <c r="IA7" s="20" t="s">
         <v>576</v>
       </c>
-      <c r="IB7" s="36" t="s">
+      <c r="IB7" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="IC7" s="36" t="s">
+      <c r="IC7" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="ID7" s="36" t="s">
+      <c r="ID7" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="IE7" s="36" t="s">
+      <c r="IE7" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="IF7" s="36" t="s">
+      <c r="IF7" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="IG7" s="36" t="s">
+      <c r="IG7" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="IH7" s="36" t="s">
+      <c r="IH7" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="II7" s="36" t="s">
+      <c r="II7" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="IJ7" s="43" t="s">
+      <c r="IJ7" s="20" t="s">
         <v>577</v>
       </c>
-      <c r="IK7" s="43" t="s">
+      <c r="IK7" s="20" t="s">
         <v>577</v>
       </c>
-      <c r="IL7" s="43" t="s">
+      <c r="IL7" s="20" t="s">
         <v>577</v>
       </c>
-      <c r="IM7" s="43" t="s">
+      <c r="IM7" s="20" t="s">
         <v>577</v>
       </c>
-      <c r="IN7" s="43" t="s">
+      <c r="IN7" s="20" t="s">
         <v>577</v>
       </c>
-      <c r="IO7" s="43" t="s">
+      <c r="IO7" s="20" t="s">
         <v>577</v>
       </c>
-      <c r="IP7" s="43" t="s">
+      <c r="IP7" s="20" t="s">
         <v>577</v>
       </c>
-      <c r="IQ7" s="43" t="s">
+      <c r="IQ7" s="20" t="s">
         <v>577</v>
       </c>
-      <c r="IR7" s="43" t="s">
+      <c r="IR7" s="20" t="s">
         <v>577</v>
       </c>
-      <c r="IS7" s="36" t="s">
+      <c r="IS7" s="13" t="s">
         <v>577</v>
       </c>
-      <c r="IT7" s="36" t="s">
+      <c r="IT7" s="13" t="s">
         <v>577</v>
       </c>
-      <c r="IU7" s="36" t="s">
+      <c r="IU7" s="13" t="s">
         <v>577</v>
       </c>
-      <c r="IV7" s="36" t="s">
+      <c r="IV7" s="13" t="s">
         <v>577</v>
       </c>
-      <c r="IW7" s="36" t="s">
+      <c r="IW7" s="13" t="s">
         <v>577</v>
       </c>
-      <c r="IX7" s="43" t="s">
+      <c r="IX7" s="20" t="s">
         <v>574</v>
       </c>
-      <c r="IY7" s="42" t="s">
+      <c r="IY7" s="19" t="s">
         <v>580</v>
       </c>
-      <c r="IZ7" s="42" t="s">
+      <c r="IZ7" s="19" t="s">
         <v>580</v>
       </c>
-      <c r="JA7" s="41" t="s">
+      <c r="JA7" s="18" t="s">
         <v>574</v>
       </c>
-      <c r="JB7" s="41" t="s">
+      <c r="JB7" s="18" t="s">
         <v>574</v>
       </c>
-      <c r="JC7" s="34" t="s">
+      <c r="JC7" s="11" t="s">
         <v>575</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="82">
-    <mergeCell ref="L1:L7"/>
-    <mergeCell ref="A1:A7"/>
-    <mergeCell ref="B1:B7"/>
-    <mergeCell ref="C1:C7"/>
-    <mergeCell ref="D1:D7"/>
-    <mergeCell ref="E1:E7"/>
-    <mergeCell ref="F1:F7"/>
-    <mergeCell ref="G1:G7"/>
-    <mergeCell ref="H1:H7"/>
-    <mergeCell ref="I1:I7"/>
-    <mergeCell ref="J1:J7"/>
-    <mergeCell ref="K1:K7"/>
-    <mergeCell ref="M1:M7"/>
-    <mergeCell ref="N1:N7"/>
-    <mergeCell ref="O1:O7"/>
-    <mergeCell ref="P1:P4"/>
-    <mergeCell ref="Q1:X1"/>
+    <mergeCell ref="IB3:II3"/>
+    <mergeCell ref="IJ3:IR3"/>
+    <mergeCell ref="IS3:IW3"/>
+    <mergeCell ref="EH3:EM3"/>
+    <mergeCell ref="EN3:EO3"/>
+    <mergeCell ref="EQ3:EX3"/>
+    <mergeCell ref="FI3:FK3"/>
+    <mergeCell ref="FL3:FQ3"/>
+    <mergeCell ref="FR3:FW3"/>
+    <mergeCell ref="HC3:HD3"/>
+    <mergeCell ref="HM3:HR3"/>
+    <mergeCell ref="HS3:HX3"/>
+    <mergeCell ref="HY3:HZ3"/>
+    <mergeCell ref="FA2:FH3"/>
+    <mergeCell ref="FI2:GC2"/>
+    <mergeCell ref="GD2:GJ2"/>
+    <mergeCell ref="DZ3:EG3"/>
+    <mergeCell ref="BM3:BQ3"/>
+    <mergeCell ref="BR3:BZ3"/>
+    <mergeCell ref="CA3:CF3"/>
+    <mergeCell ref="CG3:CK3"/>
+    <mergeCell ref="CM3:CO3"/>
+    <mergeCell ref="CP3:CU3"/>
+    <mergeCell ref="CV3:DA3"/>
+    <mergeCell ref="DB3:DG3"/>
+    <mergeCell ref="DH3:DK3"/>
+    <mergeCell ref="DM3:DP3"/>
+    <mergeCell ref="DQ3:DS3"/>
+    <mergeCell ref="IX2:IX3"/>
+    <mergeCell ref="IY2:IZ3"/>
+    <mergeCell ref="JA2:JB3"/>
+    <mergeCell ref="Y3:AD3"/>
+    <mergeCell ref="AE3:AJ3"/>
+    <mergeCell ref="AK3:AR3"/>
+    <mergeCell ref="AS3:AZ3"/>
+    <mergeCell ref="BA3:BE3"/>
+    <mergeCell ref="BF3:BG3"/>
+    <mergeCell ref="BH3:BL3"/>
+    <mergeCell ref="GY2:HB3"/>
+    <mergeCell ref="HC2:HI2"/>
+    <mergeCell ref="HJ2:HK3"/>
+    <mergeCell ref="HL2:HL3"/>
+    <mergeCell ref="HM2:II2"/>
+    <mergeCell ref="IJ2:IW2"/>
+    <mergeCell ref="GQ2:GW3"/>
+    <mergeCell ref="GX2:GX3"/>
+    <mergeCell ref="FX3:GC3"/>
+    <mergeCell ref="GF3:GG3"/>
+    <mergeCell ref="GI3:GJ3"/>
     <mergeCell ref="FA1:IX1"/>
     <mergeCell ref="IY1:JB1"/>
     <mergeCell ref="JC1:JC3"/>
@@ -6689,58 +6884,159 @@
     <mergeCell ref="EY2:EY3"/>
     <mergeCell ref="EZ2:EZ3"/>
     <mergeCell ref="GK2:GP3"/>
-    <mergeCell ref="GQ2:GW3"/>
-    <mergeCell ref="GX2:GX3"/>
-    <mergeCell ref="FX3:GC3"/>
-    <mergeCell ref="GF3:GG3"/>
-    <mergeCell ref="GI3:GJ3"/>
-    <mergeCell ref="IX2:IX3"/>
-    <mergeCell ref="IY2:IZ3"/>
-    <mergeCell ref="JA2:JB3"/>
-    <mergeCell ref="Y3:AD3"/>
-    <mergeCell ref="AE3:AJ3"/>
-    <mergeCell ref="AK3:AR3"/>
-    <mergeCell ref="AS3:AZ3"/>
-    <mergeCell ref="BA3:BE3"/>
-    <mergeCell ref="BF3:BG3"/>
-    <mergeCell ref="BH3:BL3"/>
-    <mergeCell ref="GY2:HB3"/>
-    <mergeCell ref="HC2:HI2"/>
-    <mergeCell ref="HJ2:HK3"/>
-    <mergeCell ref="HL2:HL3"/>
-    <mergeCell ref="HM2:II2"/>
-    <mergeCell ref="IJ2:IW2"/>
-    <mergeCell ref="DZ3:EG3"/>
-    <mergeCell ref="BM3:BQ3"/>
-    <mergeCell ref="BR3:BZ3"/>
-    <mergeCell ref="CA3:CF3"/>
-    <mergeCell ref="CG3:CK3"/>
-    <mergeCell ref="CM3:CO3"/>
-    <mergeCell ref="CP3:CU3"/>
-    <mergeCell ref="CV3:DA3"/>
-    <mergeCell ref="DB3:DG3"/>
-    <mergeCell ref="DH3:DK3"/>
-    <mergeCell ref="DM3:DP3"/>
-    <mergeCell ref="DQ3:DS3"/>
-    <mergeCell ref="IB3:II3"/>
-    <mergeCell ref="IJ3:IR3"/>
-    <mergeCell ref="IS3:IW3"/>
-    <mergeCell ref="EH3:EM3"/>
-    <mergeCell ref="EN3:EO3"/>
-    <mergeCell ref="EQ3:EX3"/>
-    <mergeCell ref="FI3:FK3"/>
-    <mergeCell ref="FL3:FQ3"/>
-    <mergeCell ref="FR3:FW3"/>
-    <mergeCell ref="HC3:HD3"/>
-    <mergeCell ref="HM3:HR3"/>
-    <mergeCell ref="HS3:HX3"/>
-    <mergeCell ref="HY3:HZ3"/>
-    <mergeCell ref="FA2:FH3"/>
-    <mergeCell ref="FI2:GC2"/>
-    <mergeCell ref="GD2:GJ2"/>
+    <mergeCell ref="M1:M7"/>
+    <mergeCell ref="N1:N7"/>
+    <mergeCell ref="O1:O7"/>
+    <mergeCell ref="P1:P4"/>
+    <mergeCell ref="Q1:X1"/>
+    <mergeCell ref="L1:L7"/>
+    <mergeCell ref="A1:A7"/>
+    <mergeCell ref="B1:B7"/>
+    <mergeCell ref="C1:C7"/>
+    <mergeCell ref="D1:D7"/>
+    <mergeCell ref="E1:E7"/>
+    <mergeCell ref="F1:F7"/>
+    <mergeCell ref="G1:G7"/>
+    <mergeCell ref="H1:H7"/>
+    <mergeCell ref="I1:I7"/>
+    <mergeCell ref="J1:J7"/>
+    <mergeCell ref="K1:K7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5902BFF-1298-4FA3-8DB5-A80B8D650BBE}">
+  <dimension ref="A1:U2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" style="68" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="68" customWidth="1"/>
+    <col min="4" max="10" width="14.42578125" style="68" customWidth="1"/>
+    <col min="11" max="11" width="25.140625" style="68" customWidth="1"/>
+    <col min="12" max="12" width="23.140625" style="68" customWidth="1"/>
+    <col min="13" max="13" width="21.28515625" style="68" customWidth="1"/>
+    <col min="14" max="21" width="14.42578125" style="68" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" ht="74.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="62" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="62" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="62" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="62" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="62" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="63" t="s">
+        <v>590</v>
+      </c>
+      <c r="K1" s="63" t="s">
+        <v>591</v>
+      </c>
+      <c r="L1" s="63" t="s">
+        <v>592</v>
+      </c>
+      <c r="M1" s="63" t="s">
+        <v>593</v>
+      </c>
+      <c r="N1" s="63" t="s">
+        <v>586</v>
+      </c>
+      <c r="O1" s="63" t="s">
+        <v>594</v>
+      </c>
+      <c r="P1" s="63" t="s">
+        <v>595</v>
+      </c>
+      <c r="Q1" s="63" t="s">
+        <v>596</v>
+      </c>
+      <c r="R1" s="63" t="s">
+        <v>597</v>
+      </c>
+      <c r="S1" s="63" t="s">
+        <v>587</v>
+      </c>
+      <c r="T1" s="64" t="s">
+        <v>13</v>
+      </c>
+      <c r="U1" s="64" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="65"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="66" t="s">
+        <v>588</v>
+      </c>
+      <c r="K2" s="66" t="s">
+        <v>588</v>
+      </c>
+      <c r="L2" s="66" t="s">
+        <v>588</v>
+      </c>
+      <c r="M2" s="66" t="s">
+        <v>588</v>
+      </c>
+      <c r="N2" s="66" t="s">
+        <v>588</v>
+      </c>
+      <c r="O2" s="66" t="s">
+        <v>589</v>
+      </c>
+      <c r="P2" s="66" t="s">
+        <v>589</v>
+      </c>
+      <c r="Q2" s="66" t="s">
+        <v>588</v>
+      </c>
+      <c r="R2" s="66" t="s">
+        <v>588</v>
+      </c>
+      <c r="S2" s="66" t="s">
+        <v>588</v>
+      </c>
+      <c r="T2" s="67" t="s">
+        <v>588</v>
+      </c>
+      <c r="U2" s="67" t="s">
+        <v>588</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/data/template/boq/Template_BOQ_Report.xlsx
+++ b/data/template/boq/Template_BOQ_Report.xlsx
@@ -8,19 +8,52 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JACOBS\SERVICE\API\data\template\boq\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31FCA24C-C9E5-4ECB-9D4B-FE9D88C8A551}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{800378D2-EC78-4DAA-94B4-125AF13F9035}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="BOQ PR" sheetId="5" r:id="rId1"/>
+    <sheet name="BOQ" sheetId="6" r:id="rId1"/>
+    <sheet name="BOQ PR" sheetId="5" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>None</author>
+  </authors>
+  <commentList>
+    <comment ref="JC5" authorId="0" shapeId="0" xr:uid="{063E7CA6-4506-4C42-9844-538D450504AE}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
+ID#AAAByJ2Q9vc
+which contains     (2025-12-29 04:54:26)
+D.3.1 Scan Document ATP (refer to ATP File)
+D.3.2 As Plan Drawing and As Build Drawing *.dwg (format Autocad R-2014)
+D.3.3 FO Route Cable *.kml (Google Earth)
+D.3.4 OTDR Result (Original File)
+D.3.5 Installation Documentation
+D.3.6 Permit</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="601">
   <si>
     <t>No</t>
   </si>
@@ -166,12 +199,1746 @@
   <si>
     <t>Pole Exist</t>
   </si>
+  <si>
+    <t>C. Service Installation</t>
+  </si>
+  <si>
+    <t>D. Test and Documentation</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>C.1 Trenching &amp; Reinstatement</t>
+  </si>
+  <si>
+    <t>C.2 Installation Pipe</t>
+  </si>
+  <si>
+    <t>C.3 Pole Installation</t>
+  </si>
+  <si>
+    <t>C.4 Bridge Crossing (*)</t>
+  </si>
+  <si>
+    <t>C.5 Crossing and Boring</t>
+  </si>
+  <si>
+    <t>C.6 Marking Post</t>
+  </si>
+  <si>
+    <t>C.7 Manhole/Handhole</t>
+  </si>
+  <si>
+    <t>C.8 Pulling Fiber Optic</t>
+  </si>
+  <si>
+    <t>C.9 Splicing/Termination</t>
+  </si>
+  <si>
+    <t>C.10 Bobok Tembok</t>
+  </si>
+  <si>
+    <t>C.11 Installation Patchcord Fiber Optic</t>
+  </si>
+  <si>
+    <t>C.12 Installation Termination Point</t>
+  </si>
+  <si>
+    <t>C.13 Support Integration</t>
+  </si>
+  <si>
+    <t>D.1 Testing</t>
+  </si>
+  <si>
+    <t>D.2 Documentation</t>
+  </si>
+  <si>
+    <t>C.2.1 Installation HDPE Pipe (Subduct)</t>
+  </si>
+  <si>
+    <t>C.2.2 Installation HDPE Pipe (Micro Duct)</t>
+  </si>
+  <si>
+    <t>C.2.3 Installation Galvanized Pipe</t>
+  </si>
+  <si>
+    <t>C.2.4 PVC Pipe</t>
+  </si>
+  <si>
+    <t>C.3.1 Pole 7</t>
+  </si>
+  <si>
+    <t>C.3.2 Pole 9</t>
+  </si>
+  <si>
+    <t>C.3.3 Slack Support Installation</t>
+  </si>
+  <si>
+    <t>C.3.4 Riser Pipe Installation</t>
+  </si>
+  <si>
+    <t>C.8.1 Pulling Fiber Optic Cable Aerial</t>
+  </si>
+  <si>
+    <t>C.11.1 Installation Patchcord Fiber Optic Single Mode Indoor</t>
+  </si>
+  <si>
+    <t>C.11.2 Installation Patchcord Fiber Optic Single Mode Outdoor Duplex</t>
+  </si>
+  <si>
+    <t>C.11.3 Installation Patchcord Fiber Optic Multi Mode Indoor Duplex</t>
+  </si>
+  <si>
+    <t>C.11.4 Installation Pigtail</t>
+  </si>
+  <si>
+    <t>C.11.5 Installation Adapter</t>
+  </si>
+  <si>
+    <t>C.12.1 Installation Optical Termination Box (OTB)</t>
+  </si>
+  <si>
+    <t>C.12 Installation Optical Distribution Point (ODP)</t>
+  </si>
+  <si>
+    <t>C.1.1</t>
+  </si>
+  <si>
+    <t>C.1.2</t>
+  </si>
+  <si>
+    <t>C.1.3</t>
+  </si>
+  <si>
+    <t>C.1.4</t>
+  </si>
+  <si>
+    <t>C.1.5</t>
+  </si>
+  <si>
+    <t>C.1.6</t>
+  </si>
+  <si>
+    <t>C.1.7</t>
+  </si>
+  <si>
+    <t>C.1.8</t>
+  </si>
+  <si>
+    <t>C.2.1.1</t>
+  </si>
+  <si>
+    <t>C.2.1.2</t>
+  </si>
+  <si>
+    <t>C.2.1.3</t>
+  </si>
+  <si>
+    <t>C.2.2.1</t>
+  </si>
+  <si>
+    <t>C.2.2.2</t>
+  </si>
+  <si>
+    <t>C.2.2.3</t>
+  </si>
+  <si>
+    <t>C.2.2.4</t>
+  </si>
+  <si>
+    <t>C.2.2.5</t>
+  </si>
+  <si>
+    <t>C.2.2.6</t>
+  </si>
+  <si>
+    <t>C.2.3.1</t>
+  </si>
+  <si>
+    <t>C.2.3.2</t>
+  </si>
+  <si>
+    <t>C.2.3.3</t>
+  </si>
+  <si>
+    <t>C.2.3.4</t>
+  </si>
+  <si>
+    <t>C.2.3.5</t>
+  </si>
+  <si>
+    <t>C.2.3.6</t>
+  </si>
+  <si>
+    <t>C.2.4.1</t>
+  </si>
+  <si>
+    <t>C.2.4.2</t>
+  </si>
+  <si>
+    <t>C.2.4.3</t>
+  </si>
+  <si>
+    <t>C.2.4.4</t>
+  </si>
+  <si>
+    <t>C.2.4.5</t>
+  </si>
+  <si>
+    <t>C.2.4.6</t>
+  </si>
+  <si>
+    <t>C.3.1</t>
+  </si>
+  <si>
+    <t>C.3.2</t>
+  </si>
+  <si>
+    <t>C.3.3.1</t>
+  </si>
+  <si>
+    <t>C.3.3.2</t>
+  </si>
+  <si>
+    <t>C.3.3.3</t>
+  </si>
+  <si>
+    <t>C.3.4.1</t>
+  </si>
+  <si>
+    <t>C.3.4.2</t>
+  </si>
+  <si>
+    <t>C.4.1</t>
+  </si>
+  <si>
+    <t>C.4.2</t>
+  </si>
+  <si>
+    <t>C.4.3</t>
+  </si>
+  <si>
+    <t>C.4.4</t>
+  </si>
+  <si>
+    <t>C.4.5</t>
+  </si>
+  <si>
+    <t>C.4.6</t>
+  </si>
+  <si>
+    <t>C.5.1</t>
+  </si>
+  <si>
+    <t>C.5.2</t>
+  </si>
+  <si>
+    <t>C.5.3</t>
+  </si>
+  <si>
+    <t>C.5.4</t>
+  </si>
+  <si>
+    <t>C.5.5</t>
+  </si>
+  <si>
+    <t>C.5.6</t>
+  </si>
+  <si>
+    <t>C.5.7</t>
+  </si>
+  <si>
+    <t>C.6.1</t>
+  </si>
+  <si>
+    <t>C.7.1</t>
+  </si>
+  <si>
+    <t>C.7.2</t>
+  </si>
+  <si>
+    <t>C.7.3</t>
+  </si>
+  <si>
+    <t>C.7.4</t>
+  </si>
+  <si>
+    <t>C.8.1.1</t>
+  </si>
+  <si>
+    <t>C.8.1.2</t>
+  </si>
+  <si>
+    <t>C.8.2</t>
+  </si>
+  <si>
+    <t>C.8.3</t>
+  </si>
+  <si>
+    <t>C.8.4</t>
+  </si>
+  <si>
+    <t>C.8.5</t>
+  </si>
+  <si>
+    <t>C.8.6</t>
+  </si>
+  <si>
+    <t>C.9.1</t>
+  </si>
+  <si>
+    <t>C.9.2</t>
+  </si>
+  <si>
+    <t>C.10.1</t>
+  </si>
+  <si>
+    <t>C.11.1.1</t>
+  </si>
+  <si>
+    <t>C.11.1.2</t>
+  </si>
+  <si>
+    <t>C.11.1.3</t>
+  </si>
+  <si>
+    <t>C.11.1.4</t>
+  </si>
+  <si>
+    <t>C.11.1.5</t>
+  </si>
+  <si>
+    <t>C.11.1.6</t>
+  </si>
+  <si>
+    <t>C.11.2.1</t>
+  </si>
+  <si>
+    <t>C.11.2.2</t>
+  </si>
+  <si>
+    <t>C.11.2.3</t>
+  </si>
+  <si>
+    <t>C.11.2.4</t>
+  </si>
+  <si>
+    <t>C.11.2.5</t>
+  </si>
+  <si>
+    <t>C.11.2.6</t>
+  </si>
+  <si>
+    <t>C.11.3.1</t>
+  </si>
+  <si>
+    <t>C.11.3.2</t>
+  </si>
+  <si>
+    <t>C.11.4.1</t>
+  </si>
+  <si>
+    <t>C.11.5.1</t>
+  </si>
+  <si>
+    <t>C.11.5.2</t>
+  </si>
+  <si>
+    <t>C.11.5.3</t>
+  </si>
+  <si>
+    <t>C.11.5.4</t>
+  </si>
+  <si>
+    <t>C.11.5.5</t>
+  </si>
+  <si>
+    <t>C.11.5.6</t>
+  </si>
+  <si>
+    <t>C.11.5.7</t>
+  </si>
+  <si>
+    <t>C.11.5.8</t>
+  </si>
+  <si>
+    <t>C.12.1.1</t>
+  </si>
+  <si>
+    <t>C.12.1.2</t>
+  </si>
+  <si>
+    <t>C.12.1.3</t>
+  </si>
+  <si>
+    <t>C.12.1.4</t>
+  </si>
+  <si>
+    <t>C.12.1.5</t>
+  </si>
+  <si>
+    <t>C.12.1.6</t>
+  </si>
+  <si>
+    <t>C.12.1.7</t>
+  </si>
+  <si>
+    <t>C.12.1.8</t>
+  </si>
+  <si>
+    <t>C.12.1.9</t>
+  </si>
+  <si>
+    <t>C.12.2.1</t>
+  </si>
+  <si>
+    <t>C.12.2.2</t>
+  </si>
+  <si>
+    <t>C.12.2.3</t>
+  </si>
+  <si>
+    <t>C.12.2.4</t>
+  </si>
+  <si>
+    <t>C.12.2.5</t>
+  </si>
+  <si>
+    <t>C.13.1</t>
+  </si>
+  <si>
+    <t>D.1.1</t>
+  </si>
+  <si>
+    <t>D.1.2</t>
+  </si>
+  <si>
+    <t>D.2.1</t>
+  </si>
+  <si>
+    <t>D.2.2</t>
+  </si>
+  <si>
+    <t>Trenching &amp; Reinstatement Hotmix</t>
+  </si>
+  <si>
+    <t>Trenching &amp; Reinstatement Asphalt</t>
+  </si>
+  <si>
+    <t>Trenching &amp; Reinstatement Makadam</t>
+  </si>
+  <si>
+    <t>Trenching &amp; Reinstatement Floor/Cement</t>
+  </si>
+  <si>
+    <t>Trenching &amp; Reinstatement Paving</t>
+  </si>
+  <si>
+    <t>Trenching &amp; Reinstatement Agregat /sirtu</t>
+  </si>
+  <si>
+    <t>Trenching &amp; Reinstatement Taman</t>
+  </si>
+  <si>
+    <t>Trenching &amp; Reinstatement Tanah Biasa</t>
+  </si>
+  <si>
+    <t>HDPE Pipe (Subduct) 32/27 Biru Muda strip Biru Tua</t>
+  </si>
+  <si>
+    <t>HDPE Pipe (Subduct) 40/33 Biru Muda strip Biru Tua</t>
+  </si>
+  <si>
+    <t>HDPE Pipe (Subduct) 50/43 Biru Muda strip Biru Tua</t>
+  </si>
+  <si>
+    <t>HDPE Pipe (Micro Duct) 4 Way 12/10 Biru Muda strip Biru Tua</t>
+  </si>
+  <si>
+    <t>HDPE Pipe (Micro Duct) 7 Way 12/10 Biru Muda strip Biru Tua</t>
+  </si>
+  <si>
+    <t>HDPE Pipe (Micro Duct) 14 Way 12/10 Biru Muda strip Biru Tua</t>
+  </si>
+  <si>
+    <t>HDPE Pipe (Micro Duct) 4 Way 18/14 Biru Muda strip Biru Tua</t>
+  </si>
+  <si>
+    <t>HDPE Pipe (Micro Duct) 7 Way 18/14 Biru Muda strip Biru Tua</t>
+  </si>
+  <si>
+    <t>HDPE Pipe (Micro Duct) 14 Way 18/14 Biru Muda strip Biru Tua</t>
+  </si>
+  <si>
+    <t>Galvanized Pipe 1 inch</t>
+  </si>
+  <si>
+    <t>Galvanized Pipe 1 ½ inch</t>
+  </si>
+  <si>
+    <t>Galvanized Pipe 2 inch</t>
+  </si>
+  <si>
+    <t>Galvanized Pipe 3 inch</t>
+  </si>
+  <si>
+    <t>Galvanized Pipe 4 inch</t>
+  </si>
+  <si>
+    <t>Galvanized Pipe 5 inch</t>
+  </si>
+  <si>
+    <t>PVC Pipe 20 mm</t>
+  </si>
+  <si>
+    <t>PVC Pipe 1 ½ inch</t>
+  </si>
+  <si>
+    <t>PVC Pipe 2 inch</t>
+  </si>
+  <si>
+    <t>PVC Pipe 3 inch</t>
+  </si>
+  <si>
+    <t>PVC Pipe 4 inch</t>
+  </si>
+  <si>
+    <t>PVC Pipe 5 inch</t>
+  </si>
+  <si>
+    <t>Pole Fiber Optic 7 meter installation (Incl Accessories)</t>
+  </si>
+  <si>
+    <t>Pole Fiber Optic 9 meter installation (Incl Accessories)</t>
+  </si>
+  <si>
+    <t>Install Slack Support + clamp (slack FO) Fiber Optic 50 x 50 x 3 mm</t>
+  </si>
+  <si>
+    <t>Install Slack Support + clamp (slack FO) Slack Support Fiber Optic 80 x 80 x 5 mm</t>
+  </si>
+  <si>
+    <t>Install Slack Support + clamp (slack FO) Slack Support Fiber Optic 70 x 70 x 3 mm</t>
+  </si>
+  <si>
+    <t>Install Riser pipe with galvanized pipe 1,5" length 3m</t>
+  </si>
+  <si>
+    <t>Install Riser pipe with galvanized pipe 2" length 3m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supply and Install Temberang tarik (type tanpa sekang ulir) complete </t>
+  </si>
+  <si>
+    <t>Supply and Install bridge crossing kabel FO dengan tiang tunggal 9 m dengan temberang sokong T.7 / tembereng tarik include accessories</t>
+  </si>
+  <si>
+    <t>Supply and Install bridge crossing kabel FO dengan tiang ganda 9 m dengan temberang sokong T.7 / tembereng tarik include accessories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Installation galvanized pipe 2" Attachment To Bridge (ATB) dililit kawat duri  </t>
+  </si>
+  <si>
+    <t>Installation galvanized pipe 4" thickness 3.6 mm Attachment To Bridge (ATB) di lilit kawat duri</t>
+  </si>
+  <si>
+    <t>Installation galvanized pipe 4" thickness 3.6 mm Self Support di lilit kawat duri</t>
+  </si>
+  <si>
+    <t>Boring/Rojok manual subduct (50/43, 40/34,32/27)</t>
+  </si>
+  <si>
+    <t>Boring manual crossing road, using PVC pipe  4" thickness 5,5 mm</t>
+  </si>
+  <si>
+    <t>Boring manual crossing tol, using HDPE pipe 2" thickness 2,3 mm</t>
+  </si>
+  <si>
+    <t>Boring manual crossing Railway, using HDPE pipe 2" thickness 2,3 mm</t>
+  </si>
+  <si>
+    <t>Boring machine (HDD) crossing Railway, using HDPE pipe 4" thickness 2,3 mm (*)</t>
+  </si>
+  <si>
+    <t>Boring  manual crossing river (duct slump) using PVC pipe 4" tebal 5,5  mm (*)</t>
+  </si>
+  <si>
+    <t>Boring  machine (HDD) crossing river (duct slump) using PVC pipe 4" tebal 5,5  mm (*)</t>
+  </si>
+  <si>
+    <t>Supply and Install Marking Post</t>
+  </si>
+  <si>
+    <t>Manhole (Joint Box) ukuran 100 x 100 x 120 cm ( ukuran dalam bersih)</t>
+  </si>
+  <si>
+    <t>Handhole ( Pull Box ) ukuran 80 x 80  x 120 cm ( ukuran dalam bersih)</t>
+  </si>
+  <si>
+    <t>Handhole ( Pull Box ) ukuran 60 x 60  x 120 cm ( ukuran dalam bersih)</t>
+  </si>
+  <si>
+    <t>ODC Foundation ukuran 50 x 70  x 50 cm ( ukuran dalam bersih)</t>
+  </si>
+  <si>
+    <t>Pulling Fiber Optic Cable Aerial (Incl. Installation Pole)</t>
+  </si>
+  <si>
+    <t>Pulling Fiber Optic Cable Aerial (Excl. Installation Pole)</t>
+  </si>
+  <si>
+    <t>Pulling Fiber Optic Cable Burial</t>
+  </si>
+  <si>
+    <t>Pulling Fiber Optic Cable Direct Buried</t>
+  </si>
+  <si>
+    <t>Air Blown Fiber Optic</t>
+  </si>
+  <si>
+    <t>Pulling Fiber Optic Drop Wire</t>
+  </si>
+  <si>
+    <t>Pulling Fiber Optic Inbuilding</t>
+  </si>
+  <si>
+    <t>Splicing Fiber Optic (fusion splice)</t>
+  </si>
+  <si>
+    <t>Termination Fiber Optic (fusion splice)</t>
+  </si>
+  <si>
+    <t>Bobok Tembok dengan bor</t>
+  </si>
+  <si>
+    <t>Installation Patchcord Fiber Optic Indoor Duplex SM G.657A 3.0 mm SC/UPC - SC/UPC 5 meter</t>
+  </si>
+  <si>
+    <t>Installation Patchcord Fiber Optic Indoor Duplex SM G.657A 3.0 mm SC/UPC - SC/UPC 20 meter</t>
+  </si>
+  <si>
+    <t>Installation Patchcord Fiber Optic Indoor Duplex SM G.657A 3.0 mm SC/UPC - LC/UPC 5 meter</t>
+  </si>
+  <si>
+    <t>Installation Patchcord Fiber Optic Indoor Duplex SM G.657A 3.0 mm SC/UPC - LC/UPC 20 meter</t>
+  </si>
+  <si>
+    <t>Installation Patchcord Fiber Optic Indoor Duplex SM G.657A 3.0 mm LC/UPC - LC/UPC 5 meter</t>
+  </si>
+  <si>
+    <t>Installation Patchcord Fiber Optic Indoor Duplex SM G.657A 3.0 mm LC/UPC - LC/UPC 20 meter</t>
+  </si>
+  <si>
+    <t>Installation Patchcord Fiber Optic Outdoor Duplex SM G.657A 3.0 mm SC/UPC - SC/UPC 5 meter</t>
+  </si>
+  <si>
+    <t>Installation Patchcord Fiber Optic Outdoor Duplex SM G.657A 3.0 mm SC/UPC - SC/UPC 20 meter</t>
+  </si>
+  <si>
+    <t>Installation Patchcord Fiber Optic Outdoor Duplex SM G.657A 3.0 mm SC/UPC - LC/UPC 5 meter</t>
+  </si>
+  <si>
+    <t>Installation Patchcord Fiber Optic Outdoor Duplex SM G.657A 3.0 mm SC/UPC - LC/UPC 20 meter</t>
+  </si>
+  <si>
+    <t>Installation Patchcord Fiber Optic Outdoor Duplex SM G.657A 3.0 mm LC/UPC - LC/UPC 5 meter</t>
+  </si>
+  <si>
+    <t>Installation Patchcord Fiber Optic Outdoor Duplex SM G.657A 3.0 mm LC/UPC - LC/UPC 20 meter</t>
+  </si>
+  <si>
+    <t>Installation Patchcord Fiber Optic Indoor Duplex MM G.657A 3.0 mm LC/UPC - LC/UPC 5 meter</t>
+  </si>
+  <si>
+    <t>Installation Patchcord Fiber Optic Indoor Duplex MM G.657A 3.0 mm LC/UPC - LC/UPC 20 meter</t>
+  </si>
+  <si>
+    <t>Installation Pigtail Fiber Optic Indoor G.657A 3.0 mm SC/UPC</t>
+  </si>
+  <si>
+    <t>Installation Adapter FC/FC</t>
+  </si>
+  <si>
+    <t>Installation Adapter Simplex SC/SC</t>
+  </si>
+  <si>
+    <t>Installation Adapter Duplex SC/SC</t>
+  </si>
+  <si>
+    <t>Installation Adapter Simplex LC/LC</t>
+  </si>
+  <si>
+    <t>Installation Adapter Duplex LC/LC</t>
+  </si>
+  <si>
+    <t>Installation Adapter Hybrid SC/LC</t>
+  </si>
+  <si>
+    <t>Installation Adapter Hybrid FC/LC</t>
+  </si>
+  <si>
+    <t>Installation Adapter Hybrid FC/SC</t>
+  </si>
+  <si>
+    <t>OTB Capacity 12 Core SC-UPC (Include Accessories)</t>
+  </si>
+  <si>
+    <t>OTB Capacity 12 Core FC-UPC (Include Accessories)</t>
+  </si>
+  <si>
+    <t>OTB Capacity 24 Core SC-UPC (Include Accessories)</t>
+  </si>
+  <si>
+    <t>OTB Capacity 24 Core FC-UPC (Include Accessories)</t>
+  </si>
+  <si>
+    <t>OTB Capacity 48 Core SC-UPC (Include Accessories)</t>
+  </si>
+  <si>
+    <t>OTB Capacity 96 Core SC-UPC (Include Accessories)</t>
+  </si>
+  <si>
+    <t>OTB Capacity 144 Core SC-UPC (Include Accessories)</t>
+  </si>
+  <si>
+    <t>OTB Capacity 288 Core SC-UPC (Include Accessories)</t>
+  </si>
+  <si>
+    <t>OTB Capacity 288 Core LC-UPC (Include Accessories) High Density</t>
+  </si>
+  <si>
+    <t>ODP Capacity 4 core SC-UPC (Include Accessories)</t>
+  </si>
+  <si>
+    <t>ODP Capacity 8 core SC-UPC (Include Accessories)</t>
+  </si>
+  <si>
+    <t>ODP Capacity 12 core SC-UPC (Include Accessories)</t>
+  </si>
+  <si>
+    <t>ODP Capacity 24 core SC-UPC (Include Accessories)</t>
+  </si>
+  <si>
+    <t>ODP Capacity 96 core SC-UPC (Include Accessories)</t>
+  </si>
+  <si>
+    <t>Support Integration</t>
+  </si>
+  <si>
+    <t>Test Electrical Optical Time Domain Reflectometer (OTDR) 2λ (1310 dan 1550) 2-way</t>
+  </si>
+  <si>
+    <t>Test Electrical Optical Power Meter  (OPM) 2λ (1310 dan 1550) 2-way</t>
+  </si>
+  <si>
+    <t>Documentation Hardcopy (1 Set Original and 2 Set Copy)</t>
+  </si>
+  <si>
+    <t>Documentation SoftCopy (2 pcs CD/DVD dan 1 USB/FDD )</t>
+  </si>
+  <si>
+    <t>Ovelap Cable FO (m)</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>P00802</t>
+  </si>
+  <si>
+    <t>P00803</t>
+  </si>
+  <si>
+    <t>P01007</t>
+  </si>
+  <si>
+    <t>P00783</t>
+  </si>
+  <si>
+    <t>P00784</t>
+  </si>
+  <si>
+    <t>P01043</t>
+  </si>
+  <si>
+    <t>P01044</t>
+  </si>
+  <si>
+    <t>P01045</t>
+  </si>
+  <si>
+    <t>P00733</t>
+  </si>
+  <si>
+    <t>P00785</t>
+  </si>
+  <si>
+    <t>P00786</t>
+  </si>
+  <si>
+    <t>P00789</t>
+  </si>
+  <si>
+    <t>P00790</t>
+  </si>
+  <si>
+    <t>P00794</t>
+  </si>
+  <si>
+    <t>P01046</t>
+  </si>
+  <si>
+    <t>P01053</t>
+  </si>
+  <si>
+    <t>P01049</t>
+  </si>
+  <si>
+    <t>P01048</t>
+  </si>
+  <si>
+    <t>P01054</t>
+  </si>
+  <si>
+    <t>P01055</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>Ls</t>
+  </si>
+  <si>
+    <t>pcs</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>core</t>
+  </si>
+  <si>
+    <t>titik</t>
+  </si>
+  <si>
+    <t>Core</t>
+  </si>
+  <si>
+    <t>Area (City)</t>
+  </si>
+  <si>
+    <t>Program</t>
+  </si>
+  <si>
+    <t>Work Code</t>
+  </si>
+  <si>
+    <t>Region Procurment</t>
+  </si>
+  <si>
+    <t>BOQ ID</t>
+  </si>
+  <si>
+    <t>A. Preparation</t>
+  </si>
+  <si>
+    <t>B. Material Supply</t>
+  </si>
+  <si>
+    <t>B.1 FO Cable</t>
+  </si>
+  <si>
+    <t>B.2 Closure</t>
+  </si>
+  <si>
+    <t>B.3 Termination Point</t>
+  </si>
+  <si>
+    <t>B.4 Pipe</t>
+  </si>
+  <si>
+    <t>B.5 Rack</t>
+  </si>
+  <si>
+    <t>B.6 Warning Tape</t>
+  </si>
+  <si>
+    <t>B.7 Pole Fiber Optic</t>
+  </si>
+  <si>
+    <t>B.8 Patchcord Fiber Optic</t>
+  </si>
+  <si>
+    <t>B.10 Clamp</t>
+  </si>
+  <si>
+    <t>B.11 Supporting Material</t>
+  </si>
+  <si>
+    <t>B.1.1 Supply FO Cable Aerial Figure.8</t>
+  </si>
+  <si>
+    <t>B.1.2 Supply FO Cable ADSS</t>
+  </si>
+  <si>
+    <t>B.1.3 Supply FO Cable Direct Buried Single Jacket</t>
+  </si>
+  <si>
+    <t>B.1.4 Supply FO Cable Duct</t>
+  </si>
+  <si>
+    <t>B.1.5 Supply FO Cable Micro Fiber</t>
+  </si>
+  <si>
+    <t>B.1.6 Supply FO Cable Drop Wire</t>
+  </si>
+  <si>
+    <t>B.2.1 Closure Dome</t>
+  </si>
+  <si>
+    <t>B.2.2 Closure Inline</t>
+  </si>
+  <si>
+    <t>B.3.1 Optical Termination Box (OTB)</t>
+  </si>
+  <si>
+    <t>B.3.2 Optical Distribution Point (ODP)</t>
+  </si>
+  <si>
+    <t>B.3.3 Pasive Splitter</t>
+  </si>
+  <si>
+    <t>B.3.4 Rosset</t>
+  </si>
+  <si>
+    <t>B.4.1 HDPE Pipe (Subduct)</t>
+  </si>
+  <si>
+    <t>B.4.2 HDPE Pipe (Micro Duct)</t>
+  </si>
+  <si>
+    <t>B.4.3 Galvanized Pipe</t>
+  </si>
+  <si>
+    <t>B.4.4 PVC Pipe</t>
+  </si>
+  <si>
+    <t>B.4.5 Conduit/Flexible</t>
+  </si>
+  <si>
+    <t>B.5.1 Open Rack</t>
+  </si>
+  <si>
+    <t>B.5.2 Closed Rack/Wallmount Rack</t>
+  </si>
+  <si>
+    <t>B.5.3 Outdoor Cabinet (ODC)</t>
+  </si>
+  <si>
+    <t>B.8.1 Patchcord Fiber Optic Single Mode Indoor</t>
+  </si>
+  <si>
+    <t>B.8.2 Patchcord Fiber Optic Single Mode Outdoor Duplex (Armoured)</t>
+  </si>
+  <si>
+    <t>B.8.3 Patchcord Fiber Optic Multi Mode Indoor Duplex</t>
+  </si>
+  <si>
+    <t>B.8.4 Pigtail</t>
+  </si>
+  <si>
+    <t>B.8.5 Adapter</t>
+  </si>
+  <si>
+    <t>A.1</t>
+  </si>
+  <si>
+    <t>A.2</t>
+  </si>
+  <si>
+    <t>A.3</t>
+  </si>
+  <si>
+    <t>A.4</t>
+  </si>
+  <si>
+    <t>A.5</t>
+  </si>
+  <si>
+    <t>A.6</t>
+  </si>
+  <si>
+    <t>A.7</t>
+  </si>
+  <si>
+    <t>A.8</t>
+  </si>
+  <si>
+    <t>B.1.1.1</t>
+  </si>
+  <si>
+    <t>B.1.1.2</t>
+  </si>
+  <si>
+    <t>B.1.1.3</t>
+  </si>
+  <si>
+    <t>B.1.1.4</t>
+  </si>
+  <si>
+    <t>B.1.1.5</t>
+  </si>
+  <si>
+    <t>B.1.1.6</t>
+  </si>
+  <si>
+    <t>B.1.2.1</t>
+  </si>
+  <si>
+    <t>B.1.2.2</t>
+  </si>
+  <si>
+    <t>B.1.2.3</t>
+  </si>
+  <si>
+    <t>B.1.2.4</t>
+  </si>
+  <si>
+    <t>B.1.2.5</t>
+  </si>
+  <si>
+    <t>B.1.2.6</t>
+  </si>
+  <si>
+    <t>B.1.3.1</t>
+  </si>
+  <si>
+    <t>B.1.3.2</t>
+  </si>
+  <si>
+    <t>B.1.3.3</t>
+  </si>
+  <si>
+    <t>B.1.3.4</t>
+  </si>
+  <si>
+    <t>B.1.3.5</t>
+  </si>
+  <si>
+    <t>B.1.3.6</t>
+  </si>
+  <si>
+    <t>B.1.3.7</t>
+  </si>
+  <si>
+    <t>B.1.3.8</t>
+  </si>
+  <si>
+    <t>B.1.4.1</t>
+  </si>
+  <si>
+    <t>B.1.4.2</t>
+  </si>
+  <si>
+    <t>B.1.4.3</t>
+  </si>
+  <si>
+    <t>B.1.4.4</t>
+  </si>
+  <si>
+    <t>B.1.4.5</t>
+  </si>
+  <si>
+    <t>B.1.4.6</t>
+  </si>
+  <si>
+    <t>B.1.4.7</t>
+  </si>
+  <si>
+    <t>B.1.4.8</t>
+  </si>
+  <si>
+    <t>B.1.5.1</t>
+  </si>
+  <si>
+    <t>B.1.5.2</t>
+  </si>
+  <si>
+    <t>B.1.5.3</t>
+  </si>
+  <si>
+    <t>B.1.5.4</t>
+  </si>
+  <si>
+    <t>B.1.5.5</t>
+  </si>
+  <si>
+    <t>B.1.6.1</t>
+  </si>
+  <si>
+    <t>B.1.6.2</t>
+  </si>
+  <si>
+    <t>B.2.1.1</t>
+  </si>
+  <si>
+    <t>B.2.1.2</t>
+  </si>
+  <si>
+    <t>B.2.1.3</t>
+  </si>
+  <si>
+    <t>B.2.1.4</t>
+  </si>
+  <si>
+    <t>B.2.1.5</t>
+  </si>
+  <si>
+    <t>B.2.2.1</t>
+  </si>
+  <si>
+    <t>B.2.2.2</t>
+  </si>
+  <si>
+    <t>B.2.2.3</t>
+  </si>
+  <si>
+    <t>B.2.2.4</t>
+  </si>
+  <si>
+    <t>B.2.2.5</t>
+  </si>
+  <si>
+    <t>B.3.1.1</t>
+  </si>
+  <si>
+    <t>B.3.1.2</t>
+  </si>
+  <si>
+    <t>B.3.1.3</t>
+  </si>
+  <si>
+    <t>B.3.1.4</t>
+  </si>
+  <si>
+    <t>B.3.1.5</t>
+  </si>
+  <si>
+    <t>B.3.1.6</t>
+  </si>
+  <si>
+    <t>B.3.1.7</t>
+  </si>
+  <si>
+    <t>B.3.1.8</t>
+  </si>
+  <si>
+    <t>B.3.1.9</t>
+  </si>
+  <si>
+    <t>B.3.2.1</t>
+  </si>
+  <si>
+    <t>B.3.2.2</t>
+  </si>
+  <si>
+    <t>B.3.2.3</t>
+  </si>
+  <si>
+    <t>B.3.2.4</t>
+  </si>
+  <si>
+    <t>B.3.2.5</t>
+  </si>
+  <si>
+    <t>B.3.2.6</t>
+  </si>
+  <si>
+    <t>B.3.3.1</t>
+  </si>
+  <si>
+    <t>B.3.3.2</t>
+  </si>
+  <si>
+    <t>B.3.3.3</t>
+  </si>
+  <si>
+    <t>B.3.3.4</t>
+  </si>
+  <si>
+    <t>B.3.3.5</t>
+  </si>
+  <si>
+    <t>B.3.4.1</t>
+  </si>
+  <si>
+    <t>B.4.1.1</t>
+  </si>
+  <si>
+    <t>B.4.1.2</t>
+  </si>
+  <si>
+    <t>B.4.1.3</t>
+  </si>
+  <si>
+    <t>B.4.2.1</t>
+  </si>
+  <si>
+    <t>B.4.2.2</t>
+  </si>
+  <si>
+    <t>B.4.2.3</t>
+  </si>
+  <si>
+    <t>B.4.2.4</t>
+  </si>
+  <si>
+    <t>B.4.2.5</t>
+  </si>
+  <si>
+    <t>B.4.2.6</t>
+  </si>
+  <si>
+    <t>B.4.3.1</t>
+  </si>
+  <si>
+    <t>B.4.3.2</t>
+  </si>
+  <si>
+    <t>B.4.3.3</t>
+  </si>
+  <si>
+    <t>B.4.3.4</t>
+  </si>
+  <si>
+    <t>B.4.3.5</t>
+  </si>
+  <si>
+    <t>B.4.3.6</t>
+  </si>
+  <si>
+    <t>B.4.4.1</t>
+  </si>
+  <si>
+    <t>B.4.4.2</t>
+  </si>
+  <si>
+    <t>B.4.4.3</t>
+  </si>
+  <si>
+    <t>B.4.4.4</t>
+  </si>
+  <si>
+    <t>B.4.4.5</t>
+  </si>
+  <si>
+    <t>B.4.4.6</t>
+  </si>
+  <si>
+    <t>B.4.5.1</t>
+  </si>
+  <si>
+    <t>B.4.5.2</t>
+  </si>
+  <si>
+    <t>B.4.5.3</t>
+  </si>
+  <si>
+    <t>B.4.5.4</t>
+  </si>
+  <si>
+    <t>B.5.1.1</t>
+  </si>
+  <si>
+    <t>B.5.2.1</t>
+  </si>
+  <si>
+    <t>B.5.2.2</t>
+  </si>
+  <si>
+    <t>B.5.2.3</t>
+  </si>
+  <si>
+    <t>B.5.2.4</t>
+  </si>
+  <si>
+    <t>B.5.3.1</t>
+  </si>
+  <si>
+    <t>B.5.3.2</t>
+  </si>
+  <si>
+    <t>B.5.3.3</t>
+  </si>
+  <si>
+    <t>B.6.1</t>
+  </si>
+  <si>
+    <t>B.7.1</t>
+  </si>
+  <si>
+    <t>B.7.2</t>
+  </si>
+  <si>
+    <t>B.7.3</t>
+  </si>
+  <si>
+    <t>B.7.4</t>
+  </si>
+  <si>
+    <t>B.7.5</t>
+  </si>
+  <si>
+    <t>B.8.1.1</t>
+  </si>
+  <si>
+    <t>B.8.1.2</t>
+  </si>
+  <si>
+    <t>B.8.1.3</t>
+  </si>
+  <si>
+    <t>B.8.1.4</t>
+  </si>
+  <si>
+    <t>B.8.1.5</t>
+  </si>
+  <si>
+    <t>B.8.1.6</t>
+  </si>
+  <si>
+    <t>B.8.1.7</t>
+  </si>
+  <si>
+    <t>B.8.1.8</t>
+  </si>
+  <si>
+    <t>B.8.2.1</t>
+  </si>
+  <si>
+    <t>B.8.2.2</t>
+  </si>
+  <si>
+    <t>B.8.2.3</t>
+  </si>
+  <si>
+    <t>B.8.2.4</t>
+  </si>
+  <si>
+    <t>B.8.2.5</t>
+  </si>
+  <si>
+    <t>B.8.2.6</t>
+  </si>
+  <si>
+    <t>B.8.3.1</t>
+  </si>
+  <si>
+    <t>B.8.3.2</t>
+  </si>
+  <si>
+    <t>B.8.4.1</t>
+  </si>
+  <si>
+    <t>B.8.5.1</t>
+  </si>
+  <si>
+    <t>B.8.5.2</t>
+  </si>
+  <si>
+    <t>B.8.5.3</t>
+  </si>
+  <si>
+    <t>B.8.5.4</t>
+  </si>
+  <si>
+    <t>B.8.5.5</t>
+  </si>
+  <si>
+    <t>B.8.5.6</t>
+  </si>
+  <si>
+    <t>B.8.5.7</t>
+  </si>
+  <si>
+    <t>B.8.5.8</t>
+  </si>
+  <si>
+    <t>B.10.1</t>
+  </si>
+  <si>
+    <t>B.11.1</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Pengadaan Rambu Pengaman dan Papan Nama Proyek</t>
+  </si>
+  <si>
+    <t>Pembuatan direksi keet/ bedeng kerja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koordinasi warga dan perijinan PU (*) dinas terkait </t>
+  </si>
+  <si>
+    <t>Koordinasi dan perijinan PJKA (*)</t>
+  </si>
+  <si>
+    <t>Koordinasi dan perijinan Bina marga/Jalan Toll (*)</t>
+  </si>
+  <si>
+    <t>Koordinasi, perijinan Private area/Community and supervise (*)</t>
+  </si>
+  <si>
+    <t>Survey lokasi TSSR,  pembuatan As Plan Drawing (APD/KMZ/KML) dan As Buid Drawing (ABD)</t>
+  </si>
+  <si>
+    <t>Transportasi &amp; Mobilisasi</t>
+  </si>
+  <si>
+    <t>FO Cable Aerial SM G.652D 12 core</t>
+  </si>
+  <si>
+    <t>FO Cable Aerial SM G.652D 24 core</t>
+  </si>
+  <si>
+    <t>FO Cable Aerial SM G.652D 48 core</t>
+  </si>
+  <si>
+    <t>FO Cable Aerial SM G.652D 72 core</t>
+  </si>
+  <si>
+    <t>FO Cable Aerial SM G.652D 96 core</t>
+  </si>
+  <si>
+    <t>FO Cable Aerial SM G.652D 144 core</t>
+  </si>
+  <si>
+    <t>FO Cable ADSS SM G.652D 12 core</t>
+  </si>
+  <si>
+    <t>FO Cable ADSS SM G.652D 24 core</t>
+  </si>
+  <si>
+    <t>FO Cable ADSS SM G.652D 48 core</t>
+  </si>
+  <si>
+    <t>FO Cable ADSS SM G.652D 72 core</t>
+  </si>
+  <si>
+    <t>FO Cable ADSS SM G.652D 96 core</t>
+  </si>
+  <si>
+    <t>FO Cable ADSS SM G.652D 144 core</t>
+  </si>
+  <si>
+    <t>FO Cable Direct Buried Single Jacket SM G.652D 12 core</t>
+  </si>
+  <si>
+    <t>FO Cable Direct Buried Single Jacket SM G.652D 24 core</t>
+  </si>
+  <si>
+    <t>FO Cable Direct Buried Single Jacket SM G.652D 48 core</t>
+  </si>
+  <si>
+    <t>FO Cable Direct Buried Single Jacket SM G.652D 72 core</t>
+  </si>
+  <si>
+    <t>FO Cable Direct Buried Single Jacket SM G.652D 96 core</t>
+  </si>
+  <si>
+    <t>FO Cable Direct Buried Single Jacket SM G.652D 144 core</t>
+  </si>
+  <si>
+    <t>FO Cable Direct Buried Single Jacket SM G.652D 264 core</t>
+  </si>
+  <si>
+    <t>FO Cable Direct Buried Single Jacket SM G.652D 288 core</t>
+  </si>
+  <si>
+    <t>FO Cable Duct SM G.652D 12 core</t>
+  </si>
+  <si>
+    <t>FO Cable Duct SM G.652D 24 core</t>
+  </si>
+  <si>
+    <t>FO Cable Duct SM G.652D 48 core</t>
+  </si>
+  <si>
+    <t>FO Cable Duct SM G.652D 72 core</t>
+  </si>
+  <si>
+    <t>FO Cable Duct SM G.652D 96 core</t>
+  </si>
+  <si>
+    <t>FO Cable Duct SM G.652D 144 core</t>
+  </si>
+  <si>
+    <t>FO Cable Duct SM G.652D 264 core</t>
+  </si>
+  <si>
+    <t>FO Cable Duct SM G.652D 288 core</t>
+  </si>
+  <si>
+    <t>FO Cable Micro Fiber SM G.652D 24 core</t>
+  </si>
+  <si>
+    <t>FO Cable Micro Fiber SM G.652D 48 core</t>
+  </si>
+  <si>
+    <t>FO Cable Micro Fiber SM G.652D 96 core</t>
+  </si>
+  <si>
+    <t>FO Cable Micro Fiber SM G.652D 144 core</t>
+  </si>
+  <si>
+    <t>FO Cable Micro Fiber SM G.652D 288 core</t>
+  </si>
+  <si>
+    <t>FO Cable Drop Wire SM G.657A 1 core</t>
+  </si>
+  <si>
+    <t>FO Cable Drop Wire SM G.657A 2 core</t>
+  </si>
+  <si>
+    <t>Closure Dome 24 Core</t>
+  </si>
+  <si>
+    <t>Closure Dome 48 Core</t>
+  </si>
+  <si>
+    <t>Closure Dome 144 Core</t>
+  </si>
+  <si>
+    <t>Closure Dome 96 Core</t>
+  </si>
+  <si>
+    <t>Closure Dome 864 Core High Density</t>
+  </si>
+  <si>
+    <t>Closure Inline 24 Core</t>
+  </si>
+  <si>
+    <t>Closure Inline 48 Core</t>
+  </si>
+  <si>
+    <t>Closure Inline 96 Core</t>
+  </si>
+  <si>
+    <t>Closure Inline 144 Core</t>
+  </si>
+  <si>
+    <t>Closure Inline 288 Core</t>
+  </si>
+  <si>
+    <t>ODP Capacity 16 core SC-UPC (Include Accessories)</t>
+  </si>
+  <si>
+    <t>ODP Padestal 16 Core (Under ground)</t>
+  </si>
+  <si>
+    <t>Splitter 1:2 SC-UPC</t>
+  </si>
+  <si>
+    <t>Splitter 1:4 SC-UPC</t>
+  </si>
+  <si>
+    <t>Splitter 1:8 SC-UPC</t>
+  </si>
+  <si>
+    <t>Splitter 1:16 SC-UPC</t>
+  </si>
+  <si>
+    <t>Splitter 1:32 SC-UPC</t>
+  </si>
+  <si>
+    <t>Rosset 2 Port SC-UPC</t>
+  </si>
+  <si>
+    <t>Flexible Conduit Armor ¾ inch (Spiral)</t>
+  </si>
+  <si>
+    <t>Flexible Conduit Armor 2 inch (Spiral)</t>
+  </si>
+  <si>
+    <t>Flexible Conduit Armor 3 inch (Spiral)</t>
+  </si>
+  <si>
+    <t>Flexible Conduit 20 mm (Spiral)</t>
+  </si>
+  <si>
+    <t>Open Rack 42 U (Include Accessories and cage nut)</t>
+  </si>
+  <si>
+    <t>Closed Rack 8 U-450 mm (Include Accessories, Fan, cage nut, etc)</t>
+  </si>
+  <si>
+    <t>Closed Rack 20 U-900 mm (Include Accessories, Fan, cage nut, etc)</t>
+  </si>
+  <si>
+    <t>Closed Rack 42 U-900 mm (Include Accessories, Fan, cage nut, etc)</t>
+  </si>
+  <si>
+    <t>Closed Rack 42 U-1150 mm (Include Accessories, Fan, cage nut, etc)</t>
+  </si>
+  <si>
+    <t>ODC Cap 144 Core (Include Accessories Cassete, Adapter, Pigtail, etc)</t>
+  </si>
+  <si>
+    <t>ODC Cap 288 Core (Include Accessories Cassete, Adapter, Pigtail, etc)</t>
+  </si>
+  <si>
+    <t>ODC Cap 576 Core (Include Accessories Cassete, Adapter, Pigtail, etc)</t>
+  </si>
+  <si>
+    <t>Warning Tape Fiber Optic 6 inch</t>
+  </si>
+  <si>
+    <t>Pole Fiber Optic 7 meter 2 Step</t>
+  </si>
+  <si>
+    <t>Pole Fiber Optic 9 meter 3 Step</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slack Support + clamp (slack FO),  50 x 50 x 3 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slack Support + clamp (slack FO),  80 x 50 x 5 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slack Support + clamp (slack FO),  70 x 70 x 3 mm </t>
+  </si>
+  <si>
+    <t>Patchcord Fiber Optic Indoor Duplex SM G.657A 3.0 mm SC/UPC - SC/UPC 5 meter</t>
+  </si>
+  <si>
+    <t>Patchcord Fiber Optic Indoor Duplex SM G.657A 3.0 mm SC/UPC - SC/UPC 20 meter</t>
+  </si>
+  <si>
+    <t>Patchcord Fiber Optic Indoor Duplex SM G.657A 3.0 mm SC/UPC - LC/UPC 5 meter</t>
+  </si>
+  <si>
+    <t>Patchcord Fiber Optic Indoor Duplex SM G.657A 3.0 mm SC/UPC - LC/UPC 20 meter</t>
+  </si>
+  <si>
+    <t>Patchcord Fiber Optic Indoor Duplex SM G.657A 3.0 mm LC/UPC - LC/UPC 5 meter</t>
+  </si>
+  <si>
+    <t>Patchcord Fiber Optic Indoor Duplex SM G.657A 3.0 mm LC/UPC - LC/UPC 20 meter</t>
+  </si>
+  <si>
+    <t>Patchcord Fiber Optic Indoor Duplex SM G.657A 3.0 mm FC/UPC - LC/UPC 5 meter</t>
+  </si>
+  <si>
+    <t>Patchcord Fiber Optic Indoor Duplex SM G.657A 3.0 mm FC/UPC - LC/UPC 20 meter</t>
+  </si>
+  <si>
+    <t>Patchcord Fiber Optic Outdoor Duplex SM G.657A 3.0 mm SC/UPC - SC/UPC 5 meter</t>
+  </si>
+  <si>
+    <t>Patchcord Fiber Optic Outdoor Duplex SM G.657A 3.0 mm SC/UPC - SC/UPC 20 meter</t>
+  </si>
+  <si>
+    <t>Patchcord Fiber Optic Outdoor Duplex SM G.657A 3.0 mm SC/UPC - LC/UPC 5 meter</t>
+  </si>
+  <si>
+    <t>Patchcord Fiber Optic Outdoor Duplex SM G.657A 3.0 mm SC/UPC - LC/UPC 20 meter</t>
+  </si>
+  <si>
+    <t>Patchcord Fiber Optic Outdoor Duplex SM G.657A 3.0 mm LC/UPC - LC/UPC 5 meter</t>
+  </si>
+  <si>
+    <t>Patchcord Fiber Optic Outdoor Duplex SM G.657A 3.0 mm LC/UPC - LC/UPC 20 meter</t>
+  </si>
+  <si>
+    <t>Patchcord Fiber Optic Indoor Duplex MM G.657A 3.0 mm LC/UPC - LC/UPC 5 meter</t>
+  </si>
+  <si>
+    <t>Patchcord Fiber Optic Indoor Duplex MM G.657A 3.0 mm LC/UPC - LC/UPC 20 meter</t>
+  </si>
+  <si>
+    <t>Pigtail Fiber Optic Indoor G.657A 1.0 mm SC/UPC</t>
+  </si>
+  <si>
+    <t>Adapter FC/FC</t>
+  </si>
+  <si>
+    <t>Adapter Simplex SC/SC</t>
+  </si>
+  <si>
+    <t>Adapter Duplex SC/SC</t>
+  </si>
+  <si>
+    <t>Adapter Simplex LC/LC</t>
+  </si>
+  <si>
+    <t>Adapter Duplex LC/LC</t>
+  </si>
+  <si>
+    <t>Adapter Hybrid SC/LC</t>
+  </si>
+  <si>
+    <t>Adapter Hybrid FC/LC</t>
+  </si>
+  <si>
+    <t>Adapter Hybrid FC/SC</t>
+  </si>
+  <si>
+    <t>Clamp Omega</t>
+  </si>
+  <si>
+    <t>Supporting Material</t>
+  </si>
+  <si>
+    <t>Item_ID</t>
+  </si>
+  <si>
+    <t>P00782</t>
+  </si>
+  <si>
+    <t>P00781</t>
+  </si>
+  <si>
+    <t>P00778</t>
+  </si>
+  <si>
+    <t>P00834</t>
+  </si>
+  <si>
+    <t>P00797</t>
+  </si>
+  <si>
+    <t>P01051</t>
+  </si>
+  <si>
+    <t>P01052</t>
+  </si>
+  <si>
+    <t>P00691</t>
+  </si>
+  <si>
+    <t>P00684</t>
+  </si>
+  <si>
+    <t>P00728</t>
+  </si>
+  <si>
+    <t>UoM</t>
+  </si>
+  <si>
+    <t>C.12.2.6</t>
+  </si>
+  <si>
+    <t>ODP Capacity 48 core SC-UPC (Include Accessories)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,8 +1960,31 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -219,8 +2009,80 @@
         <bgColor rgb="FF6AA84F"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+        <bgColor rgb="FF00FF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0000FF"/>
+        <bgColor rgb="FF0000FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0066"/>
+        <bgColor rgb="FFFF0066"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E0B3"/>
+        <bgColor rgb="FFC5E0B3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFD9"/>
+        <bgColor rgb="FFE2EFD9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E2F3"/>
+        <bgColor rgb="FFD9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8EAADB"/>
+        <bgColor rgb="FF8EAADB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8D8D8"/>
+        <bgColor rgb="FFD8D8D8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -256,11 +2118,110 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -282,6 +2243,129 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="12" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -584,6 +2668,4118 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{566DC2A0-09A2-46D9-9EFA-BA73FD8EC6EF}">
+  <dimension ref="A1:JD7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="260" max="263" width="16.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:264" x14ac:dyDescent="0.25">
+      <c r="A1" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="45" t="s">
+        <v>298</v>
+      </c>
+      <c r="K1" s="45" t="s">
+        <v>299</v>
+      </c>
+      <c r="L1" s="45" t="s">
+        <v>300</v>
+      </c>
+      <c r="M1" s="45" t="s">
+        <v>301</v>
+      </c>
+      <c r="N1" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="O1" s="45" t="s">
+        <v>302</v>
+      </c>
+      <c r="P1" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="9"/>
+      <c r="AE1" s="9"/>
+      <c r="AF1" s="9"/>
+      <c r="AG1" s="9"/>
+      <c r="AH1" s="9"/>
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="9"/>
+      <c r="AK1" s="9"/>
+      <c r="AL1" s="9"/>
+      <c r="AM1" s="9"/>
+      <c r="AN1" s="9"/>
+      <c r="AO1" s="9"/>
+      <c r="AP1" s="9"/>
+      <c r="AQ1" s="9"/>
+      <c r="AR1" s="9"/>
+      <c r="AS1" s="9"/>
+      <c r="AT1" s="9"/>
+      <c r="AU1" s="9"/>
+      <c r="AV1" s="9"/>
+      <c r="AW1" s="9"/>
+      <c r="AX1" s="9"/>
+      <c r="AY1" s="9"/>
+      <c r="AZ1" s="9"/>
+      <c r="BA1" s="9"/>
+      <c r="BB1" s="9"/>
+      <c r="BC1" s="9"/>
+      <c r="BD1" s="9"/>
+      <c r="BE1" s="9"/>
+      <c r="BF1" s="9"/>
+      <c r="BG1" s="9"/>
+      <c r="BH1" s="9"/>
+      <c r="BI1" s="9"/>
+      <c r="BJ1" s="9"/>
+      <c r="BK1" s="9"/>
+      <c r="BL1" s="9"/>
+      <c r="BM1" s="9"/>
+      <c r="BN1" s="9"/>
+      <c r="BO1" s="9"/>
+      <c r="BP1" s="9"/>
+      <c r="BQ1" s="9"/>
+      <c r="BR1" s="9"/>
+      <c r="BS1" s="9"/>
+      <c r="BT1" s="9"/>
+      <c r="BU1" s="9"/>
+      <c r="BV1" s="9"/>
+      <c r="BW1" s="9"/>
+      <c r="BX1" s="9"/>
+      <c r="BY1" s="9"/>
+      <c r="BZ1" s="9"/>
+      <c r="CA1" s="9"/>
+      <c r="CB1" s="9"/>
+      <c r="CC1" s="9"/>
+      <c r="CD1" s="9"/>
+      <c r="CE1" s="9"/>
+      <c r="CF1" s="9"/>
+      <c r="CG1" s="9"/>
+      <c r="CH1" s="9"/>
+      <c r="CI1" s="9"/>
+      <c r="CJ1" s="9"/>
+      <c r="CK1" s="9"/>
+      <c r="CL1" s="9"/>
+      <c r="CM1" s="9"/>
+      <c r="CN1" s="9"/>
+      <c r="CO1" s="9"/>
+      <c r="CP1" s="9"/>
+      <c r="CQ1" s="9"/>
+      <c r="CR1" s="9"/>
+      <c r="CS1" s="9"/>
+      <c r="CT1" s="9"/>
+      <c r="CU1" s="9"/>
+      <c r="CV1" s="9"/>
+      <c r="CW1" s="9"/>
+      <c r="CX1" s="9"/>
+      <c r="CY1" s="9"/>
+      <c r="CZ1" s="9"/>
+      <c r="DA1" s="9"/>
+      <c r="DB1" s="9"/>
+      <c r="DC1" s="9"/>
+      <c r="DD1" s="9"/>
+      <c r="DE1" s="9"/>
+      <c r="DF1" s="9"/>
+      <c r="DG1" s="9"/>
+      <c r="DH1" s="9"/>
+      <c r="DI1" s="9"/>
+      <c r="DJ1" s="9"/>
+      <c r="DK1" s="9"/>
+      <c r="DL1" s="9"/>
+      <c r="DM1" s="9"/>
+      <c r="DN1" s="9"/>
+      <c r="DO1" s="9"/>
+      <c r="DP1" s="9"/>
+      <c r="DQ1" s="9"/>
+      <c r="DR1" s="9"/>
+      <c r="DS1" s="9"/>
+      <c r="DT1" s="9"/>
+      <c r="DU1" s="9"/>
+      <c r="DV1" s="9"/>
+      <c r="DW1" s="9"/>
+      <c r="DX1" s="9"/>
+      <c r="DY1" s="9"/>
+      <c r="DZ1" s="9"/>
+      <c r="EA1" s="9"/>
+      <c r="EB1" s="9"/>
+      <c r="EC1" s="9"/>
+      <c r="ED1" s="9"/>
+      <c r="EE1" s="9"/>
+      <c r="EF1" s="9"/>
+      <c r="EG1" s="9"/>
+      <c r="EH1" s="9"/>
+      <c r="EI1" s="9"/>
+      <c r="EJ1" s="9"/>
+      <c r="EK1" s="9"/>
+      <c r="EL1" s="9"/>
+      <c r="EM1" s="9"/>
+      <c r="EN1" s="9"/>
+      <c r="EO1" s="9"/>
+      <c r="EP1" s="9"/>
+      <c r="EQ1" s="9"/>
+      <c r="ER1" s="9"/>
+      <c r="ES1" s="9"/>
+      <c r="ET1" s="9"/>
+      <c r="EU1" s="9"/>
+      <c r="EV1" s="9"/>
+      <c r="EW1" s="9"/>
+      <c r="EX1" s="9"/>
+      <c r="EY1" s="9"/>
+      <c r="EZ1" s="10"/>
+      <c r="FA1" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="FB1" s="9"/>
+      <c r="FC1" s="9"/>
+      <c r="FD1" s="9"/>
+      <c r="FE1" s="9"/>
+      <c r="FF1" s="9"/>
+      <c r="FG1" s="9"/>
+      <c r="FH1" s="9"/>
+      <c r="FI1" s="9"/>
+      <c r="FJ1" s="9"/>
+      <c r="FK1" s="9"/>
+      <c r="FL1" s="9"/>
+      <c r="FM1" s="9"/>
+      <c r="FN1" s="9"/>
+      <c r="FO1" s="9"/>
+      <c r="FP1" s="9"/>
+      <c r="FQ1" s="9"/>
+      <c r="FR1" s="9"/>
+      <c r="FS1" s="9"/>
+      <c r="FT1" s="9"/>
+      <c r="FU1" s="9"/>
+      <c r="FV1" s="9"/>
+      <c r="FW1" s="9"/>
+      <c r="FX1" s="9"/>
+      <c r="FY1" s="9"/>
+      <c r="FZ1" s="9"/>
+      <c r="GA1" s="9"/>
+      <c r="GB1" s="9"/>
+      <c r="GC1" s="9"/>
+      <c r="GD1" s="9"/>
+      <c r="GE1" s="9"/>
+      <c r="GF1" s="9"/>
+      <c r="GG1" s="9"/>
+      <c r="GH1" s="9"/>
+      <c r="GI1" s="9"/>
+      <c r="GJ1" s="9"/>
+      <c r="GK1" s="9"/>
+      <c r="GL1" s="9"/>
+      <c r="GM1" s="9"/>
+      <c r="GN1" s="9"/>
+      <c r="GO1" s="9"/>
+      <c r="GP1" s="9"/>
+      <c r="GQ1" s="9"/>
+      <c r="GR1" s="9"/>
+      <c r="GS1" s="9"/>
+      <c r="GT1" s="9"/>
+      <c r="GU1" s="9"/>
+      <c r="GV1" s="9"/>
+      <c r="GW1" s="9"/>
+      <c r="GX1" s="9"/>
+      <c r="GY1" s="9"/>
+      <c r="GZ1" s="9"/>
+      <c r="HA1" s="9"/>
+      <c r="HB1" s="9"/>
+      <c r="HC1" s="9"/>
+      <c r="HD1" s="9"/>
+      <c r="HE1" s="9"/>
+      <c r="HF1" s="9"/>
+      <c r="HG1" s="9"/>
+      <c r="HH1" s="9"/>
+      <c r="HI1" s="9"/>
+      <c r="HJ1" s="9"/>
+      <c r="HK1" s="9"/>
+      <c r="HL1" s="9"/>
+      <c r="HM1" s="9"/>
+      <c r="HN1" s="9"/>
+      <c r="HO1" s="9"/>
+      <c r="HP1" s="9"/>
+      <c r="HQ1" s="9"/>
+      <c r="HR1" s="9"/>
+      <c r="HS1" s="9"/>
+      <c r="HT1" s="9"/>
+      <c r="HU1" s="9"/>
+      <c r="HV1" s="9"/>
+      <c r="HW1" s="9"/>
+      <c r="HX1" s="9"/>
+      <c r="HY1" s="9"/>
+      <c r="HZ1" s="9"/>
+      <c r="IA1" s="9"/>
+      <c r="IB1" s="9"/>
+      <c r="IC1" s="9"/>
+      <c r="ID1" s="9"/>
+      <c r="IE1" s="9"/>
+      <c r="IF1" s="9"/>
+      <c r="IG1" s="9"/>
+      <c r="IH1" s="9"/>
+      <c r="II1" s="9"/>
+      <c r="IJ1" s="9"/>
+      <c r="IK1" s="9"/>
+      <c r="IL1" s="9"/>
+      <c r="IM1" s="9"/>
+      <c r="IN1" s="9"/>
+      <c r="IO1" s="9"/>
+      <c r="IP1" s="9"/>
+      <c r="IQ1" s="9"/>
+      <c r="IR1" s="9"/>
+      <c r="IS1" s="9"/>
+      <c r="IT1" s="9"/>
+      <c r="IU1" s="9"/>
+      <c r="IV1" s="9"/>
+      <c r="IW1" s="9"/>
+      <c r="IX1" s="9"/>
+      <c r="IY1" s="10"/>
+      <c r="IZ1" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="JA1" s="9"/>
+      <c r="JB1" s="9"/>
+      <c r="JC1" s="10"/>
+      <c r="JD1" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:264" x14ac:dyDescent="0.25">
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+      <c r="W2" s="14"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="46" t="s">
+        <v>305</v>
+      </c>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="9"/>
+      <c r="AD2" s="9"/>
+      <c r="AE2" s="9"/>
+      <c r="AF2" s="9"/>
+      <c r="AG2" s="9"/>
+      <c r="AH2" s="9"/>
+      <c r="AI2" s="9"/>
+      <c r="AJ2" s="9"/>
+      <c r="AK2" s="9"/>
+      <c r="AL2" s="9"/>
+      <c r="AM2" s="9"/>
+      <c r="AN2" s="9"/>
+      <c r="AO2" s="9"/>
+      <c r="AP2" s="9"/>
+      <c r="AQ2" s="9"/>
+      <c r="AR2" s="9"/>
+      <c r="AS2" s="9"/>
+      <c r="AT2" s="9"/>
+      <c r="AU2" s="9"/>
+      <c r="AV2" s="9"/>
+      <c r="AW2" s="9"/>
+      <c r="AX2" s="9"/>
+      <c r="AY2" s="9"/>
+      <c r="AZ2" s="9"/>
+      <c r="BA2" s="9"/>
+      <c r="BB2" s="9"/>
+      <c r="BC2" s="9"/>
+      <c r="BD2" s="9"/>
+      <c r="BE2" s="9"/>
+      <c r="BF2" s="9"/>
+      <c r="BG2" s="10"/>
+      <c r="BH2" s="47" t="s">
+        <v>306</v>
+      </c>
+      <c r="BI2" s="9"/>
+      <c r="BJ2" s="9"/>
+      <c r="BK2" s="9"/>
+      <c r="BL2" s="9"/>
+      <c r="BM2" s="9"/>
+      <c r="BN2" s="9"/>
+      <c r="BO2" s="9"/>
+      <c r="BP2" s="9"/>
+      <c r="BQ2" s="10"/>
+      <c r="BR2" s="46" t="s">
+        <v>307</v>
+      </c>
+      <c r="BS2" s="9"/>
+      <c r="BT2" s="9"/>
+      <c r="BU2" s="9"/>
+      <c r="BV2" s="9"/>
+      <c r="BW2" s="9"/>
+      <c r="BX2" s="9"/>
+      <c r="BY2" s="9"/>
+      <c r="BZ2" s="9"/>
+      <c r="CA2" s="9"/>
+      <c r="CB2" s="9"/>
+      <c r="CC2" s="9"/>
+      <c r="CD2" s="9"/>
+      <c r="CE2" s="9"/>
+      <c r="CF2" s="9"/>
+      <c r="CG2" s="9"/>
+      <c r="CH2" s="9"/>
+      <c r="CI2" s="9"/>
+      <c r="CJ2" s="9"/>
+      <c r="CK2" s="9"/>
+      <c r="CL2" s="10"/>
+      <c r="CM2" s="47" t="s">
+        <v>308</v>
+      </c>
+      <c r="CN2" s="9"/>
+      <c r="CO2" s="9"/>
+      <c r="CP2" s="9"/>
+      <c r="CQ2" s="9"/>
+      <c r="CR2" s="9"/>
+      <c r="CS2" s="9"/>
+      <c r="CT2" s="9"/>
+      <c r="CU2" s="9"/>
+      <c r="CV2" s="9"/>
+      <c r="CW2" s="9"/>
+      <c r="CX2" s="9"/>
+      <c r="CY2" s="9"/>
+      <c r="CZ2" s="9"/>
+      <c r="DA2" s="9"/>
+      <c r="DB2" s="9"/>
+      <c r="DC2" s="9"/>
+      <c r="DD2" s="9"/>
+      <c r="DE2" s="9"/>
+      <c r="DF2" s="9"/>
+      <c r="DG2" s="9"/>
+      <c r="DH2" s="9"/>
+      <c r="DI2" s="9"/>
+      <c r="DJ2" s="9"/>
+      <c r="DK2" s="10"/>
+      <c r="DL2" s="46" t="s">
+        <v>309</v>
+      </c>
+      <c r="DM2" s="9"/>
+      <c r="DN2" s="9"/>
+      <c r="DO2" s="9"/>
+      <c r="DP2" s="9"/>
+      <c r="DQ2" s="9"/>
+      <c r="DR2" s="9"/>
+      <c r="DS2" s="10"/>
+      <c r="DT2" s="47" t="s">
+        <v>310</v>
+      </c>
+      <c r="DU2" s="46" t="s">
+        <v>311</v>
+      </c>
+      <c r="DV2" s="14"/>
+      <c r="DW2" s="14"/>
+      <c r="DX2" s="14"/>
+      <c r="DY2" s="15"/>
+      <c r="DZ2" s="47" t="s">
+        <v>312</v>
+      </c>
+      <c r="EA2" s="9"/>
+      <c r="EB2" s="9"/>
+      <c r="EC2" s="9"/>
+      <c r="ED2" s="9"/>
+      <c r="EE2" s="9"/>
+      <c r="EF2" s="9"/>
+      <c r="EG2" s="9"/>
+      <c r="EH2" s="9"/>
+      <c r="EI2" s="9"/>
+      <c r="EJ2" s="9"/>
+      <c r="EK2" s="9"/>
+      <c r="EL2" s="9"/>
+      <c r="EM2" s="9"/>
+      <c r="EN2" s="9"/>
+      <c r="EO2" s="9"/>
+      <c r="EP2" s="9"/>
+      <c r="EQ2" s="9"/>
+      <c r="ER2" s="9"/>
+      <c r="ES2" s="9"/>
+      <c r="ET2" s="9"/>
+      <c r="EU2" s="9"/>
+      <c r="EV2" s="9"/>
+      <c r="EW2" s="9"/>
+      <c r="EX2" s="10"/>
+      <c r="EY2" s="46" t="s">
+        <v>313</v>
+      </c>
+      <c r="EZ2" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="FA2" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="FB2" s="14"/>
+      <c r="FC2" s="14"/>
+      <c r="FD2" s="14"/>
+      <c r="FE2" s="14"/>
+      <c r="FF2" s="14"/>
+      <c r="FG2" s="14"/>
+      <c r="FH2" s="15"/>
+      <c r="FI2" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="FJ2" s="9"/>
+      <c r="FK2" s="9"/>
+      <c r="FL2" s="9"/>
+      <c r="FM2" s="9"/>
+      <c r="FN2" s="9"/>
+      <c r="FO2" s="9"/>
+      <c r="FP2" s="9"/>
+      <c r="FQ2" s="9"/>
+      <c r="FR2" s="9"/>
+      <c r="FS2" s="9"/>
+      <c r="FT2" s="9"/>
+      <c r="FU2" s="9"/>
+      <c r="FV2" s="9"/>
+      <c r="FW2" s="9"/>
+      <c r="FX2" s="9"/>
+      <c r="FY2" s="9"/>
+      <c r="FZ2" s="9"/>
+      <c r="GA2" s="9"/>
+      <c r="GB2" s="9"/>
+      <c r="GC2" s="10"/>
+      <c r="GD2" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="GE2" s="9"/>
+      <c r="GF2" s="9"/>
+      <c r="GG2" s="9"/>
+      <c r="GH2" s="9"/>
+      <c r="GI2" s="9"/>
+      <c r="GJ2" s="10"/>
+      <c r="GK2" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="GL2" s="14"/>
+      <c r="GM2" s="14"/>
+      <c r="GN2" s="14"/>
+      <c r="GO2" s="14"/>
+      <c r="GP2" s="15"/>
+      <c r="GQ2" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="GR2" s="14"/>
+      <c r="GS2" s="14"/>
+      <c r="GT2" s="14"/>
+      <c r="GU2" s="14"/>
+      <c r="GV2" s="14"/>
+      <c r="GW2" s="15"/>
+      <c r="GX2" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="GY2" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="GZ2" s="14"/>
+      <c r="HA2" s="14"/>
+      <c r="HB2" s="14"/>
+      <c r="HC2" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="HD2" s="9"/>
+      <c r="HE2" s="9"/>
+      <c r="HF2" s="9"/>
+      <c r="HG2" s="9"/>
+      <c r="HH2" s="9"/>
+      <c r="HI2" s="10"/>
+      <c r="HJ2" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="HK2" s="15"/>
+      <c r="HL2" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="HM2" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="HN2" s="9"/>
+      <c r="HO2" s="9"/>
+      <c r="HP2" s="9"/>
+      <c r="HQ2" s="9"/>
+      <c r="HR2" s="9"/>
+      <c r="HS2" s="9"/>
+      <c r="HT2" s="9"/>
+      <c r="HU2" s="9"/>
+      <c r="HV2" s="9"/>
+      <c r="HW2" s="9"/>
+      <c r="HX2" s="9"/>
+      <c r="HY2" s="9"/>
+      <c r="HZ2" s="9"/>
+      <c r="IA2" s="9"/>
+      <c r="IB2" s="9"/>
+      <c r="IC2" s="9"/>
+      <c r="ID2" s="9"/>
+      <c r="IE2" s="9"/>
+      <c r="IF2" s="9"/>
+      <c r="IG2" s="9"/>
+      <c r="IH2" s="9"/>
+      <c r="II2" s="10"/>
+      <c r="IJ2" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="IK2" s="9"/>
+      <c r="IL2" s="9"/>
+      <c r="IM2" s="9"/>
+      <c r="IN2" s="9"/>
+      <c r="IO2" s="9"/>
+      <c r="IP2" s="9"/>
+      <c r="IQ2" s="9"/>
+      <c r="IR2" s="9"/>
+      <c r="IS2" s="9"/>
+      <c r="IT2" s="9"/>
+      <c r="IU2" s="9"/>
+      <c r="IV2" s="9"/>
+      <c r="IW2" s="9"/>
+      <c r="IX2" s="10"/>
+      <c r="IY2" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="IZ2" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="JA2" s="15"/>
+      <c r="JB2" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="JC2" s="15"/>
+      <c r="JD2" s="22"/>
+    </row>
+    <row r="3" spans="1:264" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="22"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="24"/>
+      <c r="S3" s="24"/>
+      <c r="T3" s="24"/>
+      <c r="U3" s="24"/>
+      <c r="V3" s="24"/>
+      <c r="W3" s="24"/>
+      <c r="X3" s="25"/>
+      <c r="Y3" s="21" t="s">
+        <v>315</v>
+      </c>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="10"/>
+      <c r="AE3" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="AF3" s="9"/>
+      <c r="AG3" s="9"/>
+      <c r="AH3" s="9"/>
+      <c r="AI3" s="9"/>
+      <c r="AJ3" s="10"/>
+      <c r="AK3" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="AL3" s="9"/>
+      <c r="AM3" s="9"/>
+      <c r="AN3" s="9"/>
+      <c r="AO3" s="9"/>
+      <c r="AP3" s="9"/>
+      <c r="AQ3" s="9"/>
+      <c r="AR3" s="10"/>
+      <c r="AS3" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="AT3" s="9"/>
+      <c r="AU3" s="9"/>
+      <c r="AV3" s="9"/>
+      <c r="AW3" s="9"/>
+      <c r="AX3" s="9"/>
+      <c r="AY3" s="9"/>
+      <c r="AZ3" s="10"/>
+      <c r="BA3" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="BB3" s="9"/>
+      <c r="BC3" s="9"/>
+      <c r="BD3" s="9"/>
+      <c r="BE3" s="10"/>
+      <c r="BF3" s="20" t="s">
+        <v>320</v>
+      </c>
+      <c r="BG3" s="10"/>
+      <c r="BH3" s="21" t="s">
+        <v>321</v>
+      </c>
+      <c r="BI3" s="9"/>
+      <c r="BJ3" s="9"/>
+      <c r="BK3" s="9"/>
+      <c r="BL3" s="10"/>
+      <c r="BM3" s="20" t="s">
+        <v>322</v>
+      </c>
+      <c r="BN3" s="9"/>
+      <c r="BO3" s="9"/>
+      <c r="BP3" s="9"/>
+      <c r="BQ3" s="10"/>
+      <c r="BR3" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="BS3" s="9"/>
+      <c r="BT3" s="9"/>
+      <c r="BU3" s="9"/>
+      <c r="BV3" s="9"/>
+      <c r="BW3" s="9"/>
+      <c r="BX3" s="9"/>
+      <c r="BY3" s="9"/>
+      <c r="BZ3" s="10"/>
+      <c r="CA3" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="CB3" s="9"/>
+      <c r="CC3" s="9"/>
+      <c r="CD3" s="9"/>
+      <c r="CE3" s="9"/>
+      <c r="CF3" s="10"/>
+      <c r="CG3" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="CH3" s="9"/>
+      <c r="CI3" s="9"/>
+      <c r="CJ3" s="9"/>
+      <c r="CK3" s="10"/>
+      <c r="CL3" s="48" t="s">
+        <v>326</v>
+      </c>
+      <c r="CM3" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="CN3" s="9"/>
+      <c r="CO3" s="10"/>
+      <c r="CP3" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="CQ3" s="9"/>
+      <c r="CR3" s="9"/>
+      <c r="CS3" s="9"/>
+      <c r="CT3" s="9"/>
+      <c r="CU3" s="10"/>
+      <c r="CV3" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="CW3" s="9"/>
+      <c r="CX3" s="9"/>
+      <c r="CY3" s="9"/>
+      <c r="CZ3" s="9"/>
+      <c r="DA3" s="10"/>
+      <c r="DB3" s="20" t="s">
+        <v>330</v>
+      </c>
+      <c r="DC3" s="9"/>
+      <c r="DD3" s="9"/>
+      <c r="DE3" s="9"/>
+      <c r="DF3" s="9"/>
+      <c r="DG3" s="10"/>
+      <c r="DH3" s="21" t="s">
+        <v>331</v>
+      </c>
+      <c r="DI3" s="9"/>
+      <c r="DJ3" s="9"/>
+      <c r="DK3" s="10"/>
+      <c r="DL3" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="DM3" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="DN3" s="9"/>
+      <c r="DO3" s="9"/>
+      <c r="DP3" s="10"/>
+      <c r="DQ3" s="20" t="s">
+        <v>334</v>
+      </c>
+      <c r="DR3" s="9"/>
+      <c r="DS3" s="10"/>
+      <c r="DT3" s="28"/>
+      <c r="DU3" s="23"/>
+      <c r="DV3" s="24"/>
+      <c r="DW3" s="24"/>
+      <c r="DX3" s="24"/>
+      <c r="DY3" s="25"/>
+      <c r="DZ3" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="EA3" s="9"/>
+      <c r="EB3" s="9"/>
+      <c r="EC3" s="9"/>
+      <c r="ED3" s="9"/>
+      <c r="EE3" s="9"/>
+      <c r="EF3" s="9"/>
+      <c r="EG3" s="10"/>
+      <c r="EH3" s="21" t="s">
+        <v>336</v>
+      </c>
+      <c r="EI3" s="9"/>
+      <c r="EJ3" s="9"/>
+      <c r="EK3" s="9"/>
+      <c r="EL3" s="9"/>
+      <c r="EM3" s="10"/>
+      <c r="EN3" s="20" t="s">
+        <v>337</v>
+      </c>
+      <c r="EO3" s="10"/>
+      <c r="EP3" s="34" t="s">
+        <v>338</v>
+      </c>
+      <c r="EQ3" s="20" t="s">
+        <v>339</v>
+      </c>
+      <c r="ER3" s="9"/>
+      <c r="ES3" s="9"/>
+      <c r="ET3" s="9"/>
+      <c r="EU3" s="9"/>
+      <c r="EV3" s="9"/>
+      <c r="EW3" s="9"/>
+      <c r="EX3" s="10"/>
+      <c r="EY3" s="28"/>
+      <c r="EZ3" s="28"/>
+      <c r="FA3" s="23"/>
+      <c r="FB3" s="24"/>
+      <c r="FC3" s="24"/>
+      <c r="FD3" s="24"/>
+      <c r="FE3" s="24"/>
+      <c r="FF3" s="24"/>
+      <c r="FG3" s="24"/>
+      <c r="FH3" s="25"/>
+      <c r="FI3" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="FJ3" s="9"/>
+      <c r="FK3" s="10"/>
+      <c r="FL3" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="FM3" s="9"/>
+      <c r="FN3" s="9"/>
+      <c r="FO3" s="9"/>
+      <c r="FP3" s="9"/>
+      <c r="FQ3" s="10"/>
+      <c r="FR3" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="FS3" s="9"/>
+      <c r="FT3" s="9"/>
+      <c r="FU3" s="9"/>
+      <c r="FV3" s="9"/>
+      <c r="FW3" s="10"/>
+      <c r="FX3" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="FY3" s="9"/>
+      <c r="FZ3" s="9"/>
+      <c r="GA3" s="9"/>
+      <c r="GB3" s="9"/>
+      <c r="GC3" s="10"/>
+      <c r="GD3" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="GE3" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="GF3" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="GG3" s="10"/>
+      <c r="GH3" s="26"/>
+      <c r="GI3" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="GJ3" s="10"/>
+      <c r="GK3" s="23"/>
+      <c r="GL3" s="24"/>
+      <c r="GM3" s="24"/>
+      <c r="GN3" s="24"/>
+      <c r="GO3" s="24"/>
+      <c r="GP3" s="25"/>
+      <c r="GQ3" s="23"/>
+      <c r="GR3" s="24"/>
+      <c r="GS3" s="24"/>
+      <c r="GT3" s="24"/>
+      <c r="GU3" s="24"/>
+      <c r="GV3" s="24"/>
+      <c r="GW3" s="25"/>
+      <c r="GX3" s="28"/>
+      <c r="GY3" s="23"/>
+      <c r="GZ3" s="24"/>
+      <c r="HA3" s="24"/>
+      <c r="HB3" s="24"/>
+      <c r="HC3" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="HD3" s="10"/>
+      <c r="HE3" s="30"/>
+      <c r="HF3" s="31"/>
+      <c r="HG3" s="30"/>
+      <c r="HH3" s="31"/>
+      <c r="HI3" s="30"/>
+      <c r="HJ3" s="23"/>
+      <c r="HK3" s="25"/>
+      <c r="HL3" s="28"/>
+      <c r="HM3" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="HN3" s="9"/>
+      <c r="HO3" s="9"/>
+      <c r="HP3" s="9"/>
+      <c r="HQ3" s="9"/>
+      <c r="HR3" s="10"/>
+      <c r="HS3" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="HT3" s="9"/>
+      <c r="HU3" s="9"/>
+      <c r="HV3" s="9"/>
+      <c r="HW3" s="9"/>
+      <c r="HX3" s="10"/>
+      <c r="HY3" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="HZ3" s="10"/>
+      <c r="IA3" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="IB3" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="IC3" s="9"/>
+      <c r="ID3" s="9"/>
+      <c r="IE3" s="9"/>
+      <c r="IF3" s="9"/>
+      <c r="IG3" s="9"/>
+      <c r="IH3" s="9"/>
+      <c r="II3" s="10"/>
+      <c r="IJ3" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="IK3" s="9"/>
+      <c r="IL3" s="9"/>
+      <c r="IM3" s="9"/>
+      <c r="IN3" s="9"/>
+      <c r="IO3" s="9"/>
+      <c r="IP3" s="9"/>
+      <c r="IQ3" s="9"/>
+      <c r="IR3" s="10"/>
+      <c r="IS3" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="IT3" s="9"/>
+      <c r="IU3" s="9"/>
+      <c r="IV3" s="9"/>
+      <c r="IW3" s="9"/>
+      <c r="IX3" s="10"/>
+      <c r="IY3" s="28"/>
+      <c r="IZ3" s="23"/>
+      <c r="JA3" s="25"/>
+      <c r="JB3" s="23"/>
+      <c r="JC3" s="25"/>
+      <c r="JD3" s="28"/>
+    </row>
+    <row r="4" spans="1:264" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="27" t="s">
+        <v>340</v>
+      </c>
+      <c r="R4" s="27" t="s">
+        <v>341</v>
+      </c>
+      <c r="S4" s="27" t="s">
+        <v>342</v>
+      </c>
+      <c r="T4" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="U4" s="27" t="s">
+        <v>344</v>
+      </c>
+      <c r="V4" s="27" t="s">
+        <v>345</v>
+      </c>
+      <c r="W4" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="X4" s="27" t="s">
+        <v>347</v>
+      </c>
+      <c r="Y4" s="34" t="s">
+        <v>348</v>
+      </c>
+      <c r="Z4" s="34" t="s">
+        <v>349</v>
+      </c>
+      <c r="AA4" s="34" t="s">
+        <v>350</v>
+      </c>
+      <c r="AB4" s="34" t="s">
+        <v>351</v>
+      </c>
+      <c r="AC4" s="34" t="s">
+        <v>352</v>
+      </c>
+      <c r="AD4" s="34" t="s">
+        <v>353</v>
+      </c>
+      <c r="AE4" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="AF4" s="49" t="s">
+        <v>355</v>
+      </c>
+      <c r="AG4" s="33" t="s">
+        <v>356</v>
+      </c>
+      <c r="AH4" s="33" t="s">
+        <v>357</v>
+      </c>
+      <c r="AI4" s="49" t="s">
+        <v>358</v>
+      </c>
+      <c r="AJ4" s="33" t="s">
+        <v>359</v>
+      </c>
+      <c r="AK4" s="34" t="s">
+        <v>360</v>
+      </c>
+      <c r="AL4" s="34" t="s">
+        <v>361</v>
+      </c>
+      <c r="AM4" s="34" t="s">
+        <v>362</v>
+      </c>
+      <c r="AN4" s="34" t="s">
+        <v>363</v>
+      </c>
+      <c r="AO4" s="34" t="s">
+        <v>364</v>
+      </c>
+      <c r="AP4" s="34" t="s">
+        <v>365</v>
+      </c>
+      <c r="AQ4" s="34" t="s">
+        <v>366</v>
+      </c>
+      <c r="AR4" s="34" t="s">
+        <v>367</v>
+      </c>
+      <c r="AS4" s="33" t="s">
+        <v>368</v>
+      </c>
+      <c r="AT4" s="33" t="s">
+        <v>369</v>
+      </c>
+      <c r="AU4" s="33" t="s">
+        <v>370</v>
+      </c>
+      <c r="AV4" s="33" t="s">
+        <v>371</v>
+      </c>
+      <c r="AW4" s="33" t="s">
+        <v>372</v>
+      </c>
+      <c r="AX4" s="33" t="s">
+        <v>373</v>
+      </c>
+      <c r="AY4" s="33" t="s">
+        <v>374</v>
+      </c>
+      <c r="AZ4" s="33" t="s">
+        <v>375</v>
+      </c>
+      <c r="BA4" s="34" t="s">
+        <v>376</v>
+      </c>
+      <c r="BB4" s="34" t="s">
+        <v>377</v>
+      </c>
+      <c r="BC4" s="34" t="s">
+        <v>378</v>
+      </c>
+      <c r="BD4" s="34" t="s">
+        <v>379</v>
+      </c>
+      <c r="BE4" s="34" t="s">
+        <v>380</v>
+      </c>
+      <c r="BF4" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="BG4" s="33" t="s">
+        <v>382</v>
+      </c>
+      <c r="BH4" s="34" t="s">
+        <v>383</v>
+      </c>
+      <c r="BI4" s="34" t="s">
+        <v>384</v>
+      </c>
+      <c r="BJ4" s="34" t="s">
+        <v>385</v>
+      </c>
+      <c r="BK4" s="34" t="s">
+        <v>386</v>
+      </c>
+      <c r="BL4" s="34" t="s">
+        <v>387</v>
+      </c>
+      <c r="BM4" s="33" t="s">
+        <v>388</v>
+      </c>
+      <c r="BN4" s="33" t="s">
+        <v>389</v>
+      </c>
+      <c r="BO4" s="33" t="s">
+        <v>390</v>
+      </c>
+      <c r="BP4" s="33" t="s">
+        <v>391</v>
+      </c>
+      <c r="BQ4" s="33" t="s">
+        <v>392</v>
+      </c>
+      <c r="BR4" s="34" t="s">
+        <v>393</v>
+      </c>
+      <c r="BS4" s="34" t="s">
+        <v>394</v>
+      </c>
+      <c r="BT4" s="34" t="s">
+        <v>395</v>
+      </c>
+      <c r="BU4" s="34" t="s">
+        <v>396</v>
+      </c>
+      <c r="BV4" s="34" t="s">
+        <v>397</v>
+      </c>
+      <c r="BW4" s="34" t="s">
+        <v>398</v>
+      </c>
+      <c r="BX4" s="34" t="s">
+        <v>399</v>
+      </c>
+      <c r="BY4" s="34" t="s">
+        <v>400</v>
+      </c>
+      <c r="BZ4" s="34" t="s">
+        <v>401</v>
+      </c>
+      <c r="CA4" s="33" t="s">
+        <v>402</v>
+      </c>
+      <c r="CB4" s="33" t="s">
+        <v>403</v>
+      </c>
+      <c r="CC4" s="33" t="s">
+        <v>404</v>
+      </c>
+      <c r="CD4" s="33" t="s">
+        <v>405</v>
+      </c>
+      <c r="CE4" s="33" t="s">
+        <v>406</v>
+      </c>
+      <c r="CF4" s="33" t="s">
+        <v>407</v>
+      </c>
+      <c r="CG4" s="34" t="s">
+        <v>408</v>
+      </c>
+      <c r="CH4" s="34" t="s">
+        <v>409</v>
+      </c>
+      <c r="CI4" s="34" t="s">
+        <v>410</v>
+      </c>
+      <c r="CJ4" s="34" t="s">
+        <v>411</v>
+      </c>
+      <c r="CK4" s="34" t="s">
+        <v>412</v>
+      </c>
+      <c r="CL4" s="33" t="s">
+        <v>413</v>
+      </c>
+      <c r="CM4" s="34" t="s">
+        <v>414</v>
+      </c>
+      <c r="CN4" s="34" t="s">
+        <v>415</v>
+      </c>
+      <c r="CO4" s="34" t="s">
+        <v>416</v>
+      </c>
+      <c r="CP4" s="33" t="s">
+        <v>417</v>
+      </c>
+      <c r="CQ4" s="33" t="s">
+        <v>418</v>
+      </c>
+      <c r="CR4" s="33" t="s">
+        <v>419</v>
+      </c>
+      <c r="CS4" s="33" t="s">
+        <v>420</v>
+      </c>
+      <c r="CT4" s="33" t="s">
+        <v>421</v>
+      </c>
+      <c r="CU4" s="33" t="s">
+        <v>422</v>
+      </c>
+      <c r="CV4" s="34" t="s">
+        <v>423</v>
+      </c>
+      <c r="CW4" s="34" t="s">
+        <v>424</v>
+      </c>
+      <c r="CX4" s="34" t="s">
+        <v>425</v>
+      </c>
+      <c r="CY4" s="34" t="s">
+        <v>426</v>
+      </c>
+      <c r="CZ4" s="34" t="s">
+        <v>427</v>
+      </c>
+      <c r="DA4" s="34" t="s">
+        <v>428</v>
+      </c>
+      <c r="DB4" s="33" t="s">
+        <v>429</v>
+      </c>
+      <c r="DC4" s="33" t="s">
+        <v>430</v>
+      </c>
+      <c r="DD4" s="33" t="s">
+        <v>431</v>
+      </c>
+      <c r="DE4" s="33" t="s">
+        <v>432</v>
+      </c>
+      <c r="DF4" s="33" t="s">
+        <v>433</v>
+      </c>
+      <c r="DG4" s="33" t="s">
+        <v>434</v>
+      </c>
+      <c r="DH4" s="34" t="s">
+        <v>435</v>
+      </c>
+      <c r="DI4" s="34" t="s">
+        <v>436</v>
+      </c>
+      <c r="DJ4" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="DK4" s="34" t="s">
+        <v>438</v>
+      </c>
+      <c r="DL4" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="DM4" s="34" t="s">
+        <v>440</v>
+      </c>
+      <c r="DN4" s="34" t="s">
+        <v>441</v>
+      </c>
+      <c r="DO4" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="DP4" s="34" t="s">
+        <v>443</v>
+      </c>
+      <c r="DQ4" s="33" t="s">
+        <v>444</v>
+      </c>
+      <c r="DR4" s="33" t="s">
+        <v>445</v>
+      </c>
+      <c r="DS4" s="33" t="s">
+        <v>446</v>
+      </c>
+      <c r="DT4" s="34" t="s">
+        <v>447</v>
+      </c>
+      <c r="DU4" s="33" t="s">
+        <v>448</v>
+      </c>
+      <c r="DV4" s="33" t="s">
+        <v>449</v>
+      </c>
+      <c r="DW4" s="34" t="s">
+        <v>450</v>
+      </c>
+      <c r="DX4" s="34" t="s">
+        <v>451</v>
+      </c>
+      <c r="DY4" s="34" t="s">
+        <v>452</v>
+      </c>
+      <c r="DZ4" s="33" t="s">
+        <v>453</v>
+      </c>
+      <c r="EA4" s="33" t="s">
+        <v>454</v>
+      </c>
+      <c r="EB4" s="33" t="s">
+        <v>455</v>
+      </c>
+      <c r="EC4" s="33" t="s">
+        <v>456</v>
+      </c>
+      <c r="ED4" s="33" t="s">
+        <v>457</v>
+      </c>
+      <c r="EE4" s="33" t="s">
+        <v>458</v>
+      </c>
+      <c r="EF4" s="33" t="s">
+        <v>459</v>
+      </c>
+      <c r="EG4" s="33" t="s">
+        <v>460</v>
+      </c>
+      <c r="EH4" s="34" t="s">
+        <v>461</v>
+      </c>
+      <c r="EI4" s="34" t="s">
+        <v>462</v>
+      </c>
+      <c r="EJ4" s="34" t="s">
+        <v>463</v>
+      </c>
+      <c r="EK4" s="34" t="s">
+        <v>464</v>
+      </c>
+      <c r="EL4" s="34" t="s">
+        <v>465</v>
+      </c>
+      <c r="EM4" s="34" t="s">
+        <v>466</v>
+      </c>
+      <c r="EN4" s="33" t="s">
+        <v>467</v>
+      </c>
+      <c r="EO4" s="33" t="s">
+        <v>468</v>
+      </c>
+      <c r="EP4" s="34" t="s">
+        <v>469</v>
+      </c>
+      <c r="EQ4" s="33" t="s">
+        <v>470</v>
+      </c>
+      <c r="ER4" s="33" t="s">
+        <v>471</v>
+      </c>
+      <c r="ES4" s="33" t="s">
+        <v>472</v>
+      </c>
+      <c r="ET4" s="33" t="s">
+        <v>473</v>
+      </c>
+      <c r="EU4" s="33" t="s">
+        <v>474</v>
+      </c>
+      <c r="EV4" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="EW4" s="33" t="s">
+        <v>476</v>
+      </c>
+      <c r="EX4" s="33" t="s">
+        <v>477</v>
+      </c>
+      <c r="EY4" s="34" t="s">
+        <v>478</v>
+      </c>
+      <c r="EZ4" s="33" t="s">
+        <v>479</v>
+      </c>
+      <c r="FA4" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="FB4" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="FC4" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="FD4" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="FE4" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="FF4" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="FG4" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="FH4" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="FI4" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="FJ4" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="FK4" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="FL4" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="FM4" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="FN4" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="FO4" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="FP4" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="FQ4" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="FR4" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="FS4" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="FT4" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="FU4" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="FV4" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="FW4" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="FX4" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="FY4" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="FZ4" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="GA4" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="GB4" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="GC4" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="GD4" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="GE4" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="GF4" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="GG4" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="GH4" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="GI4" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="GJ4" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="GK4" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="GL4" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="GM4" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="GN4" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="GO4" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="GP4" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="GQ4" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="GR4" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="GS4" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="GT4" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="GU4" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="GV4" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="GW4" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="GX4" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="GY4" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="GZ4" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="HA4" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="HB4" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="HC4" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="HD4" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="HE4" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="HF4" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="HG4" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="HH4" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="HI4" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="HJ4" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="HK4" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="HL4" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="HM4" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="HN4" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="HO4" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="HP4" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="HQ4" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="HR4" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="HS4" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="HT4" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="HU4" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="HV4" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="HW4" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="HX4" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="HY4" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="HZ4" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="IA4" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="IB4" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="IC4" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="ID4" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="IE4" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="IF4" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="IG4" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="IH4" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="II4" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="IJ4" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="IK4" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="IL4" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="IM4" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="IN4" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="IO4" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="IP4" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="IQ4" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="IR4" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="IS4" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="IT4" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="IU4" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="IV4" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="IW4" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="IX4" s="27" t="s">
+        <v>599</v>
+      </c>
+      <c r="IY4" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="IZ4" s="33" t="s">
+        <v>159</v>
+      </c>
+      <c r="JA4" s="33" t="s">
+        <v>160</v>
+      </c>
+      <c r="JB4" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="JC4" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="JD4" s="35"/>
+    </row>
+    <row r="5" spans="1:264" ht="345" x14ac:dyDescent="0.25">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="50" t="s">
+        <v>480</v>
+      </c>
+      <c r="Q5" s="36" t="s">
+        <v>481</v>
+      </c>
+      <c r="R5" s="36" t="s">
+        <v>482</v>
+      </c>
+      <c r="S5" s="36" t="s">
+        <v>483</v>
+      </c>
+      <c r="T5" s="36" t="s">
+        <v>484</v>
+      </c>
+      <c r="U5" s="36" t="s">
+        <v>485</v>
+      </c>
+      <c r="V5" s="36" t="s">
+        <v>486</v>
+      </c>
+      <c r="W5" s="36" t="s">
+        <v>487</v>
+      </c>
+      <c r="X5" s="36" t="s">
+        <v>488</v>
+      </c>
+      <c r="Y5" s="40" t="s">
+        <v>489</v>
+      </c>
+      <c r="Z5" s="40" t="s">
+        <v>490</v>
+      </c>
+      <c r="AA5" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="AB5" s="40" t="s">
+        <v>492</v>
+      </c>
+      <c r="AC5" s="40" t="s">
+        <v>493</v>
+      </c>
+      <c r="AD5" s="40" t="s">
+        <v>494</v>
+      </c>
+      <c r="AE5" s="39" t="s">
+        <v>495</v>
+      </c>
+      <c r="AF5" s="51" t="s">
+        <v>496</v>
+      </c>
+      <c r="AG5" s="39" t="s">
+        <v>497</v>
+      </c>
+      <c r="AH5" s="39" t="s">
+        <v>498</v>
+      </c>
+      <c r="AI5" s="51" t="s">
+        <v>499</v>
+      </c>
+      <c r="AJ5" s="39" t="s">
+        <v>500</v>
+      </c>
+      <c r="AK5" s="40" t="s">
+        <v>501</v>
+      </c>
+      <c r="AL5" s="40" t="s">
+        <v>502</v>
+      </c>
+      <c r="AM5" s="40" t="s">
+        <v>503</v>
+      </c>
+      <c r="AN5" s="40" t="s">
+        <v>504</v>
+      </c>
+      <c r="AO5" s="40" t="s">
+        <v>505</v>
+      </c>
+      <c r="AP5" s="40" t="s">
+        <v>506</v>
+      </c>
+      <c r="AQ5" s="40" t="s">
+        <v>507</v>
+      </c>
+      <c r="AR5" s="40" t="s">
+        <v>508</v>
+      </c>
+      <c r="AS5" s="39" t="s">
+        <v>509</v>
+      </c>
+      <c r="AT5" s="39" t="s">
+        <v>510</v>
+      </c>
+      <c r="AU5" s="39" t="s">
+        <v>511</v>
+      </c>
+      <c r="AV5" s="39" t="s">
+        <v>512</v>
+      </c>
+      <c r="AW5" s="39" t="s">
+        <v>513</v>
+      </c>
+      <c r="AX5" s="39" t="s">
+        <v>514</v>
+      </c>
+      <c r="AY5" s="39" t="s">
+        <v>515</v>
+      </c>
+      <c r="AZ5" s="39" t="s">
+        <v>516</v>
+      </c>
+      <c r="BA5" s="40" t="s">
+        <v>517</v>
+      </c>
+      <c r="BB5" s="40" t="s">
+        <v>518</v>
+      </c>
+      <c r="BC5" s="40" t="s">
+        <v>519</v>
+      </c>
+      <c r="BD5" s="40" t="s">
+        <v>520</v>
+      </c>
+      <c r="BE5" s="40" t="s">
+        <v>521</v>
+      </c>
+      <c r="BF5" s="39" t="s">
+        <v>522</v>
+      </c>
+      <c r="BG5" s="39" t="s">
+        <v>523</v>
+      </c>
+      <c r="BH5" s="40" t="s">
+        <v>524</v>
+      </c>
+      <c r="BI5" s="40" t="s">
+        <v>525</v>
+      </c>
+      <c r="BJ5" s="40" t="s">
+        <v>526</v>
+      </c>
+      <c r="BK5" s="40" t="s">
+        <v>527</v>
+      </c>
+      <c r="BL5" s="40" t="s">
+        <v>528</v>
+      </c>
+      <c r="BM5" s="39" t="s">
+        <v>529</v>
+      </c>
+      <c r="BN5" s="39" t="s">
+        <v>530</v>
+      </c>
+      <c r="BO5" s="39" t="s">
+        <v>531</v>
+      </c>
+      <c r="BP5" s="39" t="s">
+        <v>532</v>
+      </c>
+      <c r="BQ5" s="39" t="s">
+        <v>533</v>
+      </c>
+      <c r="BR5" s="40" t="s">
+        <v>250</v>
+      </c>
+      <c r="BS5" s="40" t="s">
+        <v>251</v>
+      </c>
+      <c r="BT5" s="40" t="s">
+        <v>252</v>
+      </c>
+      <c r="BU5" s="40" t="s">
+        <v>253</v>
+      </c>
+      <c r="BV5" s="40" t="s">
+        <v>254</v>
+      </c>
+      <c r="BW5" s="40" t="s">
+        <v>255</v>
+      </c>
+      <c r="BX5" s="40" t="s">
+        <v>256</v>
+      </c>
+      <c r="BY5" s="40" t="s">
+        <v>257</v>
+      </c>
+      <c r="BZ5" s="40" t="s">
+        <v>258</v>
+      </c>
+      <c r="CA5" s="39" t="s">
+        <v>259</v>
+      </c>
+      <c r="CB5" s="39" t="s">
+        <v>260</v>
+      </c>
+      <c r="CC5" s="39" t="s">
+        <v>534</v>
+      </c>
+      <c r="CD5" s="39" t="s">
+        <v>262</v>
+      </c>
+      <c r="CE5" s="39" t="s">
+        <v>263</v>
+      </c>
+      <c r="CF5" s="39" t="s">
+        <v>535</v>
+      </c>
+      <c r="CG5" s="40" t="s">
+        <v>536</v>
+      </c>
+      <c r="CH5" s="40" t="s">
+        <v>537</v>
+      </c>
+      <c r="CI5" s="40" t="s">
+        <v>538</v>
+      </c>
+      <c r="CJ5" s="40" t="s">
+        <v>539</v>
+      </c>
+      <c r="CK5" s="40" t="s">
+        <v>540</v>
+      </c>
+      <c r="CL5" s="39" t="s">
+        <v>541</v>
+      </c>
+      <c r="CM5" s="40" t="s">
+        <v>171</v>
+      </c>
+      <c r="CN5" s="40" t="s">
+        <v>172</v>
+      </c>
+      <c r="CO5" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="CP5" s="39" t="s">
+        <v>174</v>
+      </c>
+      <c r="CQ5" s="39" t="s">
+        <v>175</v>
+      </c>
+      <c r="CR5" s="39" t="s">
+        <v>176</v>
+      </c>
+      <c r="CS5" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="CT5" s="39" t="s">
+        <v>178</v>
+      </c>
+      <c r="CU5" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="CV5" s="40" t="s">
+        <v>180</v>
+      </c>
+      <c r="CW5" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="CX5" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="CY5" s="40" t="s">
+        <v>183</v>
+      </c>
+      <c r="CZ5" s="40" t="s">
+        <v>184</v>
+      </c>
+      <c r="DA5" s="40" t="s">
+        <v>185</v>
+      </c>
+      <c r="DB5" s="39" t="s">
+        <v>186</v>
+      </c>
+      <c r="DC5" s="39" t="s">
+        <v>187</v>
+      </c>
+      <c r="DD5" s="39" t="s">
+        <v>188</v>
+      </c>
+      <c r="DE5" s="39" t="s">
+        <v>189</v>
+      </c>
+      <c r="DF5" s="39" t="s">
+        <v>190</v>
+      </c>
+      <c r="DG5" s="39" t="s">
+        <v>191</v>
+      </c>
+      <c r="DH5" s="40" t="s">
+        <v>542</v>
+      </c>
+      <c r="DI5" s="40" t="s">
+        <v>543</v>
+      </c>
+      <c r="DJ5" s="40" t="s">
+        <v>544</v>
+      </c>
+      <c r="DK5" s="40" t="s">
+        <v>545</v>
+      </c>
+      <c r="DL5" s="39" t="s">
+        <v>546</v>
+      </c>
+      <c r="DM5" s="40" t="s">
+        <v>547</v>
+      </c>
+      <c r="DN5" s="40" t="s">
+        <v>548</v>
+      </c>
+      <c r="DO5" s="40" t="s">
+        <v>549</v>
+      </c>
+      <c r="DP5" s="40" t="s">
+        <v>550</v>
+      </c>
+      <c r="DQ5" s="39" t="s">
+        <v>551</v>
+      </c>
+      <c r="DR5" s="39" t="s">
+        <v>552</v>
+      </c>
+      <c r="DS5" s="39" t="s">
+        <v>553</v>
+      </c>
+      <c r="DT5" s="40" t="s">
+        <v>554</v>
+      </c>
+      <c r="DU5" s="39" t="s">
+        <v>555</v>
+      </c>
+      <c r="DV5" s="39" t="s">
+        <v>556</v>
+      </c>
+      <c r="DW5" s="40" t="s">
+        <v>557</v>
+      </c>
+      <c r="DX5" s="40" t="s">
+        <v>558</v>
+      </c>
+      <c r="DY5" s="40" t="s">
+        <v>559</v>
+      </c>
+      <c r="DZ5" s="39" t="s">
+        <v>560</v>
+      </c>
+      <c r="EA5" s="39" t="s">
+        <v>561</v>
+      </c>
+      <c r="EB5" s="39" t="s">
+        <v>562</v>
+      </c>
+      <c r="EC5" s="39" t="s">
+        <v>563</v>
+      </c>
+      <c r="ED5" s="39" t="s">
+        <v>564</v>
+      </c>
+      <c r="EE5" s="39" t="s">
+        <v>565</v>
+      </c>
+      <c r="EF5" s="39" t="s">
+        <v>566</v>
+      </c>
+      <c r="EG5" s="39" t="s">
+        <v>567</v>
+      </c>
+      <c r="EH5" s="40" t="s">
+        <v>568</v>
+      </c>
+      <c r="EI5" s="40" t="s">
+        <v>569</v>
+      </c>
+      <c r="EJ5" s="40" t="s">
+        <v>570</v>
+      </c>
+      <c r="EK5" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="EL5" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="EM5" s="40" t="s">
+        <v>573</v>
+      </c>
+      <c r="EN5" s="39" t="s">
+        <v>574</v>
+      </c>
+      <c r="EO5" s="39" t="s">
+        <v>575</v>
+      </c>
+      <c r="EP5" s="40" t="s">
+        <v>576</v>
+      </c>
+      <c r="EQ5" s="39" t="s">
+        <v>577</v>
+      </c>
+      <c r="ER5" s="39" t="s">
+        <v>578</v>
+      </c>
+      <c r="ES5" s="39" t="s">
+        <v>579</v>
+      </c>
+      <c r="ET5" s="39" t="s">
+        <v>580</v>
+      </c>
+      <c r="EU5" s="39" t="s">
+        <v>581</v>
+      </c>
+      <c r="EV5" s="39" t="s">
+        <v>582</v>
+      </c>
+      <c r="EW5" s="39" t="s">
+        <v>583</v>
+      </c>
+      <c r="EX5" s="39" t="s">
+        <v>584</v>
+      </c>
+      <c r="EY5" s="40" t="s">
+        <v>585</v>
+      </c>
+      <c r="EZ5" s="39" t="s">
+        <v>586</v>
+      </c>
+      <c r="FA5" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="FB5" s="36" t="s">
+        <v>164</v>
+      </c>
+      <c r="FC5" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="FD5" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="FE5" s="36" t="s">
+        <v>167</v>
+      </c>
+      <c r="FF5" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="FG5" s="36" t="s">
+        <v>169</v>
+      </c>
+      <c r="FH5" s="36" t="s">
+        <v>170</v>
+      </c>
+      <c r="FI5" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="FJ5" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="FK5" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="FL5" s="36" t="s">
+        <v>174</v>
+      </c>
+      <c r="FM5" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="FN5" s="36" t="s">
+        <v>176</v>
+      </c>
+      <c r="FO5" s="36" t="s">
+        <v>177</v>
+      </c>
+      <c r="FP5" s="36" t="s">
+        <v>178</v>
+      </c>
+      <c r="FQ5" s="36" t="s">
+        <v>179</v>
+      </c>
+      <c r="FR5" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="FS5" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="FT5" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="FU5" s="37" t="s">
+        <v>183</v>
+      </c>
+      <c r="FV5" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="FW5" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="FX5" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="FY5" s="36" t="s">
+        <v>187</v>
+      </c>
+      <c r="FZ5" s="36" t="s">
+        <v>188</v>
+      </c>
+      <c r="GA5" s="36" t="s">
+        <v>189</v>
+      </c>
+      <c r="GB5" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="GC5" s="36" t="s">
+        <v>191</v>
+      </c>
+      <c r="GD5" s="37" t="s">
+        <v>192</v>
+      </c>
+      <c r="GE5" s="36" t="s">
+        <v>193</v>
+      </c>
+      <c r="GF5" s="37" t="s">
+        <v>194</v>
+      </c>
+      <c r="GG5" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="GH5" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="GI5" s="36" t="s">
+        <v>197</v>
+      </c>
+      <c r="GJ5" s="36" t="s">
+        <v>198</v>
+      </c>
+      <c r="GK5" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="GL5" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="GM5" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="GN5" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="GO5" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="GP5" s="37" t="s">
+        <v>204</v>
+      </c>
+      <c r="GQ5" s="36" t="s">
+        <v>205</v>
+      </c>
+      <c r="GR5" s="36" t="s">
+        <v>206</v>
+      </c>
+      <c r="GS5" s="36" t="s">
+        <v>207</v>
+      </c>
+      <c r="GT5" s="36" t="s">
+        <v>208</v>
+      </c>
+      <c r="GU5" s="36" t="s">
+        <v>209</v>
+      </c>
+      <c r="GV5" s="36" t="s">
+        <v>210</v>
+      </c>
+      <c r="GW5" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="GX5" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="GY5" s="36" t="s">
+        <v>213</v>
+      </c>
+      <c r="GZ5" s="36" t="s">
+        <v>214</v>
+      </c>
+      <c r="HA5" s="36" t="s">
+        <v>215</v>
+      </c>
+      <c r="HB5" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="HC5" s="38" t="s">
+        <v>217</v>
+      </c>
+      <c r="HD5" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="HE5" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="HF5" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="HG5" s="36" t="s">
+        <v>221</v>
+      </c>
+      <c r="HH5" s="37" t="s">
+        <v>222</v>
+      </c>
+      <c r="HI5" s="36" t="s">
+        <v>223</v>
+      </c>
+      <c r="HJ5" s="36" t="s">
+        <v>224</v>
+      </c>
+      <c r="HK5" s="36" t="s">
+        <v>225</v>
+      </c>
+      <c r="HL5" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="HM5" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="HN5" s="36" t="s">
+        <v>228</v>
+      </c>
+      <c r="HO5" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="HP5" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="HQ5" s="36" t="s">
+        <v>231</v>
+      </c>
+      <c r="HR5" s="36" t="s">
+        <v>232</v>
+      </c>
+      <c r="HS5" s="37" t="s">
+        <v>233</v>
+      </c>
+      <c r="HT5" s="37" t="s">
+        <v>234</v>
+      </c>
+      <c r="HU5" s="37" t="s">
+        <v>235</v>
+      </c>
+      <c r="HV5" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="HW5" s="37" t="s">
+        <v>237</v>
+      </c>
+      <c r="HX5" s="37" t="s">
+        <v>238</v>
+      </c>
+      <c r="HY5" s="36" t="s">
+        <v>239</v>
+      </c>
+      <c r="HZ5" s="36" t="s">
+        <v>240</v>
+      </c>
+      <c r="IA5" s="37" t="s">
+        <v>241</v>
+      </c>
+      <c r="IB5" s="36" t="s">
+        <v>242</v>
+      </c>
+      <c r="IC5" s="36" t="s">
+        <v>243</v>
+      </c>
+      <c r="ID5" s="36" t="s">
+        <v>244</v>
+      </c>
+      <c r="IE5" s="36" t="s">
+        <v>245</v>
+      </c>
+      <c r="IF5" s="36" t="s">
+        <v>246</v>
+      </c>
+      <c r="IG5" s="36" t="s">
+        <v>247</v>
+      </c>
+      <c r="IH5" s="36" t="s">
+        <v>248</v>
+      </c>
+      <c r="II5" s="36" t="s">
+        <v>249</v>
+      </c>
+      <c r="IJ5" s="37" t="s">
+        <v>250</v>
+      </c>
+      <c r="IK5" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="IL5" s="37" t="s">
+        <v>252</v>
+      </c>
+      <c r="IM5" s="37" t="s">
+        <v>253</v>
+      </c>
+      <c r="IN5" s="37" t="s">
+        <v>254</v>
+      </c>
+      <c r="IO5" s="37" t="s">
+        <v>255</v>
+      </c>
+      <c r="IP5" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="IQ5" s="37" t="s">
+        <v>257</v>
+      </c>
+      <c r="IR5" s="37" t="s">
+        <v>258</v>
+      </c>
+      <c r="IS5" s="36" t="s">
+        <v>259</v>
+      </c>
+      <c r="IT5" s="36" t="s">
+        <v>260</v>
+      </c>
+      <c r="IU5" s="36" t="s">
+        <v>261</v>
+      </c>
+      <c r="IV5" s="36" t="s">
+        <v>262</v>
+      </c>
+      <c r="IW5" s="36" t="s">
+        <v>600</v>
+      </c>
+      <c r="IX5" s="36" t="s">
+        <v>263</v>
+      </c>
+      <c r="IY5" s="37" t="s">
+        <v>264</v>
+      </c>
+      <c r="IZ5" s="39" t="s">
+        <v>265</v>
+      </c>
+      <c r="JA5" s="39" t="s">
+        <v>266</v>
+      </c>
+      <c r="JB5" s="40" t="s">
+        <v>267</v>
+      </c>
+      <c r="JC5" s="40" t="s">
+        <v>268</v>
+      </c>
+      <c r="JD5" s="41" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="6" spans="1:264" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="50" t="s">
+        <v>587</v>
+      </c>
+      <c r="Q6" s="36" t="s">
+        <v>588</v>
+      </c>
+      <c r="R6" s="36" t="s">
+        <v>589</v>
+      </c>
+      <c r="S6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="T6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="U6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="V6" s="36" t="s">
+        <v>590</v>
+      </c>
+      <c r="W6" s="36" t="s">
+        <v>591</v>
+      </c>
+      <c r="X6" s="36" t="s">
+        <v>592</v>
+      </c>
+      <c r="Y6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="Z6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="AA6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="AB6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="AC6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="AD6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="AE6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="AF6" s="54" t="s">
+        <v>270</v>
+      </c>
+      <c r="AG6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="AH6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="AI6" s="54" t="s">
+        <v>270</v>
+      </c>
+      <c r="AJ6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="AK6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="AL6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="AM6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="AN6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="AO6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="AP6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="AQ6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="AR6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="AS6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="AT6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="AU6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="AV6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="AW6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="AX6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="AY6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="AZ6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="BA6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="BB6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="BC6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="BD6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="BE6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="BF6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="BG6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="BH6" s="40" t="s">
+        <v>593</v>
+      </c>
+      <c r="BI6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="BJ6" s="40" t="s">
+        <v>594</v>
+      </c>
+      <c r="BK6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="BL6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="BM6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="BN6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="BO6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="BP6" s="39" t="s">
+        <v>594</v>
+      </c>
+      <c r="BQ6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="BR6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="BS6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="BT6" s="40" t="s">
+        <v>595</v>
+      </c>
+      <c r="BU6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="BV6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="BW6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="BX6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="BY6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="BZ6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="CA6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="CB6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="CC6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="CD6" s="39" t="s">
+        <v>596</v>
+      </c>
+      <c r="CE6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="CF6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="CG6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="CH6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="CI6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="CJ6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="CK6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="CL6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="CM6" s="40" t="s">
+        <v>273</v>
+      </c>
+      <c r="CN6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="CO6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="CP6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="CQ6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="CR6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="CS6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="CT6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="CU6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="CV6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="CW6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="CX6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="CY6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="CZ6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="DA6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="DB6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="DC6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="DD6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="DE6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="DF6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="DG6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="DH6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="DI6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="DJ6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="DK6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="DL6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="DM6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="DN6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="DO6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="DP6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="DQ6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="DR6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="DS6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="DT6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="DU6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="DV6" s="39" t="s">
+        <v>270</v>
+      </c>
+      <c r="DW6" s="40" t="s">
+        <v>270</v>
+      </c>
+      <c r="DX6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="DY6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="DZ6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="EA6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="EB6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="EC6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="ED6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="EE6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="EF6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="EG6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="EH6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="EI6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="EJ6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="EK6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="EL6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="EM6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="EN6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="EO6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="EP6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="EQ6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="ER6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="ES6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="ET6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="EU6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="EV6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="EW6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="EX6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="EY6" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="EZ6" s="39" t="s">
+        <v>597</v>
+      </c>
+      <c r="FA6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="FB6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="FC6" s="36" t="s">
+        <v>271</v>
+      </c>
+      <c r="FD6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="FE6" s="36" t="s">
+        <v>272</v>
+      </c>
+      <c r="FF6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="FG6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="FH6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="FI6" s="37" t="s">
+        <v>273</v>
+      </c>
+      <c r="FJ6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="FK6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="FL6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="FM6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="FN6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="FO6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="FP6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="FQ6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="FR6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="FS6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="FT6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="FU6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="FV6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="FW6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="FX6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="FY6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="FZ6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="GA6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="GB6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="GC6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="GD6" s="37" t="s">
+        <v>274</v>
+      </c>
+      <c r="GE6" s="36" t="s">
+        <v>275</v>
+      </c>
+      <c r="GF6" s="37" t="s">
+        <v>276</v>
+      </c>
+      <c r="GG6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="GH6" s="37"/>
+      <c r="GI6" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="GJ6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="GK6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="GL6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="GM6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="GN6" s="37" t="s">
+        <v>278</v>
+      </c>
+      <c r="GO6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="GP6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="GQ6" s="36" t="s">
+        <v>279</v>
+      </c>
+      <c r="GR6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="GS6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="GT6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="GU6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="GV6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="GW6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="GX6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="GY6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="GZ6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="HA6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="HB6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="HC6" s="38" t="s">
+        <v>280</v>
+      </c>
+      <c r="HD6" s="38"/>
+      <c r="HE6" s="36" t="s">
+        <v>281</v>
+      </c>
+      <c r="HF6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="HG6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="HH6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="HI6" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="HJ6" s="36" t="s">
+        <v>283</v>
+      </c>
+      <c r="HK6" s="36" t="s">
+        <v>284</v>
+      </c>
+      <c r="HL6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="HM6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="HN6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="HO6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="HP6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="HQ6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="HR6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="HS6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="HT6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="HU6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="HV6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="HW6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="HX6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="HY6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="HZ6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="IA6" s="37" t="s">
+        <v>285</v>
+      </c>
+      <c r="IB6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="IC6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="ID6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="IE6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="IF6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="IG6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="IH6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="II6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="IJ6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="IK6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="IL6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="IM6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="IN6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="IO6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="IP6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="IQ6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="IR6" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="IS6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="IT6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="IU6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="IV6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="IW6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="IX6" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="IY6" s="37" t="s">
+        <v>286</v>
+      </c>
+      <c r="IZ6" s="39" t="s">
+        <v>287</v>
+      </c>
+      <c r="JA6" s="39" t="s">
+        <v>288</v>
+      </c>
+      <c r="JB6" s="40" t="s">
+        <v>289</v>
+      </c>
+      <c r="JC6" s="40" t="s">
+        <v>290</v>
+      </c>
+      <c r="JD6" s="41"/>
+    </row>
+    <row r="7" spans="1:264" x14ac:dyDescent="0.25">
+      <c r="A7" s="28"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="28"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="50" t="s">
+        <v>598</v>
+      </c>
+      <c r="Q7" s="36" t="s">
+        <v>292</v>
+      </c>
+      <c r="R7" s="36" t="s">
+        <v>292</v>
+      </c>
+      <c r="S7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="T7" s="36" t="s">
+        <v>292</v>
+      </c>
+      <c r="U7" s="36" t="s">
+        <v>292</v>
+      </c>
+      <c r="V7" s="36" t="s">
+        <v>292</v>
+      </c>
+      <c r="W7" s="36" t="s">
+        <v>292</v>
+      </c>
+      <c r="X7" s="36" t="s">
+        <v>292</v>
+      </c>
+      <c r="Y7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="Z7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="AA7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="AB7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="AC7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="AD7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="AE7" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="AF7" s="51" t="s">
+        <v>291</v>
+      </c>
+      <c r="AG7" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="AH7" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="AI7" s="51" t="s">
+        <v>291</v>
+      </c>
+      <c r="AJ7" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="AK7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="AL7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="AM7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="AN7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="AO7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="AP7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="AQ7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="AR7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="AS7" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="AT7" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="AU7" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="AV7" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="AW7" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="AX7" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="AY7" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="AZ7" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="BA7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="BB7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="BC7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="BD7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="BE7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="BF7" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="BG7" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="BH7" s="40" t="s">
+        <v>293</v>
+      </c>
+      <c r="BI7" s="40" t="s">
+        <v>293</v>
+      </c>
+      <c r="BJ7" s="40" t="s">
+        <v>293</v>
+      </c>
+      <c r="BK7" s="40" t="s">
+        <v>293</v>
+      </c>
+      <c r="BL7" s="40" t="s">
+        <v>293</v>
+      </c>
+      <c r="BM7" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="BN7" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="BO7" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="BP7" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="BQ7" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="BR7" s="40" t="s">
+        <v>294</v>
+      </c>
+      <c r="BS7" s="40" t="s">
+        <v>294</v>
+      </c>
+      <c r="BT7" s="40" t="s">
+        <v>294</v>
+      </c>
+      <c r="BU7" s="40" t="s">
+        <v>294</v>
+      </c>
+      <c r="BV7" s="40" t="s">
+        <v>294</v>
+      </c>
+      <c r="BW7" s="40" t="s">
+        <v>294</v>
+      </c>
+      <c r="BX7" s="40" t="s">
+        <v>294</v>
+      </c>
+      <c r="BY7" s="40" t="s">
+        <v>294</v>
+      </c>
+      <c r="BZ7" s="40" t="s">
+        <v>294</v>
+      </c>
+      <c r="CA7" s="39" t="s">
+        <v>294</v>
+      </c>
+      <c r="CB7" s="39" t="s">
+        <v>294</v>
+      </c>
+      <c r="CC7" s="39" t="s">
+        <v>294</v>
+      </c>
+      <c r="CD7" s="39" t="s">
+        <v>294</v>
+      </c>
+      <c r="CE7" s="39" t="s">
+        <v>294</v>
+      </c>
+      <c r="CF7" s="39" t="s">
+        <v>294</v>
+      </c>
+      <c r="CG7" s="40" t="s">
+        <v>294</v>
+      </c>
+      <c r="CH7" s="40" t="s">
+        <v>294</v>
+      </c>
+      <c r="CI7" s="40" t="s">
+        <v>294</v>
+      </c>
+      <c r="CJ7" s="40" t="s">
+        <v>294</v>
+      </c>
+      <c r="CK7" s="40" t="s">
+        <v>294</v>
+      </c>
+      <c r="CL7" s="39" t="s">
+        <v>294</v>
+      </c>
+      <c r="CM7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="CN7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="CO7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="CP7" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="CQ7" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="CR7" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="CS7" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="CT7" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="CU7" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="CV7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="CW7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="CX7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="CY7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="CZ7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="DA7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="DB7" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="DC7" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="DD7" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="DE7" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="DF7" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="DG7" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="DH7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="DI7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="DJ7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="DK7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="DL7" s="39" t="s">
+        <v>294</v>
+      </c>
+      <c r="DM7" s="40" t="s">
+        <v>294</v>
+      </c>
+      <c r="DN7" s="40" t="s">
+        <v>294</v>
+      </c>
+      <c r="DO7" s="40" t="s">
+        <v>294</v>
+      </c>
+      <c r="DP7" s="40" t="s">
+        <v>294</v>
+      </c>
+      <c r="DQ7" s="39" t="s">
+        <v>294</v>
+      </c>
+      <c r="DR7" s="39" t="s">
+        <v>294</v>
+      </c>
+      <c r="DS7" s="39" t="s">
+        <v>294</v>
+      </c>
+      <c r="DT7" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="DU7" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="DV7" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="DW7" s="40" t="s">
+        <v>293</v>
+      </c>
+      <c r="DX7" s="40" t="s">
+        <v>293</v>
+      </c>
+      <c r="DY7" s="40" t="s">
+        <v>293</v>
+      </c>
+      <c r="DZ7" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="EA7" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="EB7" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="EC7" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="ED7" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="EE7" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="EF7" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="EG7" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="EH7" s="40" t="s">
+        <v>293</v>
+      </c>
+      <c r="EI7" s="40" t="s">
+        <v>293</v>
+      </c>
+      <c r="EJ7" s="40" t="s">
+        <v>293</v>
+      </c>
+      <c r="EK7" s="40" t="s">
+        <v>293</v>
+      </c>
+      <c r="EL7" s="40" t="s">
+        <v>293</v>
+      </c>
+      <c r="EM7" s="40" t="s">
+        <v>293</v>
+      </c>
+      <c r="EN7" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="EO7" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="EP7" s="40" t="s">
+        <v>293</v>
+      </c>
+      <c r="EQ7" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="ER7" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="ES7" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="ET7" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="EU7" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="EV7" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="EW7" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="EX7" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="EY7" s="40" t="s">
+        <v>293</v>
+      </c>
+      <c r="EZ7" s="39" t="s">
+        <v>292</v>
+      </c>
+      <c r="FA7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="FB7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="FC7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="FD7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="FE7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="FF7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="FG7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="FH7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="FI7" s="37" t="s">
+        <v>291</v>
+      </c>
+      <c r="FJ7" s="37" t="s">
+        <v>291</v>
+      </c>
+      <c r="FK7" s="37" t="s">
+        <v>291</v>
+      </c>
+      <c r="FL7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="FM7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="FN7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="FO7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="FP7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="FQ7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="FR7" s="37" t="s">
+        <v>291</v>
+      </c>
+      <c r="FS7" s="37" t="s">
+        <v>291</v>
+      </c>
+      <c r="FT7" s="37" t="s">
+        <v>291</v>
+      </c>
+      <c r="FU7" s="37" t="s">
+        <v>291</v>
+      </c>
+      <c r="FV7" s="37" t="s">
+        <v>291</v>
+      </c>
+      <c r="FW7" s="37" t="s">
+        <v>291</v>
+      </c>
+      <c r="FX7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="FY7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="FZ7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="GA7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="GB7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="GC7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="GD7" s="37" t="s">
+        <v>292</v>
+      </c>
+      <c r="GE7" s="36" t="s">
+        <v>292</v>
+      </c>
+      <c r="GF7" s="37" t="s">
+        <v>293</v>
+      </c>
+      <c r="GG7" s="37" t="s">
+        <v>293</v>
+      </c>
+      <c r="GH7" s="37"/>
+      <c r="GI7" s="36" t="s">
+        <v>293</v>
+      </c>
+      <c r="GJ7" s="36" t="s">
+        <v>293</v>
+      </c>
+      <c r="GK7" s="37" t="s">
+        <v>292</v>
+      </c>
+      <c r="GL7" s="37" t="s">
+        <v>292</v>
+      </c>
+      <c r="GM7" s="37" t="s">
+        <v>292</v>
+      </c>
+      <c r="GN7" s="37" t="s">
+        <v>291</v>
+      </c>
+      <c r="GO7" s="37" t="s">
+        <v>291</v>
+      </c>
+      <c r="GP7" s="37" t="s">
+        <v>291</v>
+      </c>
+      <c r="GQ7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="GR7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="GS7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="GT7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="GU7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="GV7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="GW7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="GX7" s="37" t="s">
+        <v>293</v>
+      </c>
+      <c r="GY7" s="36" t="s">
+        <v>294</v>
+      </c>
+      <c r="GZ7" s="36" t="s">
+        <v>294</v>
+      </c>
+      <c r="HA7" s="36" t="s">
+        <v>294</v>
+      </c>
+      <c r="HB7" s="36" t="s">
+        <v>294</v>
+      </c>
+      <c r="HC7" s="38" t="s">
+        <v>291</v>
+      </c>
+      <c r="HD7" s="38"/>
+      <c r="HE7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="HF7" s="37" t="s">
+        <v>291</v>
+      </c>
+      <c r="HG7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="HH7" s="37" t="s">
+        <v>291</v>
+      </c>
+      <c r="HI7" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="HJ7" s="36" t="s">
+        <v>295</v>
+      </c>
+      <c r="HK7" s="36" t="s">
+        <v>295</v>
+      </c>
+      <c r="HL7" s="37" t="s">
+        <v>296</v>
+      </c>
+      <c r="HM7" s="36" t="s">
+        <v>293</v>
+      </c>
+      <c r="HN7" s="36" t="s">
+        <v>293</v>
+      </c>
+      <c r="HO7" s="36" t="s">
+        <v>293</v>
+      </c>
+      <c r="HP7" s="36" t="s">
+        <v>293</v>
+      </c>
+      <c r="HQ7" s="36" t="s">
+        <v>293</v>
+      </c>
+      <c r="HR7" s="36" t="s">
+        <v>293</v>
+      </c>
+      <c r="HS7" s="37" t="s">
+        <v>293</v>
+      </c>
+      <c r="HT7" s="37" t="s">
+        <v>293</v>
+      </c>
+      <c r="HU7" s="37" t="s">
+        <v>293</v>
+      </c>
+      <c r="HV7" s="37" t="s">
+        <v>293</v>
+      </c>
+      <c r="HW7" s="37" t="s">
+        <v>293</v>
+      </c>
+      <c r="HX7" s="37" t="s">
+        <v>293</v>
+      </c>
+      <c r="HY7" s="36" t="s">
+        <v>293</v>
+      </c>
+      <c r="HZ7" s="36" t="s">
+        <v>293</v>
+      </c>
+      <c r="IA7" s="37" t="s">
+        <v>293</v>
+      </c>
+      <c r="IB7" s="36" t="s">
+        <v>293</v>
+      </c>
+      <c r="IC7" s="36" t="s">
+        <v>293</v>
+      </c>
+      <c r="ID7" s="36" t="s">
+        <v>293</v>
+      </c>
+      <c r="IE7" s="36" t="s">
+        <v>293</v>
+      </c>
+      <c r="IF7" s="36" t="s">
+        <v>293</v>
+      </c>
+      <c r="IG7" s="36" t="s">
+        <v>293</v>
+      </c>
+      <c r="IH7" s="36" t="s">
+        <v>293</v>
+      </c>
+      <c r="II7" s="36" t="s">
+        <v>293</v>
+      </c>
+      <c r="IJ7" s="37" t="s">
+        <v>294</v>
+      </c>
+      <c r="IK7" s="37" t="s">
+        <v>294</v>
+      </c>
+      <c r="IL7" s="37" t="s">
+        <v>294</v>
+      </c>
+      <c r="IM7" s="37" t="s">
+        <v>294</v>
+      </c>
+      <c r="IN7" s="37" t="s">
+        <v>294</v>
+      </c>
+      <c r="IO7" s="37" t="s">
+        <v>294</v>
+      </c>
+      <c r="IP7" s="37" t="s">
+        <v>294</v>
+      </c>
+      <c r="IQ7" s="37" t="s">
+        <v>294</v>
+      </c>
+      <c r="IR7" s="37" t="s">
+        <v>294</v>
+      </c>
+      <c r="IS7" s="36" t="s">
+        <v>294</v>
+      </c>
+      <c r="IT7" s="36" t="s">
+        <v>294</v>
+      </c>
+      <c r="IU7" s="36" t="s">
+        <v>294</v>
+      </c>
+      <c r="IV7" s="36" t="s">
+        <v>294</v>
+      </c>
+      <c r="IW7" s="36" t="s">
+        <v>294</v>
+      </c>
+      <c r="IX7" s="36" t="s">
+        <v>294</v>
+      </c>
+      <c r="IY7" s="37" t="s">
+        <v>292</v>
+      </c>
+      <c r="IZ7" s="39" t="s">
+        <v>297</v>
+      </c>
+      <c r="JA7" s="39" t="s">
+        <v>297</v>
+      </c>
+      <c r="JB7" s="40" t="s">
+        <v>292</v>
+      </c>
+      <c r="JC7" s="40" t="s">
+        <v>292</v>
+      </c>
+      <c r="JD7" s="35" t="s">
+        <v>291</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="82">
+    <mergeCell ref="IJ3:IR3"/>
+    <mergeCell ref="IS3:IX3"/>
+    <mergeCell ref="GF3:GG3"/>
+    <mergeCell ref="GI3:GJ3"/>
+    <mergeCell ref="HC3:HD3"/>
+    <mergeCell ref="HM3:HR3"/>
+    <mergeCell ref="HS3:HX3"/>
+    <mergeCell ref="HY3:HZ3"/>
+    <mergeCell ref="DM3:DP3"/>
+    <mergeCell ref="DQ3:DS3"/>
+    <mergeCell ref="DZ3:EG3"/>
+    <mergeCell ref="EH3:EM3"/>
+    <mergeCell ref="EN3:EO3"/>
+    <mergeCell ref="EQ3:EX3"/>
+    <mergeCell ref="BH3:BL3"/>
+    <mergeCell ref="BM3:BQ3"/>
+    <mergeCell ref="BR3:BZ3"/>
+    <mergeCell ref="CA3:CF3"/>
+    <mergeCell ref="CG3:CK3"/>
+    <mergeCell ref="CM3:CO3"/>
+    <mergeCell ref="IJ2:IX2"/>
+    <mergeCell ref="IY2:IY3"/>
+    <mergeCell ref="IZ2:JA3"/>
+    <mergeCell ref="JB2:JC3"/>
+    <mergeCell ref="Y3:AD3"/>
+    <mergeCell ref="AE3:AJ3"/>
+    <mergeCell ref="AK3:AR3"/>
+    <mergeCell ref="AS3:AZ3"/>
+    <mergeCell ref="BA3:BE3"/>
+    <mergeCell ref="BF3:BG3"/>
+    <mergeCell ref="GX2:GX3"/>
+    <mergeCell ref="GY2:HB3"/>
+    <mergeCell ref="HC2:HI2"/>
+    <mergeCell ref="HJ2:HK3"/>
+    <mergeCell ref="HL2:HL3"/>
+    <mergeCell ref="HM2:II2"/>
+    <mergeCell ref="IB3:II3"/>
+    <mergeCell ref="EZ2:EZ3"/>
+    <mergeCell ref="FA2:FH3"/>
+    <mergeCell ref="FI2:GC2"/>
+    <mergeCell ref="GD2:GJ2"/>
+    <mergeCell ref="GK2:GP3"/>
+    <mergeCell ref="GQ2:GW3"/>
+    <mergeCell ref="FI3:FK3"/>
+    <mergeCell ref="FL3:FQ3"/>
+    <mergeCell ref="FR3:FW3"/>
+    <mergeCell ref="FX3:GC3"/>
+    <mergeCell ref="CM2:DK2"/>
+    <mergeCell ref="DL2:DS2"/>
+    <mergeCell ref="DT2:DT3"/>
+    <mergeCell ref="DU2:DY3"/>
+    <mergeCell ref="DZ2:EX2"/>
+    <mergeCell ref="EY2:EY3"/>
+    <mergeCell ref="CP3:CU3"/>
+    <mergeCell ref="CV3:DA3"/>
+    <mergeCell ref="DB3:DG3"/>
+    <mergeCell ref="DH3:DK3"/>
+    <mergeCell ref="P1:P4"/>
+    <mergeCell ref="Q1:X1"/>
+    <mergeCell ref="Y1:EZ1"/>
+    <mergeCell ref="FA1:IY1"/>
+    <mergeCell ref="IZ1:JC1"/>
+    <mergeCell ref="JD1:JD3"/>
+    <mergeCell ref="Q2:X3"/>
+    <mergeCell ref="Y2:BG2"/>
+    <mergeCell ref="BH2:BQ2"/>
+    <mergeCell ref="BR2:CL2"/>
+    <mergeCell ref="J1:J7"/>
+    <mergeCell ref="K1:K7"/>
+    <mergeCell ref="L1:L7"/>
+    <mergeCell ref="M1:M7"/>
+    <mergeCell ref="N1:N7"/>
+    <mergeCell ref="O1:O7"/>
+    <mergeCell ref="A1:A7"/>
+    <mergeCell ref="B1:B7"/>
+    <mergeCell ref="C1:C7"/>
+    <mergeCell ref="D1:D7"/>
+    <mergeCell ref="E1:E7"/>
+    <mergeCell ref="F1:F7"/>
+    <mergeCell ref="G1:G7"/>
+    <mergeCell ref="H1:H7"/>
+    <mergeCell ref="I1:I7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5902BFF-1298-4FA3-8DB5-A80B8D650BBE}">
   <dimension ref="A1:U2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
